--- a/data/articulos.xlsx
+++ b/data/articulos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,11 @@
           <t>Resumen 3 lineas</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Justificación categoría</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -519,6 +524,7 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -559,6 +565,7 @@
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -599,6 +606,7 @@
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -639,6 +647,5499 @@
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Research on Enterprise Security Operation Based on Large Model Technology</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Li L.; Wang T.; An Q.; Dong J.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>10.1145/3773365.3773614</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Graph Analysis Technology, Large Model Technology, Security Operation, The Multimodal Parsing, Artificial intelligence, Data privacy, Information management, Network security, Security systems, Enterprise security, Graph analysis, Graph analyze technology, Large models, Modeling technology, Security operation center, Security operations, Cost effectiveness, enterprise, incident response, soc</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>With the continuous evolution of cyber threats and the growing complexity of enterprise IT infrastructures, traditional Security Operations Centers (SOCs) face challenges such as alert overload, talent shortages, and the limitations of rule-based engines. Large-model technology (LMT) provides a new pathway toward intelligent and automated security operations. This study analyzes key techniques - including the Transformer architecture, the pre-training and fine-tuning paradigm, and multimodal learning - and validates their effectiveness through practical case studies in industries such as finance and manufacturing.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, models, artificial intelligence, transformer, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Evaluating Human-Machine Interaction Paradigms for Effective Human-Artificial Intelligence Collaboration in Cybersecurity</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Malatji M.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>10.1109/ICICYTA64807.2024.10913015</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>AI in cybersecurity, automated security, cybersecurity operations, human-AI teaming, human-machine interaction (HMI), incident response, Risk management, Artificial intelligence in cybersecurity, Cyber security, Cybersecurity operation, Human machine interaction, Human-artificial intelligence teaming, Human-machine interaction, Interaction paradigm, Decision making, management, detection, threat detection</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>This paper examines the efficacy of various Human-Machine Interaction (HMI) paradigms in enhancing cybersecurity practices through human-artificial intelligence (AI) collaboration. As cyber threats grow increasingly sophisticated, organisations are turning to AI to bolster their defence mechanisms, threat detection, incident response, and overall security management. Six HMI paradigms are analyzed: Humans in the Loop (HITL), Humans on the Loop (HOTL), Humans out of the Loop (HOOTL), Humans alongside the Loop (HATL), Humans-in-command (HIC), and Coactive Systems.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Generative Artificial Intelligence and Cybersecurity Risks: Implications for Healthcare Security Based on Real-life Incidents</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sallam M.; Al-Mahzoum K.; Sallam M.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F8" t="n">
+        <v>13</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>10.58496/MJAIH/2024/019</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Cybersecurity, Health care, Privacy, Risk, Threat, impact, governance, incident response, algorithms, artificial intelligence</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Background: The potential of generative artificial intelligence (genAI) tools, such as ChatGPT, is being increasingly explored in healthcare settings. However, the same tools also introduce significant cybersecurity risks that could compromise patient safety, data integrity, and institutional trust. This study aimed to examine real-world security breaches involving genAI and extrapolate their potential implications for healthcare settings.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, algorithms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Data-Driven Intelligence Can Revolutionize Today’s Cybersecurity World: A Position Paper</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sarker I.H.; Janicke H.; Maglaras L.; Camtepe S.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-48855-9_23</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>AI, Augmenting Experts Knowledge, Automation, Cybersecurity, Data-Driven Intelligence, Human Assistance, Machine Learning, Decision making, Predictive analytics, Augmenting expert knowledge, Cyber security, Cyber threats, Data driven, Decisions makings, Expert knowledge, Machine-learning, Position papers, incident response, detection, threat detection</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>As cyber threats evolve and grow progressively more sophisticated, cyber security is becoming a more significant concern in today’s digital era. Traditional security measures tend to be insufficient to defend against these persistent and dynamic threats because they are mainly intuitional. One of the most promising ways to handle this ongoing problem is utilizing the potential of data-driven intelligence, by leveraging AI and machine learning techniques.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A Machine Learning Approach to Detection of Critical Alerts from Imbalanced Multi-Appliance Threat Alert Logs</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ndichu S.; Ban T.; Takahashi T.; Inoue D.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F10" t="n">
+        <v>19</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>10.1109/BigData52589.2021.9671956</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>alert fatigue, alert screening, Class imbalance, data cleaning, machine learning, oversampling, Information management, Intrusion detection, Random forests, Support vector machines, Alert data, Machine learning approaches, Network intrusion detection systems, Over sampling, Securities analysts, Security alerts, Decision trees, management, incident response, process</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>The extraordinary number of alerts generated by network intrusion detection systems (NIDS) can desensitize security analysts tasked with incident response. Security information and event management systems (SIEMs) perform some rudimentary automation but cannot replicate the decision-making process of a skilled analyst. Machine learning and artificial intelligence (AI) can detect patterns in data with appropriate training.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, detection, artificial intelligence, intrusion detection, random forest, support vector machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Automation Bias and Complacency in Security Operation Centers</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tilbury J.; Flowerday S.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>10.3390/computers13070165</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>artificial intelligence, automation, automation bias, automation complacency, decision support systems, human-in-the-loop, machine learning, security analyst, security operation center, incident response, soc, processes, detection</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>The volume and complexity of alerts that security operation center (SOC) analysts must manage necessitate automation. Increased automation in SOCs amplifies the risk of automation bias and complacency whereby security analysts become over-reliant on automation, failing to seek confirmatory or contradictory information. To identify automation characteristics that assist in the mitigation of automation bias and complacency, we investigated the current and proposed application areas of automation in SOCs and discussed its implications for security analysts.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, artificial intelligence, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Digital Safeguards: Unravelling the Complex Interplay Between Emerging Threats and Proactive Cyber Defence Strategies</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Aladiyan A.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>10.58346/JISIS.2025.I1.022</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AI, Anomaly Detection, Automation, Cybersecurity, Data Privacy, Ethical Considerations, Incident Response, Machine Learning, Predictive Analytics, Threat Detection, company, process, algorithms, models, artificial intelligence, detection</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>In the past few years, advanced cyber security capabilities have flourished via a new era of use in dangerous A.I. technologies rapidly developed strategies using dozens of different online risks to even more effectively prevent, detect, and respond prolifically. With digital infrastructures being the backbone of enterprises today, cyber-attacks have grown in complexity and sophistication over time to thrive as we know them now this effectively means that security frameworks would need AI after that.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: algorithms, models, machine learning, artificial intelligence, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>On Cybersecurity Incident Response Decision Support System in Smart Grids</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sen O.; Mahjoob A.; Neumuller M.; Ulbig A.; Decker S.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>10.1109/SmartGridComm65349.2025.11204644</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Cyberattack, Cybersecurity, Decision Support System, Incident Response, Smart Grid, Artificial intelligence, Behavioral research, Computer crime, Decision making, Industrial management, Information management, Network security, User interfaces, Cyber security, Cyber-attacks, Decision supports, Decisions makings, Help systems, Modulars, Support systems</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>The growing complexity of control systems in smart grids has increased their vulnerability to cyber-attacks. In this paper, we introduce a modular decision support system to help system operators prioritize and select countermeasures following a cyber-incident. The proposed system combines attack graph analysis with multi-criteria decision-making techniques, enabling the evaluation of response actions based on customizable priorities such as cost, technical impact, and time required for deployment.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: incident response, management, decision making.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Human-centric Artificial Intelligence enabled Digital Images and Videos Forensic Triage</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Li S.; Liu Y.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>10.1109/HCCS59561.2023.10452651</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Artificial intelligence, Digital forensics, forensics triage, Image recognition and classification, Decision making, Electronic crime countermeasures, Image classification, Image recognition, Decisions makings, Digital image forensics, Digital system, Digital video forensics, Effectiveness and efficiencies, Forensic analysis, Forensic triage, Forensics investigators, Human-centric, Incident response, processes</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Digital forensics and incident response (DFIR) involve huge volume of data collected from digital systems that requires investigators to quickly sift through and prioritise relevant evidence. The forensics investigator team faces many challenges when analysing the processes to keep them on target and improve them. A lack of a systematic approach to data analysis can lead to slower decision-making.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: decision making, incident response, processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Hybrid LSTM-QEQ Framework for Enhanced Cyber Threat Detection and Response in Critical Power Grid Infrastructure</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Shi J.; Wang H.; Lu G.; Wang M.; Jiang X.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>10.1142/S021812662650091X</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>artificial intelligence, big data, cybersecurity, deep learning, Power grid, security warning, company, management, incident response, algorithms, model, detection, threat detection, framework, lstm</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>The rising multifaceted nature of cyber threats to critical Power Grid Infrastructure calls for new approaches in ensuring power systems resiliency and stability. Existing methods based on deep learning and predictive analysis have shown significant gains in the area of threat mitigation and response time. However, such approaches have been rendered limited in their scope by their lack of dynamic reaction to the shifts in cyberattack tactics, particularly in sequential and multi-dimensional settings.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, threat detection, framework, lstm, algorithms, model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CRUSOE: A toolset for cyber situational awareness and decision support in incident handling</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Husák M.; Sadlek L.; Špaček S.; Laštovička M.; Javorník M.; Komárková J.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>10.1016/j.cose.2022.102609</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Cyber situational awareness, Decision support, Incident response, Network monitoring, OODA Loop, Artificial intelligence, Cybersecurity, Data visualization, Network security, Cybe situational awareness, Cyber security, Decision supports, Security operation center, Security situation, Situational awareness, Toolsets, Decision support systems, process</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>The growing size and complexity of today's computer network make it hard to achieve and maintain so-called cyber situational awareness, i.e., the ability to perceive and comprehend the cyber environment and be able to project the situation in the near future. Namely, the personnel of cybersecurity incident response teams or security operation centers should be aware of the security situation in the network to effectively prevent or mitigate cyber attacks and avoid mistakes in the process. In this paper, we present a toolset for achieving cyber situational awareness in a large and heterogeneous environment.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: incident response, process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A cases and clusters framework for recording, retrieving, and reusing response plans in structured cybersecurity incident management</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Guerra P.A.C.; Nunes R.C.; de Lima Silva L.A.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>10.1016/j.engappai.2025.111831</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Case-based reasoning, Clustering, Cybersecurity, Cybersecurity incident response, Decision-support system, Explainable artificial intelligence, Ontology, Case based reasoning, Cluster analysis, Decision making, Query processing, Casebased reasonings (CBR), Clusterings, Cyber security, Decision supports, Incident response, Ontology's, Support systems, Decision support systems, organization</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>The dynamic and increasing sophistication of cyberattacks and vulnerability exploitation creates a need for Explainable Artificial Intelligence (XAI) approaches that help maintain cyber resilience in organizations. In structured cybersecurity incident management, effective incident response demands explainable outputs from AI-based decision-support systems. To approach this problem, this work presents a framework for reusing concrete experiences of cybersecurity incident response, capturing problem-solving data and knowledge as cases for integrated Case-Based Reasoning (CBR) and Clustering.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, incident management, organization, decision making, incident response, process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Multi-agent DSS for Smart Government Crisis Management</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Jiang H.; Wang Y.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-51734-1_7</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Crisis, Crisis Management, Decision Support System, Multi-Agent, Smart Government, Data warehouses, Decision making, Information management, Intelligent agents, Multi agent systems, Decision evaluations, Decision makers, Decision supports, Decision-making process, Decisions makings, Evaluation and analysis, Multi agent, Decision support systems, government, management</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>The conventional government fails to acknowledge the paramount importance of data in crisis management. The Decision Support System (DSS) for intelligent governance can furnish decision makers with effective crisis decision support. The process of government crisis decision-making entails the pre-decision monitoring of big data on crisis information, situation simulation during the decision-making process, and post-decision evaluation and analysis, thereby establishing a cyclical framework.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, governance, decision making, incident response, process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Enhancing cybersecurity incident response: AI-driven optimization for strengthened advanced persistent threat detection</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ali G.; Shah S.; ElAffendi M.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F19" t="n">
+        <v>24</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>10.1016/j.rineng.2025.104078</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Cybersecurity incident response, Machine learning, Security information and event management, Cyber attacks, Cyber security, False positive, Incident response, Machine learning techniques, Machine-learning, Optimisations, Security incident, Security information and event managements, Threat detection, Adversarial machine learning, organizational, management, process, model, detection, dataset</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>The Cyber Security Incident Response Team executes its critical duties in the Centralized Security Operation Centers. Its primary target is to protect organizational resources from all types of Advanced Persistent Threats (APTs) and attacks while making the correct judgments at the right time. Despite the great efforts and the efficient tools, the incident response mechanism faces two significant challenges.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, threat detection, model, machine learning, dataset, random forest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>UAV-Enabled Intelligent Traffic Management Using Multi-Modal Deep Learning and IoT Integration</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sahutoglu Z.; Bakirci M.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>10.1109/IISEC69317.2026.11418411</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>autonomous traffic monitoring, CNN-Transformer hybrid model, communication networks, deep learning, edge computing, intelligent transportation systems, multi-modal data fusion, real-time object detection, smart cities, UAV-IoT integration, Advanced traffic management systems, Aircraft detection, Antennas, Decision making, Highway traffic control, Internet of things, Modal analysis, Motor transportation, Network architecture, Object detection</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>The continued expansion of urban mobility and the growing complexity of connected transportation infrastructures have increased the need for real-time traffic monitoring and adaptive control mechanisms. In response to this demand, this work introduces a UAV-enabled intelligent traffic management framework that combines multi-modal deep learning with IoT-based communication networks to support dynamic traffic assessment and rapid incident response. A fleet of UAVs equipped with vision and MEMS-based sensors collects aerial observations, which are subsequently fused with data from ground-based IoT sensors to identify congestion patterns, roadway anomalies, and emerging hazards.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: deep learning, model, transformer, detection, framework, cnn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Maritime Cyber Security Platform (MCSP)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Laurenza G.; Tacconi R.; Dri M.; Landucci S.; Alì D.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>10.3233/PMST250137</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>cyber security, maritime, management, incident response, processes, artificial intelligence, framework</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>The Maritime Cyber Security Platform (MCSP) is an advanced, specialized security monitoring framework tailored specifically to the maritime domain. Its primary function is to collect and analyze data from a vessel’s digital systems. The platform is designed to identify anomalous activities and potential threats targeting onboard systems, thus enhancing the vessel’s overall cyber resilience.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, incident response, processes, decision making.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>QuickSAT/SHERLOCK-MD, A System For Autonomous Operations And Health Management of Gateway</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Santangelo A.D.; Falco G.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>10.2514/6.2024-2417</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Anomaly detection, Classification (of information), Decision support systems, Failure analysis, Fault detection, Knowledge based systems, Orbits, Risk assessment, Autonomous operations, Classification functions, Fault classification, Faults detection, Health management, Management functions, Operation management, Security risks, Vehicle health management, Vehicle management systems, NASA, management</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>sci_Zone, Inc and Cornell University are conducting research to develop QuickSAT/SHERLOCK-MD, a system for Vehicle Health Management and Fault Detection with Fault Classification Functions for the Gateway Lunar Platform. The QuickSAT/Vehicle Management System (VMS) is a flight proven flight management, Vehicle Health Management plus Fault Detection system flown on DARPA and U.S. Space Force flights.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: models, artificial intelligence, classification, detection, anomaly detection, datasets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Deep Learning-Based Hyperparameter Optimization for Enhanced Segmentation of RGB Images in Oil Spill Detection Within Port Environments</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Kurah I.M.; Adamu S.; Alhussian H.; Alwadain A.; Aliyu D.A.; Mamman H.; Garba A.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>10.1109/ACCESS.2025.3599593</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Deep learning, Deeplab, drone imagery, hyperparameter optimization, oil spill detection, port environments, Aircraft detection, Convolution, Convolutional neural networks, Drones, Environmental protection, Learning algorithms, Learning systems, Network architecture, Oil spills, Semantic Segmentation, Semantic Web, Semantics, Transfer learning, Cross validation</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Accurate detection of oil spills in dynamic port environments remains critical for timely response and effective environmental protection. Recent studies have explored the application of deep learning models to high-resolution RGB imagery; however, challenges persist due to the complex visual characteristics of ports, including dynamic water surfaces, infrastructural occlusions, and heterogeneous backgrounds. Traditional detection approaches have demonstrated limited robustness under such conditions, often resulting in elevated rates of false positives and missed detections.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: deep learning, detection, algorithms, model, models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Predicting the duration of motorway incidents using machine learning</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Corbally R.; Yang L.; Malekjafarian A.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>10.1186/s12544-024-00632-6</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Classification, Incident duration, Incident management, Incident response, M50 motorway, Machine learning, Motorway operations, Regression, Road traffic collisions, Traffic incidents, Decision making, Forecasting, Highway administration, Highway planning, Learning algorithms, Learning systems, Motor transportation, Roads and streets, Driver's safety, Machine-learning</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Motorway incidents are frequent &amp; varied in nature. Incident management on motorways is critical for both driver safety &amp; road network operation. The expected duration of an incident is a key parameter in the decision-making process for control room operators, however, the actual duration for which an incident will impact the network is never known with true certainty.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, algorithms, classification, prediction, support vector machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Application of Fuzzy Decision Support System Based on GNN in Anomaly Detection and Incident Response Service of Intelligent Security</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Chen T.; Wu X.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>10.14569/IJACSA.2024.0150912</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>anomaly detection, fuzzy decision support system, GNN, incident response service, intelligent security, Complex relationships, Embedded representation, Graph data, Graph neural networks, Incident response, Robust systems, organization, processes, model, models, machine learning, deep learning, neural network, detection, datasets</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>This paper introduces a fuzzy decision support system (FDSS) based on a graph neural network (GNN) for anomaly detection and intelligent security. The primary aim is to develop a robust system capable of accurately identifying anomalies and providing timely incident response services. GNNs are utilized to capture the complex relationships and features between nodes in graph data, learning the embedded representation of each node through information transfer and aggregation mechanisms, which encapsulate the structural information of the graph.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, anomaly detection, model, models, machine learning, deep learning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Decision Systems in Cybersecurity: A Synergy of AI and ML</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sharma R.; Sherje N.; Godbole A.; Shailesh; Deshmukh V.; Pandit P.V.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>10.1007/978-981-96-0143-1_42</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Cybersecurity, Decision systems, Incident response, Intrusion detection systems, Machine learning, Threat intelligence, Adversarial machine learning, Intrusion detection, Network intrusion, Cyber security, Cyber threats, Decision-making systems, Machine-learning, Making decision, Review papers, impact, management, processes, algorithms, model</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Cyber threats are becoming more frequent and complex, making decision systems crucial to cybersecurity. The review paper uses machine learning to examine decision systems and cybersecurity, highlighting its fundamentals, applications, and challenges. The paper begins with a detailed cybersecurity overview, emphasizing the need for strong decision-making systems to address changing threats.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: algorithms, model, machine learning, detection, intrusion detection, datasets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Monitoring Incident Response Using Real-Time Analytics</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Mohanraj G.; Nadesh R.K.; Jagannathan J.; Adityan S.; Sathiyamoorthi V.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>10.1109/ITIKD63574.2025.11004824</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ARIMA, data analytics, Decision Tree, Facebook Prophet, Incident response, KNN, LSTM, machine learning, Random Forest, SVM, time series forecasting, Cyber attacks, Intelligent systems, Risk perception, Facebook, Machine-learning, Random forests, Prediction models, organizational, management</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>In today's digital landscape, rapid and effective incident response is crucial for maintaining organizational security against sophisticated cyber threats. This project explores the optimization of incident response processes through the implementation of advanced data analytics, machine learning, and time series forecasting algorithms. The system utilizes historical incident data along with advanced algorithms like ARIMA, Support vector machine, LSTM, KNN, Facebook Prophet, Decision Tree, and Random Forest to predict incident volumes, prioritize tickets, and evaluate RFC outcomes.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: algorithms, models, machine learning, prediction, random forest, support vector machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Leveraging OSINT for Advanced Proactive Cybersecurity: Strategies and Solutions</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Avrahami Z.; Zwilling M.; Hajaj C.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>10.1109/ACCESS.2025.3603868</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CTI, cyber threat intelligence, intelligence cycle, Open-source intelligence, OSINT, proactive cybersecurity, Artificial intelligence, Behavioral research, Cybersecurity, Data integration, Data reliability, Decision making, Open systems, Terrorism, Cybe threat intelligence, Cyber security, Cyber threats, Decisions makings, Open source intelligence, Cost effectiveness</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>The growing complexity of the digital environment has increased the need for proactive and intelligence-based approaches to cybersecurity. This study examines the role of open-source intelligence (OSINT) as a strategic tool in proactive cybersecurity operations. Drawing on a wide range of peer-reviewed literature and professional sources, it reviews definitions, operational processes, areas of application, benefits, and challenges associated with OSINT.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: business, organizational, decision making, incident response, processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Novel Method of Improving Cybersecurity Posture with Real-Time Analytics in Security Operations Centers</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Boljam A.M.; Saini V.; Bojja S.G.R.; Mohammed H.U.H.; Alluri V.R.R.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>10.1109/ICCTDC64446.2025.11157987</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>anomaly detection, automated decision-making, cybersecurity automation, Cybersecurity posture, data streams, data-driven security, false positive reduction, incident response, machine learning, operational efficiency, predictive analytics, real-time analytics, security infrastructure, Security Operations Centers (SOCs), threat detection, threat intelligence, Artificial intelligence, Automation, Behavioral research, Cybersecurity</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Cyberattacks become more widespread and sophisticated, cybersecurity is now at the forefront of concern for many organizations. Security Operations Centers (SOCs) are essential for their ability to monitor, detect, and respond to these threats. The problem is traditional methods are ineffective within SOCs due to large data volumes, complexities of the threat landscape, and slow time-to-response.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: models, machine learning, artificial intelligence, detection, threat detection, anomaly detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Digital Twins for Incident Detection and Response</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Kampourakis K.E.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-92471-2_16</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>critical infrastructure, Digital twin, incident detection, incident response, Critical infrastructures, Decision making, 'current, Cyber security, Cyber threats, Detection mechanism, Dynamic decision making, Infrastructure sector, Interconnectivity, Real time monitoring, Cyber attacks, machine learning, detection</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Digital Twin (DT) technology is revolutionizing critical infrastructure (CI) sectors by enabling real-time monitoring, predictive analytics, and dynamic decision-making. However, this increased interconnectivity and complexity also introduces significant cybersecurity challenges. The current work investigates the potential of DTs to enhance cybersecurity incident detection and response mechanisms for CI systems.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, machine learning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Crisis Management Models for Cyberattacks Leveraging ML-Driven Detection Mechanisms</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rani P.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>10.1109/WorldSUAS66815.2025.11199118</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Anomaly Detection, Crisis Management, Cyberattacks, Cybersecurity, Machine Learning, Threat Classification, Decision making, Information management, Learning systems, Network layers, Public works, Random forests, Zero-day attack, Cyber security, Cyber threats, Detection mechanism, Machine-learning, Management frameworks, Management Model, Threat classifications</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Cyber threats to critical infrastructure are getting ever more serious, which calls for efficient crisis management frameworks that would allow detecting, responding, and recovering swiftly. The research specifies an integrated model of responding to cyber crises in terms of the application of machine learning driven anomaly detection mechanisms. This framework utilizes anomaly detection, threat type identification, and risk ranking, in order to enhance the process of decision-making and make the automatic incident response possible.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: models, detection, model, machine learning, classification, anomaly detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>On the Use of Artificial Intelligence in Cybersecurity Incident Investigations</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Gorda M.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>10.1109/SmartIndustryCon65166.2025.10986177</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>artificial intelligence, cybersecurity, digital forensics, incident investigation, Artificial life, Cyber attacks, Forensic engineering, Intelligent computing, Intelligent systems, Anomaly detection, Artificial intelligence techniques, Behaviour models, Cyber security, Cyber threats, Cyber-attacks, Decision support algorithms, Digital evidence, Information security incidents, Computer forensics, incident response</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>The increasing number of cyber threats significantly complicates the investigation of information security incidents. Traditional digital forensic methods face challenges due to the growing volume of data and the increasing sophistication of cyberattacks. This paper presents a decision-support algorithm designed to assist specialists in conducting efficient and accurate investigations using artificial intelligence techniques.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, algorithm, algorithms, models, detection, anomaly detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>AI-Enhanced Automated Incident Response in SIEM with Explainability for SOC Analysts</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Charla R.R.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>10.1109/iSAI-NLP66160.2025.11320514</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Automation, Compliance, Cybersecurity, Explainable AI, Incident Response, Scalability, SIEM, SOC, Threat Detection, Artificial intelligence, Information management, Security systems, Centralised, Cyber security, Explainable artificial intelligence, Incident detection, Security information and event management systems, Security information and event managements, Security operation center, enterprise</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Security Information and Event Management (SIEM) systems have become the cornerstone of enterprise cybersecurity operations, providing centralized monitoring and incident detection. However, the increasing complexity of threats has outpaced manual Security Operations Center (SOC) workflows, leading to alert fatigue and slow response times. This paper explores the integration of artificial intelligence (AI) into automated incident response pipelines within SIEM systems, with a particular focus on explainability for SOC analysts.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: incident response, soc, enterprise, management, security operations center.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>From Alert Fatigue to Augmented Defense: A Case for AI Copilots in Cybersecurity Operation Centers</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Akre V.; Kobbaey T.; Lazarov G.; Abdulsalam K.; Al-Sit W.; Diab J.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>10.1109/ITT69610.2025.11352895</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>AI Copilot, Alert Fatigue, Cybersecurity Operations Centers (CSOCs), Explainable AI (XAI), Human–AI Collaboration, Incident Response, Security Operation Centers (SOCs), SOAR, Threat Detection, Artificial intelligence, Cybersecurity, Fatigue of materials, Network security, Security systems, Cyber security, Cybersecurity operation center, Operation center, Security operation center, Security orchestration, automation</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Cybersecurity Operations Centers (CSOCs) act as one of the foremost tools for cyber defenses. However, security analysts often face overwhelming stress owing to excessive volumes of alerts, frequent false positives flagged by most existing tools, and growing mental strain. Such challenges could negatively impact threat detections by delays that cause slower incident response; thus, undermining overall security effectiveness.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: models, machine learning, artificial intelligence, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Evolution and Challenges of Security Operations Centers in the Digital Age</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Morocho-Sailema V.E.; Velasteguí H.J.; Jara-Elizalde Á.G.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-032-10310-9_3</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Cybersecurity, Digital defense, Incident response, Operational maturity, Threat detection, Artificial intelligence, Behavioral research, Digital twin, Economics, Human computer interaction, Information management, Investments, Network security, Security systems, Cyber security, Digital age, Digital environment, Exposed to, Maturity model, Security operation center</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>In an increasingly dynamic digital environment exposed to sophisticated threats, organizations face the challenge of comprehensively protecting their information assets. One key strategy involves the deployment of Security Operations Centers (SOC), which integrates people, processes, and technologies to detect, analyze, and respond to security incidents in real time. This article offers a critical narrative review of academic and technical publications from 2016 to 2025 on operational maturityOperational maturity models and conceptual frameworks that guide proactive threat detectionThreat detection.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: organizational, management, governance, incident response, soc, processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Using the MITRE ATT&amp;CK Framework in SOC Ativities and Analyzing Cyber Attack</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Uralov J.; Abdullaeva S.; Risolat I.; Yusupova M.; Kutliev S.; Qazaqov M.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>10.1109/EDM65517.2025.11096745</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Adversarial Tactics, Cyber Defense, Cyber Risk Mitigation, Cyber Threat Detection, Cybersecurity, Incident Response, MITRE ATT&amp;CK, Security Operations Center (SOC), Tactics Techniques and Procedures (TTPs), Threat Intelligence, Artificial intelligence, Computer crime, Crime, System-on-chip, Adversarial tactic, Cybe risk mitigation, Cybe threat detection, Cyber security, Cyber threats, Cyber-defense</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>The growing complexity of cyber threats demands advanced strategies to strengthen cybersecurity operations. The MITRE ATT&amp;CK Framework offers a systematic method for identifying, analyzing, and mitigating cyber-attacks within Security Operations Centers (SOCs). This paper examines how integrating the MITRE ATT&amp;CK Framework enhances SOC capabilities in threat detection, incident response, and overall cyber resilience.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: framework, artificial intelligence, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Threat Vision: A Next-Generation SOC-Inspired Platform Leveraging Hybrid Malware Analysis and Real-Time Social Media Threat Intelligence for Enhanced Cybersecurity</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Harshith C.M.; Manohar N.; Venugopal S.; Kudroli A.; Jha N.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>10.1109/ICOIICS67115.2025.11390653</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Cybersecurity Automation, Deep Learning, Human-AI Collaboration, Hybrid Analysis, Machine Learning, Malware Detection, Network Security, Security Operations Centre (SOC), Sentiment Analysis, Social Media Threat Intelligence, Cybersecurity, Learning systems, Malware, Security systems, Cyber security, Machine-learning, Networks security, Security operation center, Social media, Social medium threat intelligence</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Cybersecurity threats, like malware and network breaches, are getting harder to manage. Therefore, need security that is both stronger and easier for every person to use. Typical Security Operation Centers work well, but they're expensive, which means only big companies can use them.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: malware, machine learning, deep learning, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Air Traffic Control System Cyber Security Using Humans and Machine Learning</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Atkins G.; Sampigethaya K.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>10.1109/ICNS58246.2023.10124305</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ADS-B, air traffic control, crew, cyber security, machine learning, Air navigation, Alarm systems, Control towers, Decision making, Air traffic control systems, Air traffic controller, Automatic dependent surveillance broadcasts, Cyber-attacks, Education and training, Human learning, Machine-learning, Performance, Cybersecurity, management, incident response</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Aviation performance depends on education and training of pilots and air traffic controllers (ATCOs) on technical, procedural, crisis management, decision making, leadership and communication skills. Recent incidents and studies, however, show crew members may be caught unaware and errors in human judgement can still occur in air traffic control (ATC) systems even more so in the presence of cyberattacks. This paper focuses on raising situation awareness and decision making of ATCOs with cyberattacks impacting operations in next-generation ATC systems.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, decision making, incident response, cybersecurity management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Dynamic characterisation of cyberattacks based on the MITRE ATT&amp;CK framework applied to the optimisation of a mitigation selection process</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sánchez-Zas C.; Larriva-Novo X.; Villagrá V.A.; Solera-Cotanilla S.; Sanz-Rodrigo M.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>10.1016/j.future.2025.108272</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Countermeasure selection, Cybersecurity, Machine learning, MITRE ATT&amp;CK, Support to decision making, TTPs, Artificial intelligence, Behavioral research, Decision making, Malware, Risk analysis, Risk management, Zero-day attack, Cyber security, Cyber-attacks, Decisions makings, Dynamic characterization, Machine-learning, Optimisations, TTP</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>The main cybersecurity challenges identified nowadays arise around the need to know information about cyberattacks, in order to characterise them and applying the most appropriate mitigation techniques according to their behaviour. Current advances in cybersecurity focus on the detection of zero-day attacks, adaptability to attackers’ behaviour, and automated incident response. However, this evolution should not oppose the proven need for defence-in-depth policy, collaboration, and information sharing that can help other organisations prepare for new cyberattacks.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: framework, algorithm, model, machine learning, artificial intelligence, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Explainable AI for Malware Classification: Bridging the Gap Between Accuracy and Transparency</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Muça F.; Ahmad W.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Albania</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-032-07373-0_6</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Cybersecurity, Explainable AI, Gradient Boosting, LIME, Machine Learning, Malware Classification, Model Interpretability, Random Forest, SHAP, Transparency, Adaptive boosting, Balancing, Barium compounds, Decision support systems, Decision trees, Learning systems, Logistic regression, Malware, Network security, Random forests</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (AI) has significantly improved malware classification by enhancing detection accuracy and efficiency. However, the opaque nature of many AI models presents a major challenge in cybersecurity, as security analysts often struggle to trust or fully understand the decisions made by these systems. This lack of transparency impedes adoption in real-world applications where explainability is crucial for risk assessment, incident response, and compliance.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: classification, malware, model, models, machine learning, artificial intelligence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Combat Security Alert Fatigue with AI-Assisted Techniques</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ban T.; Samuel N.; Takahashi T.; Inoue D.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F41" t="n">
+        <v>50</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>10.1145/3474718.3474723</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>alert fatigue, Intrusion detection systems, security alert analysis, Intrusion detection, Fatigue problems, Management IS, Security alert analyse, Security alerts, Security experts, Security incident, Security information and event managements, Security products, Network security, enterprise, management, incident response, algorithms, artificial intelligence, dataset</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>The main challenge for security information and event management (SIEM) is to find critical security incidents among a huge number of false alerts generated from separate security products. To address the alert fatigue problem that is common for security experts operating the SIEM, we propose a new alert screening scheme that leverages artificial intelligence (AI)-assisted tools to distinguish actual threats from false alarms without investigating every alert. The proposed scheme incorporates carefully chosen learning algorithms and newly designed visualization tools to facilitate speedy alert analysis and incident response.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: algorithms, artificial intelligence, detection, intrusion detection, dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Improved Detection and Response via Optimized Alerts: Usability Study</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>McRee G.R.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>10.3390/jcp2020020</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>data science, detection, security alert, text alert output, user acceptance, user experience, visual alert output, visualization, impact, incident response, soc, model, models, machine learning</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Security analysts working in the modern threat landscape face excessive events and alerts, a high volume of false-positive alerts, significant time constraints, innovative adversaries, and a staggering volume of unstructured data. Organizations thus risk data breach, loss of valuable human resources, reputational damage, and impact to revenue when excessive security alert volume and a lack of fidelity degrade detection services. This study examined tactics to reduce security data fatigue, increase detection accuracy, and enhance security analysts’ experience using security alert output generated via data science and machine learning models.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, model, models, machine learning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Predicting Crash-Related Incident Clearance Time on Louisiana’s Rural Interstate Using Ensemble Tree-Based Learning Methods</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Khan W.A.; Moomen M.; Rahman M.A.; Terkper K.A.; Codjoe J.; Gopu V.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>10.3390/app142310964</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>incident clearance time, machine learning, rural interstate, SHAP analysis, Adaptive boosting, Highway accidents, Highway administration, Truck transportation, Gradient boosting, Incident duration, Light gradients, Louisiana, Machine-learning, Rural interstates, Shapley, Shapley additive explanation analyze, Traffic crashes, Traffic congestion, incident response, models</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Traffic crashes contribute significantly to non-recurrent congestion, thereby increasing delays, congestion pollution, and other challenges. It is important to have tools that enable accurate prediction of incident duration to reduce delays. It is also necessary to understand factors that affect the duration of traffic crashes.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: models, machine learning, prediction, model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SMS-I: Intelligent Security for Cyber–Physical Systems</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Maia E.; Sousa N.; Oliveira N.; Wannous S.; Sousa O.; Praça I.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F44" t="n">
+        <v>6</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>10.3390/info13090403</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>cyber–physical systems, cyber–physical systems forensics, digital forensics, machine learning, rule mining, security incident response, Computer crime, Computer forensics, Critical infrastructures, Cybersecurity, Decision making, E-learning, Public works, Cybe-physical systems, Cybe–physical system forensic, Incident response, Machine-learning, Security incident, society, impact</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Critical infrastructures are an attractive target for attackers, mainly due to the catastrophic impact of these attacks on society. In addition, the cyber–physical nature of these infrastructures makes them more vulnerable to cyber–physical threats and makes the detection, investigation, and remediation of security attacks more difficult. Therefore, improving cyber–physical correlations, forensics investigations, and Incident response tasks is of paramount importance.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, artificial intelligence, classification, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ARCS: Adaptive Reinforcement Learning Framework for Automated Cybersecurity Incident Response Strategy Optimization</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ren S.; Jin J.; Niu G.; Liu Y.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F45" t="n">
+        <v>20</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>10.3390/app15020951</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>automated incident response, cybersecurity optimization, reinforcement learning, security event analytics, Adversarial machine learning, Adaptive reinforcement, Cyber security, Incident response, Optimisations, Reinforcement learnings, Response strategies, Security event analytic, Security events, Cyber attacks, process, dataset, framework</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>The increasing sophistication and frequency of cyber attacks necessitate automated and intelligent response mechanisms that can adapt to evolving threats. This paper presents ARCS (Adaptive Reinforcement learning for Cybersecurity Strategy), a novel framework that leverages deep reinforcement learning to optimize automated incident response strategies in cybersecurity systems. Our approach uniquely combines state representation learning of security events with a hierarchical decision-making process to map attack patterns to optimal defense measures.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: framework, machine learning, dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ensemble-Based Intrusion Detection Enhanced with LLM-Driven Incident Response Automation</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Thumala S.R.; Mane V.; Inamdar C.; Pethkar P.; Poke A.; Patil R.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>10.1109/I4Tech64670.2025.11277913</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>cybersecurity automation, incident response, Intrusion detection, LangChain, random forest, REST API, XGBoost, Artificial intelligence, Automation, Computer crime, Cybersecurity, Decision making, Learning systems, Network security, Cyber security, Intrusion-Detection, Random forests, Response systems, Threat detection, model</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Traditional incident response systems lack adaptability and autonomous decision-making, limiting their effectiveness against sophisticated cyber threats. A modular AI framework is implemented to address this challenge by integrating ensemble-based binary intrusion detection and multiclass attack classification with real-time automation. Using the UNSW-NB15 dataset, Random Forest, XGBoost, and LightGBM models are trained for binary threat detection, followed by classification into nine attack categories.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, intrusion detection, model, models, artificial intelligence, classification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>A Practical Approach to Defining a Framework for Developing an Agentic AIOps System</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Zota R.D.; Bărbulescu C.; Constantinescu R.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F47" t="n">
+        <v>10</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>10.3390/electronics14091775</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Agentic AIOps, AI-driven agents, AIOps, ITIL, MLOps, PRM-IT, Empowerment of personnel, Human resource management, Information management, Predictive maintenance, Agentic artificial intelligence for IT operation, AI-driven agent, AIOp, Information technology infrastructure, Information technology infrastructure library, MLOp, Operation system, Process reference model for IT, Process reference models, Work-flows</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>The increasing complexity of IT operations necessitates advanced automation to ensure system availability, resilience, continuity, performance, security, and maintainability. Traditional IT management frameworks, such as the Information Technology Infrastructure Library (ITIL), have standardized service management processes, while models like IBM’s Process Reference Model for IT (PRM-IT) have facilitated automation through structured workflows. However, critical tasks, such as incident resolution and problem management, still require significant human intervention.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: enterprise, management, decision making, incident response, process, processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Human Factors in AI-Driven Cybersecurity: Cognitive Biases and Trust Issues</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Hagen R.A.; Øverlier L.; Helkala K.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>10.1145/3759260</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>AI (XAI), alert fatigue, automation bias, bias mitigation, cognitive biases, confirmation bias, dual-process theory, false positives, human–AI collaboration, incident response workflows, model interpretability, practitioner perspectives, security operations centers (SOC), trust calibration, Artificial intelligence, Automation, Cybersecurity, Human computer interaction, Human engineering, Cognitive bias</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>The integration of AI in cybersecurity promises enhanced threat detection and response capabilities, yet its adoption is hindered by human factors, particularly cognitive biases and trust issues. This study investigates how cognitive biases, such as automation bias (47%) and confirmation bias (37%), influence security analysts’ trust in AI-driven tools, drawing on Kahneman’s dual-process theory. Through qualitative interviews with 19 cybersecurity professionals and a comparative analysis of AI solutions from Microsoft, CrowdStrike, Darktrace, and IBM, we identify key barriers to adoption, including explainability gaps and high false positive rates.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, models, artificial intelligence, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>AutoSOC Cyber Analyst (ASOC-CA): Using AI to Automate SOC Tier 1 &amp; 2 Activities</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Mihalopoulos I.; Ngo-Antonio J.-R.; Pugh M.; Neal D.; Cao Y.; Watkins L.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>10.1109/CCWC67433.2026.11393893</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Advanced Persistent Threat (APT) Detection, Artificial Intelligence (AI), Machine Learning (ML), MITRE ATT&amp;CK, Security Information and Event Management (SIEM), Cybersecurity, Learning systems, Machine learning, Network security, Public works, Advanced persistent threat detection, Artificial intelligence, Artificial intelligence systems, Incident response, Machine-learning, Security information and event management, Security information and event managements, Threat detection, Information management, organizational</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Hackers are now beginning to use artificial intelligence (AI) to expand the capabilities and sophistication of their attacks, creating challenges for network owners. As state-sponsored adversaries and advanced persistent threats (APTs) utilize AI to their advantage, network owners must evolve concurrently to address the emergent threat landscape shaped by advanced AI systems. Thus, in this paper, we propose an end-to-end Machine Learning Framework to automate and strengthen cybersecurity operations.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, machine learning, artificial intelligence, detection, threat detection, framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>From Vulnerability to Defense: The Role of Large Language Models in Enhancing Cybersecurity</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Kasri W.; Himeur Y.; Alkhazaleh H.A.; Tarapiah S.; Atalla S.; Mansoor W.; Al-Ahmad H.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Palestine</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F50" t="n">
+        <v>67</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>10.3390/computation13020030</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>cybersecurity, deep learning, intrusion detection, large language models, malware detection, phishing attack detection, organizational, management, incident management, incident response, detection, threat detection, phishing, malware, datasets, bert</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>The escalating complexity of cyber threats, coupled with the rapid evolution of digital landscapes, poses significant challenges to traditional cybersecurity mechanisms. This review explores the transformative role of LLMs in addressing critical challenges in cybersecurity. With the rapid evolution of digital landscapes and the increasing sophistication of cyber threats, traditional security mechanisms often fall short in detecting, mitigating, and responding to complex risks.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: models, deep learning, detection, threat detection, intrusion detection, phishing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Toward Robust Security Orchestration and Automated Response in Security Operations Centers with a Hyper-Automation Approach Using Agentic Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ismail; Kurnia R.; Brata Z.A.; Nelistiani G.A.; Heo S.; Kim H.; Kim H.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F51" t="n">
+        <v>22</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>10.3390/info16050365</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>agentic-LLM, hyper-automation, incident-response, security operation center, SOAR, Intelligent systems, Agentic-large language model, Automated response, Cyber security, Incident response, Language model, Robust security, Security orchestration, automation, and response, Threats mitigations, Cyber attacks, soc, models, detection</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>The evolving landscape of cybersecurity threats demands the modernization of Security Operations Centers (SOCs) to enhance threat detection, response, and mitigation. Security Orchestration, Automation, and Response (SOAR) platforms play a crucial role in addressing operational inefficiencies; however, traditional no-code SOAR solutions face significant limitations, including restricted flexibility, scalability challenges, inadequate support for advanced logic, and difficulties in managing large playbooks. These constraints hinder effective automation, reduce adaptability, and underutilize analysts’ technical expertise, underscoring the need for more sophisticated solutions.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, model, models, detection, threat detection, framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Empowering Security Operation Center with Artificial Intelligence and Machine Learning - A Systematic Literature Review</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Khayat M.; Barka E.; Adel Serhani M.; Sallabi F.; Shuaib K.; Khater H.M.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F52" t="n">
+        <v>33</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>10.1109/ACCESS.2025.3532951</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Artificial intelligence, cyber threats, cybersecurity, healthcare security, incident response, machine learning, neural networks, next-generation SOC, security operation center, threat detection, Cyber security, Machine-learning, Neural-networks, Next-generation security operation center, Adversarial machine learning, sector, organizational, soc, model, deep learning</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Organizational cybersecurity relies heavily on security operation centers (SOCs) to protect businesses and institutions from emerging cyber threats. In recent years, the complexity and sophistication of cyber threats have increased, pushing SOCs to their limits. As a result, SOCs struggle to address the evolving threat landscape due to their reliance on isolation technologies and reactive strategies.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, artificial intelligence, model, deep learning, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Finding Harmony in the Noise: Blending Security Alerts for Attack Detection</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Roelofs T.-M.; Barbaro E.; Pekarskikh S.; Orzechowska K.; Kwapień M.; Tyrlik J.; Smadu D.; Van Eeten M.; Zhauniarovich Y.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F53" t="n">
+        <v>4</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>10.1145/3605098.3635981</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>intrusion detection, machine learning, security alert integration, Blending, Integration, Personnel training, Security systems, Attack detection, End to end, Global organization, Intrusion-Detection, Machine-learning, Medium sized organizations, Securities analysts, Security alerts, Security detection systems, global, organization, incident response, soc</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Large- and medium-sized organizations employ various security systems to protect their assets. These systems, often developed by different vendors, focus on different threats and usually work independently. They generate separate and voluminous alerts that have to be monitored and analyzed by often overburdened security analysts.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, model, machine learning, intrusion detection, dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Explainable Intelligence and LLM-Based Secure Framework for Industrial Internet of Things</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Mehta D.; Patel C.; Shah M.; Shah A.; Gupta R.; Tanwar S.; Alabdulatif A.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>10.1109/MNET.2025.3637291</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Artificial intelligence, Electronic data interchange, Internet of things, Learning systems, Network security, Decision-making process, Human intervention, Language model, Machine-learning, Manual labors, Model-based OPC, Real-time data exchange, Security frameworks, Security vulnerabilities, Threat identification, Complex networks, Decision making, incident response, processes, model</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>The Industrial Internet of Things (IIoT) is transforming the industrial landscape by enabling real-time data exchange and automation, reducing the need for human intervention and enhancing accuracy beyond manual labor. However, this interconnectedness creates a vast assortment of security vulnerabilities, ranging from device-level attacks to a complex nexus of network breaches. This paper introduces a comprehensive security framework utilizing Machine Learning (ML) for smart threat identification and Explainable AI (XAI) to improve transparency and build trust in decision-making processes.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: framework, model, models, machine learning, artificial intelligence, prediction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Machine Learning-Based Alert Correlation for Enhanced Cybersecurity: A Multi-Classification Approach</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Diakhame M.L.; Diallo C.; Mejri M.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>10.1109/CSNet67572.2025.11288163</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Alert Correlation, Classification, Cybersecurity, Incident Response, Machine Learning, SIEM, Convolutional neural networks, Learning algorithms, Learning systems, Logistic regression, Network security, Pattern recognition, Security systems, Support vector regression, Classification approach, Cyber security, Machine-learning, Multi-classification, Performance, Random forests</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Modern Security Operations Centers (SOCs) struggle with an overwhelming influx of security alerts from diverse sources, leading to alert fatigue and delayed incident response times. Conventional Security Information and Event Management (SIEM) systems typically process alerts in isolation, missing complex attack patterns that unfold across multiple detection points. This research introduces a comprehensive machine learning framework for intelligent alert correlation using three classification approaches: binary correlation detection, correlation type classification, and incident classification.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, classification, algorithms, models, detection, dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Enhancing Urban Resilience in Smart Cities Through Edge AI, Point of Interest Analysis, and Multi-Criteria Decision-Making</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ke C.-K.; Wu M.-Y.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>10.1109/IS3C65361.2025.11130986</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>edge artificial intelligence, multi-criteria decision analysis, point of interest, smart city, urban resilience, Analytic hierarchy process, Artificial intelligence, Decision support systems, Disaster prevention, Distributed computer systems, Emergency services, Information services, Information use, Network security, Quality of service, Multi criteria decision-making, Multicriteria decision-making, Multicriterion decision makings, Real- time, Service oriented computing</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>In today's urban environment, where extreme weather, epidemic outbreaks, and social security threats are frequent, the construction of smart cities must focus not only on efficiency and convenience but also on defensive resilience to handle crises effectively. This study proposes an innovative information service architecture that integrates edge artificial intelligence (Edge AI), point of interest (POI) analysis, and multi-criteria decision analysis (MCDA) to enhance early warning and solution recommendation processes for smart city incidents. The proposed system will identify critical POI maps in the city through POI risk analysis.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: decision making, management, incident response, process, processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Strategic cyber threat intelligence: Building the situational picture with emerging technologies</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Voutilainen J.; Kari M.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F57" t="n">
+        <v>4</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>10.34190/EWS.20.030</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Machine Learning, Strategic Cyber Threat Intelligence, Crime, Cybersecurity, Decision making, Large dataset, Malware, Network security, Cyber threats, Cyber-attacks, Cyberspaces, Decisions makings, Emerging technologies, Incident response, Large organizations, Machine-learning, Strategic cybe threat intelligence, Tacticals, impact</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>In 2019, e-criminals adopted new tactics to demand enormous ransoms from large organizations by using ransomware, a phenomenon known as “big game hunting.” Big game hunting is an excellent example of a sophisticated and coordinated modern cyber-attack that has a significant impact on the target. Cyber threat intelligence (CTI) increases the possibilities to detect and prevent cyber-attacks and gives defenders more time to act. CTI is a combination of incident response and traditional intelligence.</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, artificial intelligence, detection, malware, ransomware, dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Optimization and Implementation of Network Security Incident Handling Process Based on Secure Arrangement</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ni L.; Qian Y.; Zhang S.; Tong S.; Bao C.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>10.1109/ICSECE61636.2024.10729589</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Automation, Configuration management, Network security incident, Security arrangement, Decision making, Network security, Resource allocation, Risk management, Handling process, In networks, Incident response, Innovative solutions, Integrating security, Network security incidents, Optimisations, Process-based, Security arrangements, Network intrusion, management, incident management</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>This article addresses the issues of low efficiency and fragmented processes in network security incident response, proposing an innovative solution that utilizes security orchestration technology to optimize the handling process and achieve automation. Through an analysis of existing processes, the limitations of traditional methods are clearly defined. The research elaborates on the principles of security orchestration technology, including its advantages in integrating security tools and designing automated processes.</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: process, management, decision making, incident management, incident response, processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>A Context-Aware, AI-Driven Load Balancing Framework for Incident Escalation in SOCs</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Abuaziz A.; Celiktas B.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>10.1109/ISAS66241.2025.11101733</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>AI-driven incident escalation, context-aware assignment, escalation, load balancing, security operation center, Artificial intelligence, Computational methods, Programmable logic controllers, System-on-chip, Context-Aware, Cyber-attacks, Incident escalations, Incident Management, Load-Balancing, Rule based, Resource allocation, organizational, management, incident response, soc</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>SOCs face growing challenges in incident management due to increasing alert volumes and the complexity of cyberattacks. Traditional rule-based escalation models often fail to account for the workload of the analyst, the severity of the incident, and the organizational context. This paper proposes a context-aware, AI-driven load balancing framework for intelligent analyst assignment and incident escalation.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: organizational, management, incident management, incident response, soc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Cyber-DRIVE: Dynamic Risk Versatile Engine for Cyber Security Risk Analysis, Situational Awareness and Incident Response</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Solari S.; Pedrotti U.; Castelli E.; Ceccoli G.; Oneto A.; Russo E.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Cyber Threat Intelligence, Cybersecurity Ontology, Dynamic Risk Analysis, Kill Chain Generation, Markov Decision Process, Security Mechanisms, Situational Awareness, Threat Propagation, Cyber attacks, Intelligent systems, Markov processes, Risk analysis, Cybe threat intelligence, Cyber security, Cyber threats, Dynamic risk analyze, Dynamic risks, Kill chain, Markov Decision Processes, Ontology's</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>In dynamic and regulated critical environments, continuously assessing cyber risks is essential for effective situational awareness and decision-making. While methodologies like Security Risk Analysis (SRA) and Threat Assessment and Remediation Analysis (TARA) provide structured approaches, they often lack dynamic updates, real-time threat modeling, and advanced visualization capabilities. This paper introduces Cyber-DRIVE, a novel framework for dynamic risk analysis, incident response, and situational awareness.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: incident response, business, soc, process, processes, decision making.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>European framework and proofs-of-concept for the intelliGent aUtomAtion of cybeR Defence Incident mAnagemeNt</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Garcia Cid M.I.; Gil Perez M.; Jorquera Valero J.M.; Lopez Martinez A.; Maestre Vidal J.; Martinez Perez G.; Garcia L.M.; Plaza F.M.; Nespoli P.; Galindo J.P.; Ramon Y Cajal Ramo P.J.; Rodriguez Lopez F.A.; Sanchez Sanchez P.M.; Sotelo Monge M.A.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>10.23919/JNIC58574.2023.10205559</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Cyber defence, Incident management, Automation, Cybersecurity, Decision making, Automatic Detection, Automatic response, Cyber-defense, Defense response, Incident response, Intelligent automation, Proof of concept, Security challenges, Semi-automatics, detection, framework</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence and Automation are revolutionizing cyber defence and incident response by addressing traditional inefficiencies and enabling faster and easier incident resolutions. However, challenges arise in cyber response. The European framework and proofs-of-concept for the EUGUARDIAN project aims to develop a reliable AI-based solution focusing on semi-automatic or automatic detection, mitigation, and response to security challenges, supporting analysts and decision-makers, enhancing cyber situational awareness and military infrastructure resilience.</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, incident management, decision making, incident response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Dynamic Playbooks Quality Metrics</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Zolotarev V.; Oleynikova A.; Zakhir B.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>10.1109/SmartIndustryCon61328.2024.10516048</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>continuous detection and response, decision support system, dynamic playbook, incident, information security incidents, investigation, quality metrics, Artificial intelligence, Information management, Security of data, Continuous detections, Control objects, Dynamic controls, Incident response, Quality metrices, Decision support systems, organizational, management, processes, algorithms</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>The text discusses the challenges and solutions related to dynamic control objects in the task of information security monitoring. New approaches for data collection and analysis, as well as the development of methods for creating dynamic incident response scenarios (playbooks), are highlighted. The focus is on resolving these challenges through the creation of applicable algorithms, models, methods, and security management approaches, including at the level of organizational processes, data handling, and formation of the organization's information security architecture.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: organizational, management, incident response, processes, organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>A collaborative cybersecurity framework for higher education</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Otoom A.A.; Atoum I.; Al-Harahsheh H.; Aljawarneh M.; Al Refai M.N.; Baklizi M.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F63" t="n">
+        <v>6</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>10.1108/ICS-02-2024-0048</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Collaboration, Incident Response:, Cybersecurity, Design Science Research (DSR), Higher education, Organizational Learning The-ory (OLT), Decision making, Electronic design automation, Emotional intelligence, Energy policy, Intelligent systems, International cooperation, Knowledge acquisition, Problem solving, Risk management, Structural analysis, Structural dynamics, Systems analysis, Cyber security, Design science research</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Purpose: The purpose of this paper is to present the educational computer emergency response team (EduCERT) framework, an integrated response mechanism to bolster national cybersecurity through collaborative efforts in the higher education sector. The EduCERT framework addresses this gap by enhancing cyber security and mitigating cybercrime through collaborative incident management, knowledge sharing and university awareness campaigns. Design/methodology/approach: The authors propose an EduCERT framework following the design science methodology.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Clasificado como Macro por coincidencias en metadatos: countries, national, international, global, sector, policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Enhancing Traffic Incident Management and Regulatory Compliance Using IoT and Itms: A Mumbai Traffic Police Case Study</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Salunke S.J.; Bang S.S.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F64" t="n">
+        <v>5</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>10.1109/TQCEBT59414.2024.10545276</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, City Surveillance System, Computational Intelligenc, Intelligent Transportation Systems, Internet of Things, Mumbai Traffic Management, Advanced traffic management systems, Air traffic control, Decision making, Emergency traffic control, Energy security, Financial markets, Highway administration, Highway traffic control, Information systems, Motor transportation, Nanotechnology, Urban transportation, Incident Management, Incident reports</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>In the rapidly urbanizing landscape of Mumbai, a megacity confronted with significant traffic management and law enforcement challenges, the deployment of an advanced city surveillance system represents a transformative approach to urban governance. This paper examines the integration of over 11,000 CCTV cameras into the Mumbai Traffic Police's operational framework, covering an area of 438 square kilometers encompassing 41 traffic divisions and 94 police stations. Since its inception in 2016, the system has been pivotal in enhancing safety, order, and mobility within the city, especially amid obstacles such as ongoing infrastructure projects, traffic congestion, accidents, and natural...</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, incident management, governance, decision making, incident response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Coordinating Incident Response and Risk Management for Enhanced Cybersecurity: A Comprehensive Analysis</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Loganathan S.; Jayaprakash M.; Gunasekaran K.; Shanmugam R.; Vinoth D.; Agoramoorthy M.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>10.1109/ICCDS64403.2025.11209412</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>AI in Cybersecurity, Automated Risk Assessment, Cybersecurity, Incident Response, Real-Time Monitoring, Risk Management, Threat Detection, Artificial intelligence, Decision making, Human resource management, Network security, Real time systems, Risk analysis, Risk assessment, Cyber security, Incident Response Management, Real time monitoring, Risks assessments, Risks management, management</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>The increasing complexity and frequency of cyber threats have made coordinated incident response and risk management essential components of robust cybersecurity frameworks. This research explores the integration of incident response protocols with risk management strategies to enhance the overall cybersecurity posture of organizations. Through a combination of qualitative and quantitative methods, including case studies, interviews with cybersecurity professionals, and analysis of security incident reports, this study investigates how effective collaboration between these two domains can mitigate the impacts of cyber incidents and improve recovery times.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, incident response, risk management, decision making, process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Incident Response in Smart Agriculture: An MQTT Case Study</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Rudrakar S.; Rughani P.H.; Sadineni L.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>10.1109/ICCCNT61001.2024.10723835</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Agricultural Internet of Things (Ag-IoT), Incident Response Model, Internet of Things, IoT Security, MQTT Protocol, Smart Agriculture, Quality of service, Agricultural internet of thing, Agriculture systems, Case-studies, Incident response, Internet of thing security, Message queuing telemetry transport protocol, Response model, Smart agricultures, Transport protocols, impact, management, decision making, algorithms</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>The integration of Internet of Things (IoT) technology into agriculture has significantly enhanced farm management and productivity. The Message Queuing Telemetry Transport (MQTT) protocol, pivotal in this transformation, facilitates communication among IoT devices and decision making systems. Being a cost-effective and time-effective system, Ag-IoT is prone to attacks due to its inherent vulnerabilities and weak security policies.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: algorithms, model, machine learning, datasets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>A Deep Learning-Based Dual-Model Framework for Real-Time Malware and Network Anomaly Detection with MITRE ATT&amp;CK Integration</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Migara H.M.S.; Sandakelum M.D.B.; Maduranga D.B.W.N.; Kumara D.D.K.C.; Fernando H.; Abeywardena K.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>10.14569/IJACSA.2025.0160728</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Cybersecurity, deep learning, feedforward neu-ral network, generative adver-sarial networks, malware detection, MITRE ATT&amp;CK, Anomaly detection, Computer viruses, Intrusion detection, Learning systems, Network security, Neural networks, Open systems, Cyber security, Feed forward, Generative adver-sarial network, Network anomaly detection, Real- time, Threat detection, organization</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>The contemporary world of high connectivity in the digital realm has presented cybersecurity with more advanced threats, such as advanced malware and network attacks, which in most cases will not be detected using traditional detection tools. Static cybersecurity tools, which are traditional, often fail to deal with dynamic and hitherto unseen attacks, including signature-based antivirus systems and rule-based intrusion detection. To ad-dress this issue, we would suggest a two-part, AI-powered solution to cybersecurity which would allow real-time threat detection on an endpoint and a network level.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, deep learning, detection, anomaly detection, malware, framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>LINKING EXPLOITS FROM THE DARK WEB TO KNOWN VULNERABILITIES FOR PROACTIVE CYBER THREAT INTELLIGENCE: AN ATTENTION-BASED DEEP STRUCTURED SEMANTIC MODEL1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Samtani S.; Chai Y.; Chen H.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F68" t="n">
+        <v>71</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>10.25300/MISQ/2022/15392</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>cybersecurity, cybersecurity analytics, dark web, design science, hacker forums, online hacker community, Deep learning, Denial-of-service attack, Design, Personal computing, Risk management, SCADA systems, Semantics, Cyber security, Cyber threats, Cybersecurity analytic, Hacker communities, Hacker forum, Semantic modelling, global</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Black hat hackers use malicious exploits to circumvent security controls and take advantage of system vulnerabilities worldwide, costing the global economy over $450 billion annually. While many organizations are increasingly turning to cyber threat intelligence (CTI) to help prioritize their vulnerabilities, extant CTI processes are often criticized as being reactive to known exploits. One promising data source that can help develop proactive CTI is the vast and ever-evolving Dark Web.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, incident response, processes, risk management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Ai/ml in security orchestration, automation and response: Future research directions</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Kinyua J.; Awuah L.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F69" t="n">
+        <v>68</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>10.32604/iasc.2021.016240</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Deep learning, Deep reinforcement learning, Incident response, Machine learning, Security automation, Security management, Security orchestration, Security orchestration and automation, SOAR, industry, soc, processes, detection, threat detection</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Today’s cyber defense capabilities in many organizations consist of a diversity of tools, products, and solutions, which are very challenging for Security Operations Centre (SOC) teams to manage in current advanced and dynamic cyber threat environments. Security researchers and industry practitioners have proposed security orchestration, automation, and response (SOAR) solutions designed to integrate and automate the disparate security tasks, processes, and applications in response to security incidents to empower SOC teams. The next big step for cyber threat detection, mitigation, and prevention efforts is to leverage AI/ML in SOAR solutions.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, deep learning, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Harmonizing paradoxical tensions in SOCs: A Strategic model for integrating AI, automation, and human expertise in cyber defense and incident response</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Saadallah M.; Shahim A.; Khapova S.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>10.24251/hicss.2025.738</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Automation, Cybernetics, Paradoxical Tensions, Security Operations Centers, Artificial life, Cyber attacks, Decision theory, Intelligent computing, Neural networks, Risk perception, Robotics, Cyber-attacks, Cyber-defense, Defense response, Human expertise, Incident response, Paradoxical tension, Private industries, Research advances</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Security operations centers (SOCs) from public and private industries are under pressure to cope with the surge of cyberattacks, making paradoxical tensions in strategic navigation within security operations centers (SOCs) a priority. Our research advances our understanding of ambidexterity in the cybersecurity field and introduces an equilibrium path for adaptability, consistency, expediency, and authority paradoxes through the strategic integration of artificial intelligence (AI), automation, and human expertise. We developed a conceptual model that incorporates insights from the identified paradoxical tensions, cybernetic, organizational paradox, complexity, and decision-making theories,...</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, artificial intelligence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>A Conceptual Framework to Leverage Heuristics for Effective Human-Machine Collaboration in Incident Handling</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Gurabi M.A.; Mansoor M.U.; Matzutt R.; Mandal A.; Decker S.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-87760-5_3</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Human-machine Teaming, Incident Handling, Incident Response, Cybersecurity, Decision making, Learning systems, Machine learning, Man machine systems, Phishing, Conceptual frameworks, Cyber security, High-accuracy, Human-machine, Human-machine collaboration, Levels of automation, Machine-learning, Heuristic methods, process, model, classification</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Managing cybersecurity incidents increasingly depends on advanced levels of automation. However, human involvement remains essential due to the need for high accuracy and the risk of severe damage. Therefore, incident response requires a high degree of human-machine teaming to both simplify the complexity of modern incident handling tasks and ensure a reliable decision-making process.</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: framework, model, machine learning, classification, detection, phishing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>UrbanSense: A Multimodal Spatio-Temporal Neural Framework for Real-Incident Detection and Response Prioritization in Smart Cities</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Preethi M.S.; Sarnika Raj D.; Vedhavathy T.R.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>10.1109/ICMSCI67830.2026.11469758</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Emergency Response, Incident Detection, Public Safety, Real-time Monitoring, Situational Awareness, Smart Cities, Urban Intelligence, Civil defense, Constrained optimization, Decision making, Emergency services, Emergency traffic control, Highway accidents, Highway traffic control, Intelligent systems, MATLAB, Visual analytics, Incident response, Multi-modal, Prioritization</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>This MobileNet-powered incident detection and prioritization of response to different incidents in a smart city setup through MATLAB and camera images in real-time. The system takes advantage of the low and compressed MobileNet framework to introduce on-the-fly categorization of urban incidents as standard or irregular, such as road accidents, traffic jam, and unauthorized usage. The model supports a high detection accuracy with a low computational complexity by using optimized depthwise separable convictions and transfer learning, allowing it to run in resource- and edge-constrained devices.</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, framework, model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Influence diagrams in cyber security: Conceptualization and potential applications</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Chockalingam S.; Maathuis C.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>10.34190/eccws.22.1.1303</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Cyber security, Decision making, Graphical model., Incident response, Influence diagrams, Artificial intelligence, Bayesian networks, Computer crime, Crime, Cybersecurity, Decision support systems, Graphic methods, Network security, Cyber-attacks, Decisions makings, Emerging technologies, Influence diagram, Informed decision, Securities analysts</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Over the last years, cyber-Attacks are increasing in organizations especially due to the use of emerging technologies and transformation in terms of how we work. Informed decision-making in cyber security is critical to prevent, detect, respond, and recover from cyber-Attacks effectively and efficiently. In cyber security, Decision Support System (DSS) plays a crucial role especially in supporting security analysts, managers, and operators in making informed decisions.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, artificial intelligence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Cross-Attention Feature Fusion for Interpretable Zero-Day MalwareDetection</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Aljarrah N.; Shehadeh H.H.; Obeidat R.A.; Tawfik M.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>10.19139/soic-2310-5070-2900</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Cross-Attention, Cybersecurity, Explainable AI, Feature Fusion, Malware Detection, Zero-Day Attacks, international, global, incident response, processes, models, machine learning, deep learning, artificial intelligence, classification, detection, malware, datasets, framework</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>The exponential proliferation of sophisticated zero-day malware variants poses critical challenges to traditional signature-based detection systems, necessitating advanced machine learning approaches that combine high-performance classification with transparent decision-making processes. While existing deep learning models achieve remarkable accuracy in malware detection, their black-box nature severely limits adoption in critical cybersecurity applications where interpretability is paramount for threat analysis and incident response. This work presents a novel cross-attention feature fusion architecture integrated with comprehensive explainable artificial intelligence (XAI) techniques for...</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: models, machine learning, deep learning, artificial intelligence, classification, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>AI-Augmented SOC: A Survey of LLMs and Agents for Security Automation</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Srinivas S.; Kirk B.; Zendejas J.; Espino M.; Boskovich M.; Bari A.; Dajani K.; Alzahrani N.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.3390/jcp5040095</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>AI agent, cybersecurity automation, human-AI collaboration, Large Language Models, security operation center, management, incident response, soc, processes, model, models, artificial intelligence, detection</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>The increasing volume, velocity, and sophistication of cyber threats have placed immense pressure on modern Security Operations Centers (SOCs). Traditional rule-based and manual processes are proving insufficient, leading to alert fatigue, delayed responses, high false-positive rates, analyst dependency, and escalating operational costs. Recent advancements in Artificial Intelligence (AI) offer new opportunities to transform SOC workflows through automation and augmentation.</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: soc, management, incident response, processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>The Integration of Stream Data Models in Modern Transportation Networks</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Naval P.; Jain S.K.; Krishna K.G.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>10.1109/ICTBIG59752.2023.10456023</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Commuter Satisfaction, Data Accuracy, Dynamic Routing, Environmental Impact, Incident Response, Network Efficiency, Predictive Analytics, Real-Time Data Processing, Transportation Networks, Application programs, Data mining, Decision making, Digital storage, Traffic control, Travel time, Urban transportation, Stream data, Transport networks, Transportation network, Wait time</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>The study proposal proposes an innovative strategy for managing modern transport networks, with an emphasis on the coordinated use of analytics, real-time data processing, and dynamic decision-making utilizing stream data models. To create a solid infrastructure for real-time data analysis, it is required to use a diverse set of data sources, such as sensors, GPS devices, traffic cameras, and mobile application software. A strategy for reaching this goal is described below.</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: models, algorithms, machine learning, artificial intelligence, prediction, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Explainable AI and Block chain for Cyber Resilient Online Retail: A Framework for Enhanced Security and Trust</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Syed Abuthahir S.; Jagan Naik G.; Damodhar Rao K.; Venkata Naga Ramesh J.; Jangir P.; Prasanth Kumar K.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Blockchain technologies, Cyber resilience, Explainable deep learning, Online retailing platforms, Operations continuity, Behavioral research, Cybersecurity, Decision making, Deep learning, Network security, Block-chain, Blockchain technology, Cybe resilience, Decisions makings, Online retailing, Online retailing platform, Online retails, Operation continuity, Security and trusts, national</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Online retail platforms frequently encounter challenges such as cyberattacks, data breaches, device malfunctions, and operational disruptions. These issues have intensified in recent years, highlighting the urgent need for businesses to prioritize resilience. Traditional cybersecurity systems are increasingly ineffective against sophisticated cyber threats.</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: framework, deep learning, detection, datasets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Incident Response ChatOps Bot with Automated Dynamic Playbooks for Threat Mitigation</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Decha N.; Chantakhad A.; Ponglimagorn P.; Imsaard S.; Fugkeaw S.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>10.1109/KST67832.2026.11432408</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>automation, ChatOps bot, dynamic playbook, Gemini, incident response, threat mitigation, Artificial intelligence, Behavioral research, Bot (Internet), Botnet, Chatbots, Decision making, Intelligent agents, Markup languages, Network security, Application security, Chat-based operation bot, Common vulnerabilities and exposures, Cyber-attacks, Geminus</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Cyberattacks have become increasingly complex, exploiting vulnerabilities such as those listed in the Open Worldwide Application Security Project (OWASP) Top 10 to compromise systems and delay response times. Traditional incident response (IR) still depends heavily on manual procedures, which are prone to human error and slow mitigation. To address this challenge, this project proposes an AI-driven ChatOps (chat-based operations) Incident Response Bot that integrates automation, dynamic playbooks, and human-in-the-loop decision-making.</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: incident response, organizational, decision making.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>South East Water holistic catchment based monitoring and operational modelling</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Decision Support Systems, Incident Management, Managing discharge of contaminated water, Predictive Operational Models, Real-time Event Forecasting and Warning, Artificial intelligence, Catchments, Decision making, Hazardous materials spills, Real time systems, Runoff, Water pollution, Weather forecasting, Contaminated water, Operational modeling, Predictive operational model, Pump station, Real- time, Time event, Toolsets</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Elster Creek is a low-lying coastal catchment that historically suffered from surcharging, localised spills, and discharge to emergency relief structures (ERS) during extreme weather events. Previously, South East Water (SEW) had no means of prediction or early warning for these events; as a result, intervention could not be taken to mitigate the consequences. In addition to wet weather issues at Elster Creek, the whole of SEW network experiences occasional pump station power failures and dry weather pipe blockages.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, models, artificial intelligence, prediction, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>XAINTRUDER: An Explainable Deep Neural Network-Based Intrusion Detection System for Real-Time Cyber Threats</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Rasmika G.V.; Madhumathi C.S.; Srinivasan L.; Suganya R.T.; Savithadevi T.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>10.1109/ICRTEECT67512.2025.11448726</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Adversarial Training, Concept Drift Detection, Deep Neural Networks (DNN), Explainable Artificial Intelligence (XAI), Graph Attention Network (GAT), Intrusion Detection System (IDS), Temporal Convolutional Network (TCN), Computation theory, Computer crime, Convolution, Convolutional neural networks, Intrusion detection, Network architecture, Network intrusion, Network security, Concept drifts, Convolutional networks, Deep neural network, Graph attention network, Intrusion detection system</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Deep Neural Networks (DNN)-based Intrusion Detection Systems (IDS) can identify advanced cyber threats with high precision but are typically opaque, which restricts the implementation of these systems in operational Security Operations Center (SOCs). Lack of transparency lowers the confidence of the analyst and prevents the efficient incident response. The paper presents the explainable DNN-based IDS named XAINTRUDER, which is a system of real-time cyber threat detection, which combines high classification with multi-level explainability.</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: neural network, detection, intrusion detection, model, models, artificial intelligence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Integrating Artificial Intelligence and Zero Trust Principles in Cloud Forensics and Incident Response: A Comprehensive Review</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Kaur B.; Gupta S.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>10.1109/ISCS69371.2025.11386291</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Cloud Forensics, Cloud Security, Cyber Resilience, Digital Forensics, Forensic Automation, Incident Response, Machine Learning, Threat Detection, Zero Trust Security, Computer crime, Computer forensics, Decision making, Electronic crime countermeasures, Forensic engineering, Learning systems, Network security, Trusted computing, Cloud securities, Cybe resilience</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>The rapid expansion in the domain of cloud computing has significantly changed digital infrastructures by improving scalability, flexibility, and cost-effectiveness. However, this evolution has introduced new caveats for digital forensics because of data distribution, changing environments, and multi-tenant architecture. This paper presents the AI-driven Zero Trust Cloud Forensics and Incident Response (AIZT-CFIR) framework.</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, machine learning, detection, threat detection, framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning with AI for Autonomous Incident Response in DevSecOps: Using RL Agents to Detect, Classify, and Mitigate Security Threats in Cloud-Native DevOps Environments</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Gunawat C.; Nankani J.S.; Gupta R.K.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-032-14044-9_30</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Autonomous incident response, Reinforcement learning, Threat detection, Autonomous agents, Decision making, DevOps, Intelligent agents, Security systems, Artificial intelligence learning, Incident response, Learning frameworks, Machine-learning, Reinforcement learning agent, Reinforcement learning approach, Reinforcement learnings, Security threats, process, machine learning, artificial intelligence, detection</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>In this paper, we provide a complete framework to operationalize security automation in DevSecOps utilizing Artificial Intelligence (AI) and Machine Learning (ML) with a focus on Reinforcement Learning (RL) approaches. The paper describes the development of a RL framework to enable autonomous and adaptive incident response in a Cloud-native environment. Our RL-based framework utilizes intelligent agents that discover, classify, and mitigate security threats autonomously and learn, improve, and apply their detection and response abilities in the continuous learning process autonomously.</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, artificial intelligence, detection, threat detection, framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Improving Cyber Security Incident Response: A Collaborative Tabletop Game Approach</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Seiler A.; Lechner U.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-94924-1_9</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>critical infrastructure, incident response, serious game, tabletop exercise, Decision making, Distributed computer systems, Game design, Human computer interaction, Information systems, Information use, Intelligent systems, Network security, Public works, Cyber security, De facto standard, Game approach, Incident response phase, IT networks, Response process, Security incident</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>This paper explores the potential of a collaborative tabletop game called Operation Raven to improve incident response processes for critical infrastructure. The game material consists of a game board representing the IT network of a critical infrastructure, various cards, and structured response cards to simulate cyber security incident scenarios. The game introduces hypotheses as a collaborative basis for response actions.</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: incident response, decision making, process, processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>QuickSAT/SHERLOCK, An AI Architecture For Vehicle Health Management, Fault Detection and Fault Management For Small Satellites</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Santangelo A.D.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>10.2514/6.2026-0790</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Anomaly detection, Aviation, Data handling, Fault detection, Industrial management, Information analysis, Interplanetary flight, Knowledge based systems, Knowledge management, Orbits, Safety engineering, Small satellites, Space platforms, Vehicle detection, Assembly operations, Fault classification, Fault management, Faults detection, In-orbit servicing, Management functions</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>sci_Zone, Inc is conducting research to develop QuickSAT/SHERLOCK, a system for Vehicle Health Management, Fault Management and Fault Detection with Fault Classification Functions for deep space satellites, human-rated space vehicles, vehicles operating other terrestrial surfaces and small satellites including those in support of In-Orbit Servicing, Assembly and Manufacturing (ISAM) operations and other mission goals. The QuickSAT/Vehicle Management System (VMS) is a flight proven flight management, Vehicle Health Management plus Fault Detection system flown on DARPA and U.S. Space Force flights and scheduled for flights in 2029.</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, artificial intelligence, classification, anomaly detection, framework, module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>The role of generative AI in cyber security</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Curran K.; Curran E.; Killen J.; Duffy C.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F85" t="n">
+        <v>5</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>10.54517/m.v5i2.2796</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, cybersecurity, GenAI, Generative AI, incident response, processes, machine learning, detection, threat detection</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>In the ever-evolving landscape of cyber threats, the integration of Artificial Intelligence (AI) has become popular into safeguarding digital assets and sensitive information for organisations throughout the world. This evolution of technology has given rise to a proliferation of cyber threats, necessitating robust cybersecurity measures. Traditional approaches to cybersecurity often struggle to keep pace with these rapidly evolving threats.</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, artificial intelligence, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Human-AI Collaboration and Cyber Security Training: Learning Analytics Opportunities and Challenges</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Maennel K.; Maennel O.M.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F86" t="n">
+        <v>3</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>10.1109/SIN63213.2024.10871610</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>artificial intelligence, cyber security, education, human-AI collaboration, incident response, learning analytics, Cyber attacks, Federated learning, Complex decision, Cyber security exercise, Cyber security trainings, Cyber-defense, Exponential growth, Global threats, Human-artificial intelligence collaboration, Learning analytic, Adversarial machine learning, global, processes, model</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Cyber security is becoming more complex due to the exponential growth of interconnected systems and the global threat landscape. To mitigate those risks, there is a need for a skilled cyber security workforce that can navigate the complex decision-making in rapidly evolving cyberspace. Artificial intelligence (AI) is rapidly adopted into cyber defence operations, but we can not effectively train human and AI-assisted cyber defence operators without understanding the underlying learning theory and eco-systems.</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, machine learning, artificial intelligence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Digital technologies in the system of state economic security management</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Kryvonos L.; Logvynenko S.; Zhurba O.; Kukin I.; Pynda Y.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>10.21533/pen.v14.i1.1527</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Cyber Resilience, Digitalization, Economic Security, Multi-Criteria Analysis, Ukraine, national, economic, government, management, incident response, security operations center, artificial intelligence, detection, phishing, malware, framework</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>This study investigates how digital technologies can strengthen Ukraine’s system of economic security management under conditions of war, reconstruction, and escalating cyber threats. The research applies systems analysis, strengths-weaknesses-opportunities-threats analysis, comparative benchmarking with Estonia, Lithuania, and Poland, and an evidence-informed modeling framework. An Economic Security Digitalization Index is constructed from the United Nations E-Government Development Index and the Network Readiness Index, and seven candidate technologies are evaluated: a Government Security Operations Center with Security Information and Event Management and Security Orchestration,...</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, detection, phishing, malware, framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>An Integration of Digital Twin and 6G Edge Computing Approach to Secure Cyber Physical Systems</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Suganya R.; Kiran A.; Akila D.; Spandana S.; Rajagopal M.; Nageswaran A.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F88" t="n">
+        <v>17</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>10.1007/s11277-024-11181-5</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>6G, Cyber physical systems, Digital twin, Edge of Things, Optimization, Security, Cybersecurity, Decision making, Edge computing, Embedded systems, Emergency services, Learning algorithms, Machine learning, Network security, Cybe-physical systems, Cyber-physical systems, Edge of thing, Optimisations, Proposed architectures, Smart devices</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>The proposed architecture for the 6G Edge of Things (EoT) system integrates two distinct networks: the EoT network and the digital twin (DT) network. The EoT network consists of interconnected smart devices and sensors organized into layers of things, edges, and clouds. Edge computing nodes facilitate low-latency services, emergency responses, and real-time decision-making, while the central cloud layer manages resource-intensive tasks.</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: algorithms, models, machine learning, detection, threat detection, module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Assessing the Frontiers of SIEM Technology: A Rigorous Evaluation and Validation of Innovative Features in SIEM Solutions</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Akbas E.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>10.1145/3704391.3704395</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Big Data, Correlation Engine, Cyber Security, Event Correlation, Incident Response, Log, Machine Learning, Security Information and Event Management, Security Operation Center, Threat Detection, Cyber attacks, Risk management, Laws and regulations, Machine-learning, Security information and event managements, Information management, industry, management</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Security Information and Event Management (SIEM) systems play a crucial role in modern cybersecurity by aggregating, correlating, and analyzing vast amounts of security data. As cyber threats continue to evolve, the demand for Next-Generation SIEMs (NG-SIEMs) has grown, promising advanced features and enhanced capabilities. There are dozens of studies related to the analysis and comparison of SIEM solutions in academia and industry, but none of them have examined these analyses in terms of existing laws and regulations related to SIEM worldwide.</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, incident response, risk management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>The vigilance paradox: automation reliance inside the modern SOC</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Tilbury J.; Flowerday S.V.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>10.1108/ICS-08-2025-0318</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Automation, Bias, Complacency, Human-Automation Interaction, Security Operations Center, Artificial intelligence, Behavioral research, Human computer interaction, Information use, Least squares approximations, Life cycle, Man machine systems, Security systems, Automation bias, Cognitive factors, Design/methodology/approach, Human-automation interactions, Large scale surveys, Mixed method, Securities analysts</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Purpose – The purpose of this study is to measure how susceptible security analysts are to these cognitive factors. Automation and artificial intelligence (AI) are increasingly leveraged in Security Operations Centers (SOCs) to assist security analysts in managing growing alert volumes and escalating threats. However, their rapid integration introduces the cognitive risks of automation complacency (AC) which can lead to automation bias (AB) among security analysts.</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: algorithm, model, models, artificial intelligence, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>The Risk Operations Center (RoC): A Unified Framework for Proactive, Business-Aligned Cyber Risk Management</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Singh J.P.; Das S.; Verma N.; Katheria S.; Joshi S.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>10.1109/ICSES66558.2026.11478902</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Adaptive decision-making, AI-driven cybersecurity, Cognitive threat modeling, Enterprise Knowledge Graph, Explainable reinforcement learning, Predictive analytics, Risk Operations Center, Bayesian networks, Cybersecurity, Decision making, Deep learning, Inference engines, Intelligent agents, Intelligent systems, Knowledge management, Network security, Neural networks, Risk assessment, Risk management, Adaptive decision making</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>As cybersecurity threats continue to grow in complexity, dynamism and business impact, the demand for advanced intelligence systems that move beyond reactive detection methods grows. Traditional Security Operations Centers (SOCs) are typically not predictive, aligned with the business and agile enough to adapt to changing threats with delayed responses, operational inefficiencies and residual enterprise risk. This study plans to design and assess an AI-driven Risk Operations Center (RoC) based on multi-source data aggregation, cognitive threat modeling, predictive and prescriptive analytics, business context alignment, and explainable reinforcement learning to improve proactive cyber risk...</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: business, management, risk management, enterprise, decision making, incident response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Detection of Network Intrusions Using Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>MacEdo A.M.; Magalhaes J.P.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>10.1109/AICCSA59173.2023.10479349</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Automation, Incident, Recovery, Security, Security Operations Center, Anomaly detection, Computer crime, Cybersecurity, Digital forensics, Machine learning, Central point, Cyber security, Cyber-attacks, Machine-learning, Network intrusions, Security operation center, Security threats, Network security, incident response</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>The proliferation and widespread use of new technologies has inevitably brought an increase in the occurrence of cyber-attacks. The adoption of cybersecurity technologies and policies are increasingly a central point that requires innovative and appropriate solutions. This paper proposes a solution that aims to help organisations to identify, detect, manage, and respond to security threats assertively and timely.</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, anomaly detection, machine learning, artificial intelligence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>LE2C: LLM-Enhanced Event Evolutionary Graph for Explainable Classification</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Liang J.; Wu S.; Wang X.; Niu J.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>10.1007/978-981-95-5719-6_23</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Event Evolutionary Graph, Explainable Multi-label Classification, Knowledge Discovery, Large Language Model, Classification (of information), Decision making, Graphic methods, Intelligent systems, Knowledge graph, Knowledge management, Learning systems, Semantics, Customer service management, Decisions makings, Events classification, Incident response, Language model, Multi-label classifications, Multi-labels, Directed graphs</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>In the development of intelligent systems, multi-label event classification plays a vital role in enabling accurate decision-making across diverse scenarios such as incident response, customer service, and urban management. Although existing graph-based approaches for multi-label classification have shown potential, they struggle to model directed label dependencies and lack explainability, resulting in black-box decision-making processes. To address these issues, we propose a novel LLM-enhanced Event Evolutionary graph for Explainable Classification (LE2C) method.</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: classification, model, models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>IP SafeGuard-An AI-Driven Malicious IP Detection Framework</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Siam A.A.; Alazab M.; Awajan A.; Hasan M.R.; Obeidat A.; Faruqui N.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F94" t="n">
+        <v>2</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>10.1109/ACCESS.2025.3569289</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>artificial intelligence, cyber attack, cyber defense, Cyber security, IP address, SOC, threat intelligence, Computer viruses, Cyber attacks, Search engines, Critical challenges, Cyber-attacks, Cyber-defense, Detection framework, Machine-learning, Real- time, Security operation center, Federated learning, management, incident response</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>The rising frequency and sophistication of cyberattacks have made real-time malicious IP detection a critical challenge for modern Security Operations Center (SOC). Traditional solutions, such as static blacklists and manual IP reputation checks, are no longer sufficient in today's dynamic threat scenario. To overcome these constraints, we present IP SafeGuard, an AI-driven platform that incorporates multi-source threat intelligence, sophisticated feature engineering, and machine learning (ML)for real-time IP categorization.</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, framework, model, machine learning, artificial intelligence, classification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Towards Data Science for Cybersecurity: Machine Learning Advances as Glowing Perspective</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Mihailescu M.I.; Nita S.L.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-16078-3_2</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Artificial intelligence, Cyber threat intelligence, Cybersecurity, Data science, Decision making, Deep learning, Intrusion detection, Machine learning, incident response, model, framework</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>The current computing context has developed important opportunities and challenges by the new attacks that occurred recently due to the pandemic situation (COVID-19), cybersecurity has crossed and still passing through significant changes by the technology and its operation. Many computer security incident response teams (CSIRT) and cybersecurity centers had reported significant behaviors of the attacks and they raised multiple warning signs, some of them being ignored by different third parties and others were taken into consideration and new frameworks started to be translated into research directions as a cross-collaboration between researchers and professionals. As a conclusion of...</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, model, deep learning, artificial intelligence, detection, intrusion detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>The Role of Artificial Intelligence in Enhancing Cybersecurity: Trends, Challenges, and Ethical Considerations</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Serafim G.M.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>10.1007/978-981-96-8632-2_1</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>AI-powered cyber-attacks, Cyber threat intelligence, Ethical AI governance human-AI teaming, Predictive security analysis, SOCs, Anomaly detection, Behavioral research, Computer crime, Crime, Cybersecurity, Deep learning, Ethical aspects, Internet of things, Learning algorithms, Learning systems, Network security, Artificial intelligence-powered cybe-attack, Cybe threat intelligence, Cyber security, Cyber threats</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>The increasing integration of Artificial Intelligence (AI) in the Cybersecurity domain has changed the way that countries defend themselves against ever-evolving and dynamic threats. This paper provides a broad survey of the use of AI in Cybersecurity, focusing on the new and emerging trends, the main issues, and the need for ethical steering (Harshith J, Gill MS, Jothimani M (2023) Evaluating the Vulnerabilities in ML systems in terms of adversarial attacks. arXiv preprint arXiv:2308.12918.</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, algorithms, models, machine learning, deep learning, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>An Integrated Approach to AI-Enhanced Security Information and Event Management</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Mugeshwaran K.; Maharajan K.; Nithish D.; Dinesh S.; Uday N.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>10.1109/ICCRTEE64519.2025.11053120</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>adaptive threat defense, AI-driven security event processing, AI-powered SIEM, automated incident response, deep learning security analytics, Innovation &amp; Infrastructure, machine learning for cybersecurity, real-time threat detection, Resilient Digital Infrastructure, Secure &amp; Sustainable Societies, Security information and event management (SIEM), Computer architecture, Cybersecurity, Learning systems, Machine learning, Network security, Security systems, Systems analysis, Artificial intelligence-driven security event processing, Artificial intelligence-powered security information and event management</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>An SIEM system enabled by Artificial Intelligence (AI) was proposed to solve the major challenges of current security monitoring practices. The proposed architecture incorporates the use of artificial intelligence at all levels of the security operation center to transform traditional security operations from passive detection to active protection. The system design incorporates the application of machine learning for pattern recognition, contextual analysis, and alert prioritization to overcome the major challenges of traditional SIEM solutions that are based on rules and produce numerous alerts.</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, deep learning, artificial intelligence, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Application of Large Language Models for Cybersecurity of Power Distribution Grids: Challenges and Opportunities</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Rahman M.M.; Rahman A.; Sun W.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>10.1109/NAPS66256.2025.11272351</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Cyber-physical power system, cybersecurity, human-in-the-loop, large language model, vulnerability, Artificial intelligence, Cyber Physical System, Electric power system security, Embedded systems, Learning systems, Network security, Probability distributions, Cybe-physical power system, Cyber physicals, Cyber security, Domain specific, Language model, Physical power, Threat detection, Predictive analytics</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>This paper explores the application of domain-specific large language models (LLMs) as a transformative approach to enhancing cybersecurity in power distribution networks. We propose a comprehensive framework that integrates LLMs with existing grid infrastructure to enable predictive analytics, proactive vulnerability assessment, intelligent threat detection, and automated incident response. By incorporating reinforcement learning (RL) agents and a human-in-the-loop mechanism, the framework supports robust and trustworthy decision-making.</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: models, model, artificial intelligence, detection, threat detection, framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>LLMs for Cybersecurity in the Big Data Era: A Comprehensive Review of Applications, Challenges, and Future Directions</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Karras A.; Theodorakopoulos L.; Karras C.; Theodoropoulou A.; Kalliampakou I.; Kalogeratos G.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F99" t="n">
+        <v>7</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>10.3390/info16110957</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>adversarial attacks, AI-powered cybercrime, big data, cyber threat intelligence, cybersecurity, decision-making, ethical AI, explainable AI (XAI), governance, human–AI collaboration, incident response, large language models (LLMs), security analytics, threat detection, Artificial intelligence, Computer crime, Cyber attacks, Data integration, Decision making, Network security</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>This paper presents a systematic review of research (2020–2025) on the role of Large Language Models (LLMs) in cybersecurity, with emphasis on their integration into Big Data infrastructures. Based on a curated corpus of 235 peer-reviewed studies, this review synthesizes evidence across multiple domains to evaluate how models such as GPT-4, BERT, and domain-specific variants support threat detection, incident response, vulnerability assessment, and cyber threat intelligence. The findings confirm that LLMs, particularly when coupled with scalable Big Data pipelines, improve detection accuracy and reduce response latency compared with traditional approaches.</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, models, artificial intelligence, detection, threat detection, bert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Serious Games for Cybersecurity: How to Improve Perception and Human Factors</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Barletta V.S.; Calvano M.; Caruso F.; Curci A.; Piccinno A.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F100" t="n">
+        <v>9</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>10.1109/MetroXRAINE58569.2023.10405607</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>cybersecurity, Explainable AI, human factors, serious game, Behavioral research, Decision making, Domain Knowledge, Human engineering, Risk management, Behaviour models, Cognitive model, Cyber security, Cyber threats, Dark web, Digital economy, Explainable artificial intelligence, Research analysis, Technological innovation, Threat detection, Serious games</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Cybersecurity is a growing problem in today's technological innovation and new digital economy. Threat actors cause a danger to people's safety or lead to the compromise of intellectual property, either sold on the dark web or used as leverage for ransom. Many executives believe cybersecurity is the responsibility of Information Technologies (IT).</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, decision making, incident response, processes, risk management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Analysis of Explainable Artificial Intelligence Methods in Security Information and Event Management Systems</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Bulgakova E.V.; Vasilevskiy P.A.; Doynikov D.S.; Kubankov A.N.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>10.1109/IEEECONF64229.2025.10948089</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>AI, cyber threats, cybersecurity, incident response, information security, LIME, threat detection, XAI SIEM, Decision making, Information management, Artificial intelligence methods, Cyber security, Data volume, Information security systems, Intelligence models, Security information and event management systems, Cyber attacks, management, processes, models</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>The present article engages with the ongoing discourse surrounding the implementation of artificial intelligence and explainable artificial intelligence within the domain of information security systems. In the context of escalating cyber threats and mounting data volumes, conventional defense methodologies are proving to be inadequate. Consequently, the integration of artificial intelligence has emerged as a pivotal strategy to enhance the efficacy of threat detection and response processes.</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, models, detection, threat detection, model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Advancing the Threat Intelligence with AI: An Overview, Taxonomy and Roadmap</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Tomičić I.; Grd P.; Bernik A.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>10.3897/jucs.137544</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Cybersecurity, Incident Response, SOC, Threat Detection, Threat Intelligence, processes, workflow, machine learning, deep learning, classification, prediction, detection, framework</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>This paper presents a comprehensive analysis of the integration of artificial intelligence (AI) into threat intelligence (TI) systems, focusing on its potential to enhance cybersecurity operations. The paper presents an extensive literature review, covering the current state of AI applications in TI, including machine learning, deep learning, and natural language processing for automating threat detection, classification, and analysis. It outlines the core functions of AI in TI, such as threat detection, correlation, prediction, and automated response, and introduces a detailed taxonomy categorizing AI techniques based on their roles in enhancing TI processes.</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, deep learning, artificial intelligence, classification, prediction, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>AI-Driven Threat Intelligence for Predictive Cyber Defense in Smart Cities</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Nagpal M.; Singh R.P.; Shubneet; Yadav A.R.; Siwach P.; Talwandi N.S.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-032-17020-0_23</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>AI-Driven Threat Intelligence, Federated Learning, Predictive Cyber Defense, Smart City Security, Zero-Day Attacks, Anomaly detection, Artificial intelligence, Blockchain, Critical infrastructures, Cybersecurity, Data privacy, Malware, Network security, Predictive analytics, Public works, Resource allocation, City securities, Cyber security, Cyber-defense, Polymorphic malware</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Smart cities are rapidly embracing interconnected IoT devices and critical infrastructure, expanding the complexity and vulnerability of urban cyberspace. Conventional cybersecurity remains largely reactive and signature-based, falling short against advanced attacks such as zero-day exploits and polymorphic malware. This research introduces a novel AI-driven threat intelligence framework for predictive cyber defense in smart city environments that integrates federated learning for privacy-preserving analytics, blockchain-secured data provenance for immutable logging, and real-time anomaly detection to anticipate and mitigate threats across municipal networks.</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, detection, threat detection, anomaly detection, malware, benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>QuickSAT/SHERLOCK, An AI Architecture For Vehicle Health Management, Fault Detection and Fault Management and complex Human-Machine Systems</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Santangelo A.D.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>10.2514/6.2026-0995</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Aerospace vehicles, Anomaly detection, Aviation, Data handling, Fault detection, Industrial management, Information analysis, Interplanetary flight, Knowledge based systems, Knowledge management, Man machine systems, Orbits, Risk perception, Safety engineering, Small satellites, Space platforms, Vehicle detection, Assembly operations, Fault classification, Fault management</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>sci_Zone, Inc is conducting research to develop QuickSAT/SHERLOCK, a system for Vehicle Health Management, Fault Management and Fault Detection with Fault Classification Functions for deep space satellites, human-rated space vehicles, vehicles operating other terrestrial surfaces and small satellites including those in support of In-Orbit Servicing, Assembly and Manufacturing (ISAM) operations and other mission goals. The QuickSAT/Vehicle Management System (VMS) is a flight proven flight management, Vehicle Health Management plus Fault Detection system flown on DARPA and U.S. Space Force flights and scheduled for flights in 2029.</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, artificial intelligence, classification, anomaly detection, framework, module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Generative AI in Cybersecurity: Threats, Vulnerabilities, and Protective Measures</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ugale S.P.; Sinha A.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>10.1109/ICFT66708.2025.11336288</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Cybersecurity, Deepfakes, Generative Adversarial Networks (GANs), Generative AI, Large Language Models (LLMs), Model Vulnerabilities, Behavioral research, Computer crime, Data privacy, Generative adversarial networks, Network security, Adversarial networks, Cyber security, Decisions makings, Deepfake, Generative adversarial network, Language model, Large language model, Model vulnerability, Protective measures</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence: Generation GenAI will turn entire industries on their heads because it can generate and simulate content, roleplaying or decision making. But in the case of cybersecurity, GenAI is a double-edged sword: It can strengthen defense systems even as it broadens the attack surface for bad actors. The rest of this paper is organized as follow: Section II presents an overview regarding the threats, vulnerabilities and countermeasure existed for cyber security from GenAI aspect.</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, models, artificial intelligence, phishing, malware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Vulnerability Assessment in Heterogeneous Web Environment Using Probabilistic Arithmetic Automata</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Moshika A.; Thirumaran M.; Natarajan B.; Andal K.; Sambasivam G.; Manoharan R.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F106" t="n">
+        <v>12</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>10.1109/ACCESS.2021.3081567</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Deterministic Arithmetic Automata (DAA), heterogeneous web application, probabilistic arithmetic automata (PAA), Security analytics, Automata theory, Decision making, Learning systems, Predictive analytics, Robots, Business enterprise, Incident response, Machine learning techniques, Probabilistic arithmetics, Security programs, Statistical datas, Vulnerability assessments, Vulnerability detection, Web services, enterprise, business</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>In the current scenario most of the business enterprises are running through web applications. But the major drawback is that they fail to provide a secure environment. To overcome this security issue in web applications, there are many vulnerability detection tools are available at present.</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: enterprise, business, decision making, incident response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Use of Explainable Artificial Intelligence for Analyzing and Explaining Intrusion Detection Systems</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Hermosilla P.; Díaz M.; Berríos S.; Allende-Cid H.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F107" t="n">
+        <v>7</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>10.3390/computers14050160</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>forensic analysis, LIME, SHAP, TabNet, UNSW-NB15, XAI, XGBoost, Computer forensics, Forensic engineering, Intelligent computing, Intelligent systems, Decision-making process, Intrusion Detection Systems, Local interpretable model-agnostic explanation, Shapley, Shapley additive explanation, Deep learning, global, incident response, process</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>The increase in malicious cyber activities has generated the need to produce effective tools for the field of digital forensics and incident response. Artificial intelligence (AI) and its fields, specifically machine learning (ML) and deep learning (DL), have shown great potential to aid the task of processing and analyzing large amounts of information. However, models generated by DL are often considered “black boxes”, a name derived due to the difficulties faced by users when trying to understand the decision-making process for obtaining results.</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, detection, intrusion detection, model, models, machine learning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Protecting Public Safety and Critical Infrastructure Systems in Smart Cities via Cybersecurity: AI- Based Threat Detection and Response</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Sethi M.; Verma V.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>10.1109/GINOTECH63460.2025.11077039</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Adversarial attacks, AI-based threat detection, Anomaly detection, Critical infrastructure, Distributed systems, Federated learning, Incident response, Internet of Things (IoT), Machine learning, Public safety, Automation, Behavioral research, Civil defense, Cybersecurity, Data privacy, Denial-of-service attack, Distributed computer systems, Emergency services, Health care, Internet of things</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Smart cities are evolving rapidly (enhanced public safety, improved infrastructure management and optimized urban services) as IoT and automation technologies are embraced in urban spaces worldwide. Yet this very transformation exposes critical infrastructure systems to risks of cyberattacks unprecedented in scale and in nature. That said, safeguarding public safety within smart cities - especially at critical infrastructure sectors such as energy, transportation, health care, and emergency response - requires proactive measures against emerging cyber threats against both physical and digital infrastructures.</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, threat detection, algorithms, models, machine learning, deep learning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Security Tools' API Recommendation Using Machine Learning</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Sworna Z.T.; Sreekumar A.; Islam C.; Babar M.A.</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>10.5220/0011708300003464</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>API Recommendation, Security Operation Center, Security Orchestration, Security Tools' API, Information use, Learning systems, Regression analysis, System-on-chip, Incident response, Learning models, Machine learning models, Security incident, Security tool' API, Security tools, State of the art, Deep learning, soc, model, models, machine learning</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Security Operation Center (SOC) teams manually analyze numerous tools' API documentation to find appropriate APIs to define, update and execute incident response plans for responding to security incidents. Manually identifying security tools' APIs is time consuming that can slow down security incident response. To mitigate this manual process's negative effects, automated API recommendation support is desired.</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, model, models, deep learning.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/articulos.xlsx
+++ b/data/articulos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:Q113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,17 +471,8587 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Revista/Conferencia</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Volumen</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Numero</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Paginas</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Editorial</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Palabras Indexadas</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Resumen 3 lineas</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Justificación categoría</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Research on Enterprise Security Operation Based on Large Model Technology</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Li L.; Wang T.; An Q.; Dong J.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>10.1145/3773365.3773614</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Proceedings of 2025 8th International Conference on Computer Information Science and Artificial Intelligence, CISAI 2025</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1587-1593</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105026341399?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Association for Computing Machinery, Inc</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Graph Analysis Technology, Large Model Technology, Security Operation, The Multimodal Parsing, Artificial intelligence, Data privacy, Information management, Network security, Security systems, Enterprise security, Graph analysis, Graph analyze technology, Large models, Modeling technology, Security operation center, Security operations, Cost effectiveness, enterprise, incident response, soc</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>With the continuous evolution of cyber threats and the growing complexity of enterprise IT infrastructures, traditional Security Operations Centers (SOCs) face challenges such as alert overload, talent shortages, and the limitations of rule-based engines. Large-model technology (LMT) provides a new pathway toward intelligent and automated security operations. This study analyzes key techniques - including the Transformer architecture, the pre-training and fine-tuning paradigm, and multimodal learning - and validates their effectiveness through practical case studies in industries such as finance and manufacturing.</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, models, artificial intelligence, transformer, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Evaluating Human-Machine Interaction Paradigms for Effective Human-Artificial Intelligence Collaboration in Cybersecurity</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Malatji M.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>10.1109/ICICYTA64807.2024.10913015</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2024 International Conference on Intelligent Cybernetics Technology and Applications, ICICyTA 2024</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1268-1272</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105001661286?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>AI in cybersecurity, automated security, cybersecurity operations, human-AI teaming, human-machine interaction (HMI), incident response, Risk management, Artificial intelligence in cybersecurity, Cyber security, Cybersecurity operation, Human machine interaction, Human-artificial intelligence teaming, Human-machine interaction, Interaction paradigm, Decision making, management, detection, threat detection</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>This paper examines the efficacy of various Human-Machine Interaction (HMI) paradigms in enhancing cybersecurity practices through human-artificial intelligence (AI) collaboration. As cyber threats grow increasingly sophisticated, organisations are turning to AI to bolster their defence mechanisms, threat detection, incident response, and overall security management. Six HMI paradigms are analyzed: Humans in the Loop (HITL), Humans on the Loop (HOTL), Humans out of the Loop (HOOTL), Humans alongside the Loop (HATL), Humans-in-command (HIC), and Coactive Systems.</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Generative Artificial Intelligence and Cybersecurity Risks: Implications for Healthcare Security Based on Real-life Incidents</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sallam M.; Al-Mahzoum K.; Sallam M.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>10.58496/MJAIH/2024/019</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Mesopotamian Journal of Artificial Intelligence in Healthcare</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>184-203</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105020297769?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Mesopotamian Academic Press</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Cybersecurity, Health care, Privacy, Risk, Threat, impact, governance, incident response, algorithms, artificial intelligence</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Background: The potential of generative artificial intelligence (genAI) tools, such as ChatGPT, is being increasingly explored in healthcare settings. However, the same tools also introduce significant cybersecurity risks that could compromise patient safety, data integrity, and institutional trust. This study aimed to examine real-world security breaches involving genAI and extrapolate their potential implications for healthcare settings.</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, algorithms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Data-Driven Intelligence Can Revolutionize Today’s Cybersecurity World: A Position Paper</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sarker I.H.; Janicke H.; Maglaras L.; Camtepe S.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-48855-9_23</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Communications in Computer and Information Science</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1936</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>302-316</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85181978743?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Springer Science and Business Media Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>AI, Augmenting Experts Knowledge, Automation, Cybersecurity, Data-Driven Intelligence, Human Assistance, Machine Learning, Decision making, Predictive analytics, Augmenting expert knowledge, Cyber security, Cyber threats, Data driven, Decisions makings, Expert knowledge, Machine-learning, Position papers, incident response, detection, threat detection</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>As cyber threats evolve and grow progressively more sophisticated, cyber security is becoming a more significant concern in today’s digital era. Traditional security measures tend to be insufficient to defend against these persistent and dynamic threats because they are mainly intuitional. One of the most promising ways to handle this ongoing problem is utilizing the potential of data-driven intelligence, by leveraging AI and machine learning techniques.</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A Machine Learning Approach to Detection of Critical Alerts from Imbalanced Multi-Appliance Threat Alert Logs</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ndichu S.; Ban T.; Takahashi T.; Inoue D.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>10.1109/BigData52589.2021.9671956</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Proceedings - 2021 IEEE International Conference on Big Data, Big Data 2021</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2119-2127</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85125346905?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>alert fatigue, alert screening, Class imbalance, data cleaning, machine learning, oversampling, Information management, Intrusion detection, Random forests, Support vector machines, Alert data, Machine learning approaches, Network intrusion detection systems, Over sampling, Securities analysts, Security alerts, Decision trees, management, incident response, process</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>The extraordinary number of alerts generated by network intrusion detection systems (NIDS) can desensitize security analysts tasked with incident response. Security information and event management systems (SIEMs) perform some rudimentary automation but cannot replicate the decision-making process of a skilled analyst. Machine learning and artificial intelligence (AI) can detect patterns in data with appropriate training.</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, detection, artificial intelligence, intrusion detection, random forest, support vector machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Automation Bias and Complacency in Security Operation Centers</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tilbury J.; Flowerday S.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>10.3390/computers13070165</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Computers</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85199625999?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Multidisciplinary Digital Publishing Institute (MDPI)</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>artificial intelligence, automation, automation bias, automation complacency, decision support systems, human-in-the-loop, machine learning, security analyst, security operation center, incident response, soc, processes, detection</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>The volume and complexity of alerts that security operation center (SOC) analysts must manage necessitate automation. Increased automation in SOCs amplifies the risk of automation bias and complacency whereby security analysts become over-reliant on automation, failing to seek confirmatory or contradictory information. To identify automation characteristics that assist in the mitigation of automation bias and complacency, we investigated the current and proposed application areas of automation in SOCs and discussed its implications for security analysts.</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, artificial intelligence, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Digital Safeguards: Unravelling the Complex Interplay Between Emerging Threats and Proactive Cyber Defence Strategies</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Aladiyan A.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>10.58346/JISIS.2025.I1.022</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Journal of Internet Services and Information Security</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>348-360</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105002409456?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Innovative Information Science and Technology Research Group</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>AI, Anomaly Detection, Automation, Cybersecurity, Data Privacy, Ethical Considerations, Incident Response, Machine Learning, Predictive Analytics, Threat Detection, company, process, algorithms, models, artificial intelligence, detection</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>In the past few years, advanced cyber security capabilities have flourished via a new era of use in dangerous A.I. technologies rapidly developed strategies using dozens of different online risks to even more effectively prevent, detect, and respond prolifically. With digital infrastructures being the backbone of enterprises today, cyber-attacks have grown in complexity and sophistication over time to thrive as we know them now this effectively means that security frameworks would need AI after that.</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: algorithms, models, machine learning, artificial intelligence, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>On Cybersecurity Incident Response Decision Support System in Smart Grids</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sen O.; Mahjoob A.; Neumuller M.; Ulbig A.; Decker S.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>10.1109/SmartGridComm65349.2025.11204644</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2025 IEEE International Conference on Communications, Control, and Computing Technologies for Smart Grids, SmartGridComm 2025 - Proceedings</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105022116026?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Cyberattack, Cybersecurity, Decision Support System, Incident Response, Smart Grid, Artificial intelligence, Behavioral research, Computer crime, Decision making, Industrial management, Information management, Network security, User interfaces, Cyber security, Cyber-attacks, Decision supports, Decisions makings, Help systems, Modulars, Support systems</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>The growing complexity of control systems in smart grids has increased their vulnerability to cyber-attacks. In this paper, we introduce a modular decision support system to help system operators prioritize and select countermeasures following a cyber-incident. The proposed system combines attack graph analysis with multi-criteria decision-making techniques, enabling the evaluation of response actions based on customizable priorities such as cost, technical impact, and time required for deployment.</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: incident response, management, decision making.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Human-centric Artificial Intelligence enabled Digital Images and Videos Forensic Triage</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Li S.; Liu Y.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>10.1109/HCCS59561.2023.10452651</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Proceedings - 2023 Human-Centered Cognitive Systems, HCCS 2023</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85187197721?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Artificial intelligence, Digital forensics, forensics triage, Image recognition and classification, Decision making, Electronic crime countermeasures, Image classification, Image recognition, Decisions makings, Digital image forensics, Digital system, Digital video forensics, Effectiveness and efficiencies, Forensic analysis, Forensic triage, Forensics investigators, Human-centric, Incident response, processes</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Digital forensics and incident response (DFIR) involve huge volume of data collected from digital systems that requires investigators to quickly sift through and prioritise relevant evidence. The forensics investigator team faces many challenges when analysing the processes to keep them on target and improve them. A lack of a systematic approach to data analysis can lead to slower decision-making.</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: decision making, incident response, processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hybrid LSTM-QEQ Framework for Enhanced Cyber Threat Detection and Response in Critical Power Grid Infrastructure</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Shi J.; Wang H.; Lu G.; Wang M.; Jiang X.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>10.1142/S021812662650091X</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Journal of Circuits, Systems and Computers</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2650091</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105030181838?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>World Scientific</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>artificial intelligence, big data, cybersecurity, deep learning, Power grid, security warning, company, management, incident response, algorithms, model, detection, threat detection, framework, lstm</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>The rising multifaceted nature of cyber threats to critical Power Grid Infrastructure calls for new approaches in ensuring power systems resiliency and stability. Existing methods based on deep learning and predictive analysis have shown significant gains in the area of threat mitigation and response time. However, such approaches have been rendered limited in their scope by their lack of dynamic reaction to the shifts in cyberattack tactics, particularly in sequential and multi-dimensional settings.</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, threat detection, framework, lstm, algorithms, model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CRUSOE: A toolset for cyber situational awareness and decision support in incident handling</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Husák M.; Sadlek L.; Špaček S.; Laštovička M.; Javorník M.; Komárková J.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F12" t="n">
+        <v>49</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>10.1016/j.cose.2022.102609</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Computers and Security</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>102609</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85123054280?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Elsevier Ltd</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Cyber situational awareness, Decision support, Incident response, Network monitoring, OODA Loop, Artificial intelligence, Cybersecurity, Data visualization, Network security, Cybe situational awareness, Cyber security, Decision supports, Security operation center, Security situation, Situational awareness, Toolsets, Decision support systems, process</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>The growing size and complexity of today's computer network make it hard to achieve and maintain so-called cyber situational awareness, i.e., the ability to perceive and comprehend the cyber environment and be able to project the situation in the near future. Namely, the personnel of cybersecurity incident response teams or security operation centers should be aware of the security situation in the network to effectively prevent or mitigate cyber attacks and avoid mistakes in the process. In this paper, we present a toolset for achieving cyber situational awareness in a large and heterogeneous environment.</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: incident response, process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A cases and clusters framework for recording, retrieving, and reusing response plans in structured cybersecurity incident management</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Guerra P.A.C.; Nunes R.C.; de Lima Silva L.A.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>10.1016/j.engappai.2025.111831</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Engineering Applications of Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>111831</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105012589651?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Elsevier Ltd</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Case-based reasoning, Clustering, Cybersecurity, Cybersecurity incident response, Decision-support system, Explainable artificial intelligence, Ontology, Case based reasoning, Cluster analysis, Decision making, Query processing, Casebased reasonings (CBR), Clusterings, Cyber security, Decision supports, Incident response, Ontology's, Support systems, Decision support systems, organization</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>The dynamic and increasing sophistication of cyberattacks and vulnerability exploitation creates a need for Explainable Artificial Intelligence (XAI) approaches that help maintain cyber resilience in organizations. In structured cybersecurity incident management, effective incident response demands explainable outputs from AI-based decision-support systems. To approach this problem, this work presents a framework for reusing concrete experiences of cybersecurity incident response, capturing problem-solving data and knowledge as cases for integrated Case-Based Reasoning (CBR) and Clustering.</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, incident management, organization, decision making, incident response, process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Multi-agent DSS for Smart Government Crisis Management</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Jiang H.; Wang Y.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-51734-1_7</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Lecture Notes in Computer Science (including subseries Lecture Notes in Artificial Intelligence and Lecture Notes in Bioinformatics)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>14208</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>88-100</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85184148168?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Springer Science and Business Media Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Crisis, Crisis Management, Decision Support System, Multi-Agent, Smart Government, Data warehouses, Decision making, Information management, Intelligent agents, Multi agent systems, Decision evaluations, Decision makers, Decision supports, Decision-making process, Decisions makings, Evaluation and analysis, Multi agent, Decision support systems, government, management</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>The conventional government fails to acknowledge the paramount importance of data in crisis management. The Decision Support System (DSS) for intelligent governance can furnish decision makers with effective crisis decision support. The process of government crisis decision-making entails the pre-decision monitoring of big data on crisis information, situation simulation during the decision-making process, and post-decision evaluation and analysis, thereby establishing a cyclical framework.</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, governance, decision making, incident response, process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Enhancing cybersecurity incident response: AI-driven optimization for strengthened advanced persistent threat detection</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ali G.; Shah S.; ElAffendi M.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F15" t="n">
+        <v>24</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>10.1016/j.rineng.2025.104078</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Results in Engineering</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>104078</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85215391564?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Elsevier B.V.</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Cybersecurity incident response, Machine learning, Security information and event management, Cyber attacks, Cyber security, False positive, Incident response, Machine learning techniques, Machine-learning, Optimisations, Security incident, Security information and event managements, Threat detection, Adversarial machine learning, organizational, management, process, model, detection, dataset</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>The Cyber Security Incident Response Team executes its critical duties in the Centralized Security Operation Centers. Its primary target is to protect organizational resources from all types of Advanced Persistent Threats (APTs) and attacks while making the correct judgments at the right time. Despite the great efforts and the efficient tools, the incident response mechanism faces two significant challenges.</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, threat detection, model, machine learning, dataset, random forest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>UAV-Enabled Intelligent Traffic Management Using Multi-Modal Deep Learning and IoT Integration</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sahutoglu Z.; Bakirci M.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>10.1109/IISEC69317.2026.11418411</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Proceedings - 5th International Conference on Informatics and Software Engineering, IISEC 2026</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>158-163</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105036002674?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>autonomous traffic monitoring, CNN-Transformer hybrid model, communication networks, deep learning, edge computing, intelligent transportation systems, multi-modal data fusion, real-time object detection, smart cities, UAV-IoT integration, Advanced traffic management systems, Aircraft detection, Antennas, Decision making, Highway traffic control, Internet of things, Modal analysis, Motor transportation, Network architecture, Object detection</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>The continued expansion of urban mobility and the growing complexity of connected transportation infrastructures have increased the need for real-time traffic monitoring and adaptive control mechanisms. In response to this demand, this work introduces a UAV-enabled intelligent traffic management framework that combines multi-modal deep learning with IoT-based communication networks to support dynamic traffic assessment and rapid incident response. A fleet of UAVs equipped with vision and MEMS-based sensors collects aerial observations, which are subsequently fused with data from ground-based IoT sensors to identify congestion patterns, roadway anomalies, and emerging hazards.</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: deep learning, model, transformer, detection, framework, cnn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Feasibility Analysis of Static-Image-Based Traffic Accident Detection Under Domain Shift for Edge-AI Surveillance Systems</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Wu C.-C.; Chen W.-C.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>10.3390/electronics15091803</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Electronics (Switzerland)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>9</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105038390346?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Multidisciplinary Digital Publishing Institute (MDPI)</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>domain shift, edge AI, feasibility study, intelligent transportation systems, static-image-based detection, Swin Transformer, traffic accident detection, Vision Transformer, Architectural design, Behavioral research, Decision making, Edge detection, Highway accidents, Highway traffic control, Image analysis, Intelligent systems, Intelligent vehicle highway systems, Motor transportation, Screening, Accident detections</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Traffic accident detection is a critical component of intelligent transportation systems (ITS), enabling timely incident response and traffic management. While most existing approaches rely on temporal information from video sequences, such methods are not always applicable in resource-constrained surveillance environments. This study investigates the feasibility of detecting traffic accidents from single static images by formulating the task as a binary classification problem.</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, model, models, transformer, classification, dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Maritime Cyber Security Platform (MCSP)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Laurenza G.; Tacconi R.; Dri M.; Landucci S.; Alì D.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>10.3233/PMST250137</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Progress in Marine Science and Technology</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1154-1163</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105016225511?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>IOS Press BV</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>cyber security, maritime, management, incident response, processes, artificial intelligence, framework</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>The Maritime Cyber Security Platform (MCSP) is an advanced, specialized security monitoring framework tailored specifically to the maritime domain. Its primary function is to collect and analyze data from a vessel’s digital systems. The platform is designed to identify anomalous activities and potential threats targeting onboard systems, thus enhancing the vessel’s overall cyber resilience.</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, incident response, processes, decision making.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>QuickSAT/SHERLOCK-MD, A System For Autonomous Operations And Health Management of Gateway</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Santangelo A.D.; Falco G.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>10.2514/6.2024-2417</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>AIAA SciTech Forum and Exposition, 2024</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85194191160?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>American Institute of Aeronautics and Astronautics Inc, AIAA</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Anomaly detection, Classification (of information), Decision support systems, Failure analysis, Fault detection, Knowledge based systems, Orbits, Risk assessment, Autonomous operations, Classification functions, Fault classification, Faults detection, Health management, Management functions, Operation management, Security risks, Vehicle health management, Vehicle management systems, NASA, management</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>sci_Zone, Inc and Cornell University are conducting research to develop QuickSAT/SHERLOCK-MD, a system for Vehicle Health Management and Fault Detection with Fault Classification Functions for the Gateway Lunar Platform. The QuickSAT/Vehicle Management System (VMS) is a flight proven flight management, Vehicle Health Management plus Fault Detection system flown on DARPA and U.S. Space Force flights.</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: models, artificial intelligence, classification, detection, anomaly detection, datasets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Deep Learning-Based Hyperparameter Optimization for Enhanced Segmentation of RGB Images in Oil Spill Detection Within Port Environments</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Kurah I.M.; Adamu S.; Alhussian H.; Alwadain A.; Aliyu D.A.; Mamman H.; Garba A.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>10.1109/ACCESS.2025.3599593</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>146052-146067</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105013795195?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Deep learning, Deeplab, drone imagery, hyperparameter optimization, oil spill detection, port environments, Aircraft detection, Convolution, Convolutional neural networks, Drones, Environmental protection, Learning algorithms, Learning systems, Network architecture, Oil spills, Semantic Segmentation, Semantic Web, Semantics, Transfer learning, Cross validation</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Accurate detection of oil spills in dynamic port environments remains critical for timely response and effective environmental protection. Recent studies have explored the application of deep learning models to high-resolution RGB imagery; however, challenges persist due to the complex visual characteristics of ports, including dynamic water surfaces, infrastructural occlusions, and heterogeneous backgrounds. Traditional detection approaches have demonstrated limited robustness under such conditions, often resulting in elevated rates of false positives and missed detections.</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: deep learning, detection, algorithms, model, models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Predicting the duration of motorway incidents using machine learning</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Corbally R.; Yang L.; Malekjafarian A.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>10.1186/s12544-024-00632-6</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>European Transport Research Review</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85185452067?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Springer Science and Business Media Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Classification, Incident duration, Incident management, Incident response, M50 motorway, Machine learning, Motorway operations, Regression, Road traffic collisions, Traffic incidents, Decision making, Forecasting, Highway administration, Highway planning, Learning algorithms, Learning systems, Motor transportation, Roads and streets, Driver's safety, Machine-learning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Motorway incidents are frequent &amp; varied in nature. Incident management on motorways is critical for both driver safety &amp; road network operation. The expected duration of an incident is a key parameter in the decision-making process for control room operators, however, the actual duration for which an incident will impact the network is never known with true certainty.</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, algorithms, classification, prediction, support vector machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Application of Fuzzy Decision Support System Based on GNN in Anomaly Detection and Incident Response Service of Intelligent Security</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Chen T.; Wu X.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>10.14569/IJACSA.2024.0150912</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>International Journal of Advanced Computer Science and Applications</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>9</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>112-121</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/86000672971?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Science and Information Organization</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>anomaly detection, fuzzy decision support system, GNN, incident response service, intelligent security, Complex relationships, Embedded representation, Graph data, Graph neural networks, Incident response, Robust systems, organization, processes, model, models, machine learning, deep learning, neural network, detection, datasets</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>This paper introduces a fuzzy decision support system (FDSS) based on a graph neural network (GNN) for anomaly detection and intelligent security. The primary aim is to develop a robust system capable of accurately identifying anomalies and providing timely incident response services. GNNs are utilized to capture the complex relationships and features between nodes in graph data, learning the embedded representation of each node through information transfer and aggregation mechanisms, which encapsulate the structural information of the graph.</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, anomaly detection, model, models, machine learning, deep learning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Decision Systems in Cybersecurity: A Synergy of AI and ML</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sharma R.; Sherje N.; Godbole A.; Shailesh; Deshmukh V.; Pandit P.V.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>10.1007/978-981-96-0143-1_42</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Smart Innovation, Systems and Technologies</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>527-535</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105002384135?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Springer Science and Business Media Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Cybersecurity, Decision systems, Incident response, Intrusion detection systems, Machine learning, Threat intelligence, Adversarial machine learning, Intrusion detection, Network intrusion, Cyber security, Cyber threats, Decision-making systems, Machine-learning, Making decision, Review papers, impact, management, processes, algorithms, model</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Cyber threats are becoming more frequent and complex, making decision systems crucial to cybersecurity. The review paper uses machine learning to examine decision systems and cybersecurity, highlighting its fundamentals, applications, and challenges. The paper begins with a detailed cybersecurity overview, emphasizing the need for strong decision-making systems to address changing threats.</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: algorithms, model, machine learning, detection, intrusion detection, datasets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Monitoring Incident Response Using Real-Time Analytics</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Mohanraj G.; Nadesh R.K.; Jagannathan J.; Adityan S.; Sathiyamoorthi V.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>10.1109/ITIKD63574.2025.11004824</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2nd International Conference on IT Innovations and Knowledge Discovery, ITIKD 2024</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105007528500?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>ARIMA, data analytics, Decision Tree, Facebook Prophet, Incident response, KNN, LSTM, machine learning, Random Forest, SVM, time series forecasting, Cyber attacks, Intelligent systems, Risk perception, Facebook, Machine-learning, Random forests, Prediction models, organizational, management</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>In today's digital landscape, rapid and effective incident response is crucial for maintaining organizational security against sophisticated cyber threats. This project explores the optimization of incident response processes through the implementation of advanced data analytics, machine learning, and time series forecasting algorithms. The system utilizes historical incident data along with advanced algorithms like ARIMA, Support vector machine, LSTM, KNN, Facebook Prophet, Decision Tree, and Random Forest to predict incident volumes, prioritize tickets, and evaluate RFC outcomes.</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: algorithms, models, machine learning, prediction, random forest, support vector machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Leveraging OSINT for Advanced Proactive Cybersecurity: Strategies and Solutions</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Avrahami Z.; Zwilling M.; Hajaj C.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>10.1109/ACCESS.2025.3603868</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>154229-154250</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105014630832?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>CTI, cyber threat intelligence, intelligence cycle, Open-source intelligence, OSINT, proactive cybersecurity, Artificial intelligence, Behavioral research, Cybersecurity, Data integration, Data reliability, Decision making, Open systems, Terrorism, Cybe threat intelligence, Cyber security, Cyber threats, Decisions makings, Open source intelligence, Cost effectiveness</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>The growing complexity of the digital environment has increased the need for proactive and intelligence-based approaches to cybersecurity. This study examines the role of open-source intelligence (OSINT) as a strategic tool in proactive cybersecurity operations. Drawing on a wide range of peer-reviewed literature and professional sources, it reviews definitions, operational processes, areas of application, benefits, and challenges associated with OSINT.</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: business, organizational, decision making, incident response, processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Novel Method of Improving Cybersecurity Posture with Real-Time Analytics in Security Operations Centers</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Boljam A.M.; Saini V.; Bojja S.G.R.; Mohammed H.U.H.; Alluri V.R.R.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>10.1109/ICCTDC64446.2025.11157987</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2025 International Conference on Computing Technologies and Data Communication, ICCTDC 2025</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105019060909?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>anomaly detection, automated decision-making, cybersecurity automation, Cybersecurity posture, data streams, data-driven security, false positive reduction, incident response, machine learning, operational efficiency, predictive analytics, real-time analytics, security infrastructure, Security Operations Centers (SOCs), threat detection, threat intelligence, Artificial intelligence, Automation, Behavioral research, Cybersecurity</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Cyberattacks become more widespread and sophisticated, cybersecurity is now at the forefront of concern for many organizations. Security Operations Centers (SOCs) are essential for their ability to monitor, detect, and respond to these threats. The problem is traditional methods are ineffective within SOCs due to large data volumes, complexities of the threat landscape, and slow time-to-response.</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: models, machine learning, artificial intelligence, detection, threat detection, anomaly detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Digital Twins for Incident Detection and Response</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Kampourakis K.E.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-92471-2_16</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Lecture Notes in Business Information Processing</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>548 LNBIP</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>197-206</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105005933537?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Springer Science and Business Media Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>critical infrastructure, Digital twin, incident detection, incident response, Critical infrastructures, Decision making, 'current, Cyber security, Cyber threats, Detection mechanism, Dynamic decision making, Infrastructure sector, Interconnectivity, Real time monitoring, Cyber attacks, machine learning, detection</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Digital Twin (DT) technology is revolutionizing critical infrastructure (CI) sectors by enabling real-time monitoring, predictive analytics, and dynamic decision-making. However, this increased interconnectivity and complexity also introduces significant cybersecurity challenges. The current work investigates the potential of DTs to enhance cybersecurity incident detection and response mechanisms for CI systems.</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, machine learning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Crisis Management Models for Cyberattacks Leveraging ML-Driven Detection Mechanisms</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Rani P.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>10.1109/WorldSUAS66815.2025.11199118</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2025 World Skills Conference on Universal Data Analytics and Sciences, WorldSUAS 2025</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105022281099?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Anomaly Detection, Crisis Management, Cyberattacks, Cybersecurity, Machine Learning, Threat Classification, Decision making, Information management, Learning systems, Network layers, Public works, Random forests, Zero-day attack, Cyber security, Cyber threats, Detection mechanism, Machine-learning, Management frameworks, Management Model, Threat classifications</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Cyber threats to critical infrastructure are getting ever more serious, which calls for efficient crisis management frameworks that would allow detecting, responding, and recovering swiftly. The research specifies an integrated model of responding to cyber crises in terms of the application of machine learning driven anomaly detection mechanisms. This framework utilizes anomaly detection, threat type identification, and risk ranking, in order to enhance the process of decision-making and make the automatic incident response possible.</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: models, detection, model, machine learning, classification, anomaly detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>On the Use of Artificial Intelligence in Cybersecurity Incident Investigations</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Gorda M.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>10.1109/SmartIndustryCon65166.2025.10986177</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Proceedings - 2025 International Russian Smart Industry Conference, SmartIndustryCon 2025</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>747-752</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105007160179?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>artificial intelligence, cybersecurity, digital forensics, incident investigation, Artificial life, Cyber attacks, Forensic engineering, Intelligent computing, Intelligent systems, Anomaly detection, Artificial intelligence techniques, Behaviour models, Cyber security, Cyber threats, Cyber-attacks, Decision support algorithms, Digital evidence, Information security incidents, Computer forensics, incident response</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>The increasing number of cyber threats significantly complicates the investigation of information security incidents. Traditional digital forensic methods face challenges due to the growing volume of data and the increasing sophistication of cyberattacks. This paper presents a decision-support algorithm designed to assist specialists in conducting efficient and accurate investigations using artificial intelligence techniques.</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, algorithm, algorithms, models, detection, anomaly detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>AI-Enhanced Automated Incident Response in SIEM with Explainability for SOC Analysts</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Charla R.R.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>10.1109/iSAI-NLP66160.2025.11320514</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2025 20th International Joint Symposium on Artificial Intelligence and Natural Language Processing, iSAI-NLP 2025</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105032722475?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Automation, Compliance, Cybersecurity, Explainable AI, Incident Response, Scalability, SIEM, SOC, Threat Detection, Artificial intelligence, Information management, Security systems, Centralised, Cyber security, Explainable artificial intelligence, Incident detection, Security information and event management systems, Security information and event managements, Security operation center, enterprise</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Security Information and Event Management (SIEM) systems have become the cornerstone of enterprise cybersecurity operations, providing centralized monitoring and incident detection. However, the increasing complexity of threats has outpaced manual Security Operations Center (SOC) workflows, leading to alert fatigue and slow response times. This paper explores the integration of artificial intelligence (AI) into automated incident response pipelines within SIEM systems, with a particular focus on explainability for SOC analysts.</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: incident response, soc, enterprise, management, security operations center.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>From Alert Fatigue to Augmented Defense: A Case for AI Copilots in Cybersecurity Operation Centers</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Akre V.; Kobbaey T.; Lazarov G.; Abdulsalam K.; Al-Sit W.; Diab J.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>10.1109/ITT69610.2025.11352895</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2025 10th International Conference on Information Technology Trends, ITT 2025</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>282-287</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105033661365?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>AI Copilot, Alert Fatigue, Cybersecurity Operations Centers (CSOCs), Explainable AI (XAI), Human–AI Collaboration, Incident Response, Security Operation Centers (SOCs), SOAR, Threat Detection, Artificial intelligence, Cybersecurity, Fatigue of materials, Network security, Security systems, Cyber security, Cybersecurity operation center, Operation center, Security operation center, Security orchestration, automation</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Cybersecurity Operations Centers (CSOCs) act as one of the foremost tools for cyber defenses. However, security analysts often face overwhelming stress owing to excessive volumes of alerts, frequent false positives flagged by most existing tools, and growing mental strain. Such challenges could negatively impact threat detections by delays that cause slower incident response; thus, undermining overall security effectiveness.</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: models, machine learning, artificial intelligence, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Evolution and Challenges of Security Operations Centers in the Digital Age</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Morocho-Sailema V.E.; Velasteguí H.J.; Jara-Elizalde Á.G.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-032-10310-9_3</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>EAI/Springer Innovations in Communication and Computing</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>29-39</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105031498339?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Springer Science and Business Media Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Cybersecurity, Digital defense, Incident response, Operational maturity, Threat detection, Artificial intelligence, Behavioral research, Digital twin, Economics, Human computer interaction, Information management, Investments, Network security, Security systems, Cyber security, Digital age, Digital environment, Exposed to, Maturity model, Security operation center</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>In an increasingly dynamic digital environment exposed to sophisticated threats, organizations face the challenge of comprehensively protecting their information assets. One key strategy involves the deployment of Security Operations Centers (SOC), which integrates people, processes, and technologies to detect, analyze, and respond to security incidents in real time. This article offers a critical narrative review of academic and technical publications from 2016 to 2025 on operational maturityOperational maturity models and conceptual frameworks that guide proactive threat detectionThreat detection.</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: organizational, management, governance, incident response, soc, processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Using the MITRE ATT&amp;CK Framework in SOC Ativities and Analyzing Cyber Attack</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Uralov J.; Abdullaeva S.; Risolat I.; Yusupova M.; Kutliev S.; Qazaqov M.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>10.1109/EDM65517.2025.11096745</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>International Conference of Young Specialists on Micro/Nanotechnologies and Electron Devices, EDM</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2160-2164</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105014152671?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>IEEE Computer Society</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Adversarial Tactics, Cyber Defense, Cyber Risk Mitigation, Cyber Threat Detection, Cybersecurity, Incident Response, MITRE ATT&amp;CK, Security Operations Center (SOC), Tactics Techniques and Procedures (TTPs), Threat Intelligence, Artificial intelligence, Computer crime, Crime, System-on-chip, Adversarial tactic, Cybe risk mitigation, Cybe threat detection, Cyber security, Cyber threats, Cyber-defense</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>The growing complexity of cyber threats demands advanced strategies to strengthen cybersecurity operations. The MITRE ATT&amp;CK Framework offers a systematic method for identifying, analyzing, and mitigating cyber-attacks within Security Operations Centers (SOCs). This paper examines how integrating the MITRE ATT&amp;CK Framework enhances SOC capabilities in threat detection, incident response, and overall cyber resilience.</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: framework, artificial intelligence, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Threat Vision: A Next-Generation SOC-Inspired Platform Leveraging Hybrid Malware Analysis and Real-Time Social Media Threat Intelligence for Enhanced Cybersecurity</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Harshith C.M.; Manohar N.; Venugopal S.; Kudroli A.; Jha N.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>10.1109/ICOIICS67115.2025.11390653</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Proceedings of the 4th International Conference on Intelligent Computing, Information and Control Systems, ICOIICS 2025</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>177-183</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105036680880?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Cybersecurity Automation, Deep Learning, Human-AI Collaboration, Hybrid Analysis, Machine Learning, Malware Detection, Network Security, Security Operations Centre (SOC), Sentiment Analysis, Social Media Threat Intelligence, Cybersecurity, Learning systems, Malware, Security systems, Cyber security, Machine-learning, Networks security, Security operation center, Social media, Social medium threat intelligence</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Cybersecurity threats, like malware and network breaches, are getting harder to manage. Therefore, need security that is both stronger and easier for every person to use. Typical Security Operation Centers work well, but they're expensive, which means only big companies can use them.</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: malware, machine learning, deep learning, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Air Traffic Control System Cyber Security Using Humans and Machine Learning</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Atkins G.; Sampigethaya K.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>10.1109/ICNS58246.2023.10124305</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Integrated Communications, Navigation and Surveillance Conference, ICNS</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2023-April</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85160613092?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>ADS-B, air traffic control, crew, cyber security, machine learning, Air navigation, Alarm systems, Control towers, Decision making, Air traffic control systems, Air traffic controller, Automatic dependent surveillance broadcasts, Cyber-attacks, Education and training, Human learning, Machine-learning, Performance, Cybersecurity, management, incident response</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Aviation performance depends on education and training of pilots and air traffic controllers (ATCOs) on technical, procedural, crisis management, decision making, leadership and communication skills. Recent incidents and studies, however, show crew members may be caught unaware and errors in human judgement can still occur in air traffic control (ATC) systems even more so in the presence of cyberattacks. This paper focuses on raising situation awareness and decision making of ATCOs with cyberattacks impacting operations in next-generation ATC systems.</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, decision making, incident response, cybersecurity management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Dynamic characterisation of cyberattacks based on the MITRE ATT&amp;CK framework applied to the optimisation of a mitigation selection process</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sánchez-Zas C.; Larriva-Novo X.; Villagrá V.A.; Solera-Cotanilla S.; Sanz-Rodrigo M.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>10.1016/j.future.2025.108272</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Future Generation Computer Systems</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>108272</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105030025553?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Elsevier B.V.</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Countermeasure selection, Cybersecurity, Machine learning, MITRE ATT&amp;CK, Support to decision making, TTPs, Artificial intelligence, Behavioral research, Decision making, Malware, Risk analysis, Risk management, Zero-day attack, Cyber security, Cyber-attacks, Decisions makings, Dynamic characterization, Machine-learning, Optimisations, TTP</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>The main cybersecurity challenges identified nowadays arise around the need to know information about cyberattacks, in order to characterise them and applying the most appropriate mitigation techniques according to their behaviour. Current advances in cybersecurity focus on the detection of zero-day attacks, adaptability to attackers’ behaviour, and automated incident response. However, this evolution should not oppose the proven need for defence-in-depth policy, collaboration, and information sharing that can help other organisations prepare for new cyberattacks.</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: framework, algorithm, model, machine learning, artificial intelligence, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Explainable AI for Malware Classification: Bridging the Gap Between Accuracy and Transparency</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Muça F.; Ahmad W.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Albania</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-032-07373-0_6</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Communications in Computer and Information Science</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2669 CCIS</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>79-99</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105021337689?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Springer Science and Business Media Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Cybersecurity, Explainable AI, Gradient Boosting, LIME, Machine Learning, Malware Classification, Model Interpretability, Random Forest, SHAP, Transparency, Adaptive boosting, Balancing, Barium compounds, Decision support systems, Decision trees, Learning systems, Logistic regression, Malware, Network security, Random forests</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (AI) has significantly improved malware classification by enhancing detection accuracy and efficiency. However, the opaque nature of many AI models presents a major challenge in cybersecurity, as security analysts often struggle to trust or fully understand the decisions made by these systems. This lack of transparency impedes adoption in real-world applications where explainability is crucial for risk assessment, incident response, and compliance.</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: classification, malware, model, models, machine learning, artificial intelligence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Combat Security Alert Fatigue with AI-Assisted Techniques</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ban T.; Samuel N.; Takahashi T.; Inoue D.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F38" t="n">
+        <v>50</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>10.1145/3474718.3474723</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ACM International Conference Proceeding Series</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>9-16</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85115272683?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Association for Computing Machinery</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>alert fatigue, Intrusion detection systems, security alert analysis, Intrusion detection, Fatigue problems, Management IS, Security alert analyse, Security alerts, Security experts, Security incident, Security information and event managements, Security products, Network security, enterprise, management, incident response, algorithms, artificial intelligence, dataset</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>The main challenge for security information and event management (SIEM) is to find critical security incidents among a huge number of false alerts generated from separate security products. To address the alert fatigue problem that is common for security experts operating the SIEM, we propose a new alert screening scheme that leverages artificial intelligence (AI)-assisted tools to distinguish actual threats from false alarms without investigating every alert. The proposed scheme incorporates carefully chosen learning algorithms and newly designed visualization tools to facilitate speedy alert analysis and incident response.</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: algorithms, artificial intelligence, detection, intrusion detection, dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Improved Detection and Response via Optimized Alerts: Usability Study</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>McRee G.R.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>10.3390/jcp2020020</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Journal of Cybersecurity and Privacy</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>379-401</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85180125257?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Multidisciplinary Digital Publishing Institute (MDPI)</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>data science, detection, security alert, text alert output, user acceptance, user experience, visual alert output, visualization, impact, incident response, soc, model, models, machine learning</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Security analysts working in the modern threat landscape face excessive events and alerts, a high volume of false-positive alerts, significant time constraints, innovative adversaries, and a staggering volume of unstructured data. Organizations thus risk data breach, loss of valuable human resources, reputational damage, and impact to revenue when excessive security alert volume and a lack of fidelity degrade detection services. This study examined tactics to reduce security data fatigue, increase detection accuracy, and enhance security analysts’ experience using security alert output generated via data science and machine learning models.</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, model, models, machine learning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Predicting Crash-Related Incident Clearance Time on Louisiana’s Rural Interstate Using Ensemble Tree-Based Learning Methods</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Khan W.A.; Moomen M.; Rahman M.A.; Terkper K.A.; Codjoe J.; Gopu V.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F40" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>10.3390/app142310964</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Applied Sciences (Switzerland)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>23</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>10964</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85212441380?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Multidisciplinary Digital Publishing Institute (MDPI)</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>incident clearance time, machine learning, rural interstate, SHAP analysis, Adaptive boosting, Highway accidents, Highway administration, Truck transportation, Gradient boosting, Incident duration, Light gradients, Louisiana, Machine-learning, Rural interstates, Shapley, Shapley additive explanation analyze, Traffic crashes, Traffic congestion, incident response, models</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Traffic crashes contribute significantly to non-recurrent congestion, thereby increasing delays, congestion pollution, and other challenges. It is important to have tools that enable accurate prediction of incident duration to reduce delays. It is also necessary to understand factors that affect the duration of traffic crashes.</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: models, machine learning, prediction, model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SMS-I: Intelligent Security for Cyber–Physical Systems</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Maia E.; Sousa N.; Oliveira N.; Wannous S.; Sousa O.; Praça I.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>10.3390/info13090403</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Information (Switzerland)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>9</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85138752924?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>MDPI</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>cyber–physical systems, cyber–physical systems forensics, digital forensics, machine learning, rule mining, security incident response, Computer crime, Computer forensics, Critical infrastructures, Cybersecurity, Decision making, E-learning, Public works, Cybe-physical systems, Cybe–physical system forensic, Incident response, Machine-learning, Security incident, society, impact</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Critical infrastructures are an attractive target for attackers, mainly due to the catastrophic impact of these attacks on society. In addition, the cyber–physical nature of these infrastructures makes them more vulnerable to cyber–physical threats and makes the detection, investigation, and remediation of security attacks more difficult. Therefore, improving cyber–physical correlations, forensics investigations, and Incident response tasks is of paramount importance.</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, artificial intelligence, classification, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ARCS: Adaptive Reinforcement Learning Framework for Automated Cybersecurity Incident Response Strategy Optimization</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ren S.; Jin J.; Niu G.; Liu Y.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F42" t="n">
+        <v>20</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>10.3390/app15020951</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Applied Sciences (Switzerland)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85215680132?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Multidisciplinary Digital Publishing Institute (MDPI)</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>automated incident response, cybersecurity optimization, reinforcement learning, security event analytics, Adversarial machine learning, Adaptive reinforcement, Cyber security, Incident response, Optimisations, Reinforcement learnings, Response strategies, Security event analytic, Security events, Cyber attacks, process, dataset, framework</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>The increasing sophistication and frequency of cyber attacks necessitate automated and intelligent response mechanisms that can adapt to evolving threats. This paper presents ARCS (Adaptive Reinforcement learning for Cybersecurity Strategy), a novel framework that leverages deep reinforcement learning to optimize automated incident response strategies in cybersecurity systems. Our approach uniquely combines state representation learning of security events with a hierarchical decision-making process to map attack patterns to optimal defense measures.</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: framework, machine learning, dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ensemble-Based Intrusion Detection Enhanced with LLM-Driven Incident Response Automation</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Thumala S.R.; Mane V.; Inamdar C.; Pethkar P.; Poke A.; Patil R.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>10.1109/I4Tech64670.2025.11277913</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2025 3rd International Conference on Industry 4.0 Technology, I4Tech 2025</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105031115669?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>cybersecurity automation, incident response, Intrusion detection, LangChain, random forest, REST API, XGBoost, Artificial intelligence, Automation, Computer crime, Cybersecurity, Decision making, Learning systems, Network security, Cyber security, Intrusion-Detection, Random forests, Response systems, Threat detection, model</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Traditional incident response systems lack adaptability and autonomous decision-making, limiting their effectiveness against sophisticated cyber threats. A modular AI framework is implemented to address this challenge by integrating ensemble-based binary intrusion detection and multiclass attack classification with real-time automation. Using the UNSW-NB15 dataset, Random Forest, XGBoost, and LightGBM models are trained for binary threat detection, followed by classification into nine attack categories.</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, intrusion detection, model, models, artificial intelligence, classification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>A Practical Approach to Defining a Framework for Developing an Agentic AIOps System</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Zota R.D.; Bărbulescu C.; Constantinescu R.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F44" t="n">
+        <v>10</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>10.3390/electronics14091775</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Electronics (Switzerland)</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>9</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1775</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105004831302?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Multidisciplinary Digital Publishing Institute (MDPI)</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Agentic AIOps, AI-driven agents, AIOps, ITIL, MLOps, PRM-IT, Empowerment of personnel, Human resource management, Information management, Predictive maintenance, Agentic artificial intelligence for IT operation, AI-driven agent, AIOp, Information technology infrastructure, Information technology infrastructure library, MLOp, Operation system, Process reference model for IT, Process reference models, Work-flows</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>The increasing complexity of IT operations necessitates advanced automation to ensure system availability, resilience, continuity, performance, security, and maintainability. Traditional IT management frameworks, such as the Information Technology Infrastructure Library (ITIL), have standardized service management processes, while models like IBM’s Process Reference Model for IT (PRM-IT) have facilitated automation through structured workflows. However, critical tasks, such as incident resolution and problem management, still require significant human intervention.</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: enterprise, management, decision making, incident response, process, processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Human Factors in AI-Driven Cybersecurity: Cognitive Biases and Trust Issues</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Hagen R.A.; Øverlier L.; Helkala K.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>10.1145/3759260</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Digital Threats: Research and Practice</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>4</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105026323076?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Association for Computing Machinery</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>AI (XAI), alert fatigue, automation bias, bias mitigation, cognitive biases, confirmation bias, dual-process theory, false positives, human–AI collaboration, incident response workflows, model interpretability, practitioner perspectives, security operations centers (SOC), trust calibration, Artificial intelligence, Automation, Cybersecurity, Human computer interaction, Human engineering, Cognitive bias</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>The integration of AI in cybersecurity promises enhanced threat detection and response capabilities, yet its adoption is hindered by human factors, particularly cognitive biases and trust issues. This study investigates how cognitive biases, such as automation bias (47%) and confirmation bias (37%), influence security analysts’ trust in AI-driven tools, drawing on Kahneman’s dual-process theory. Through qualitative interviews with 19 cybersecurity professionals and a comparative analysis of AI solutions from Microsoft, CrowdStrike, Darktrace, and IBM, we identify key barriers to adoption, including explainability gaps and high false positive rates.</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, models, artificial intelligence, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AutoSOC Cyber Analyst (ASOC-CA): Using AI to Automate SOC Tier 1 &amp; 2 Activities</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Mihalopoulos I.; Ngo-Antonio J.-R.; Pugh M.; Neal D.; Cao Y.; Watkins L.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>10.1109/CCWC67433.2026.11393893</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026 IEEE 16th Annual Computing and Communication Workshop and Conference, CCWC 2026</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>519-525</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105035592886?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Advanced Persistent Threat (APT) Detection, Artificial Intelligence (AI), Machine Learning (ML), MITRE ATT&amp;CK, Security Information and Event Management (SIEM), Cybersecurity, Learning systems, Machine learning, Network security, Public works, Advanced persistent threat detection, Artificial intelligence, Artificial intelligence systems, Incident response, Machine-learning, Security information and event management, Security information and event managements, Threat detection, Information management, organizational</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hackers are now beginning to use artificial intelligence (AI) to expand the capabilities and sophistication of their attacks, creating challenges for network owners. As state-sponsored adversaries and advanced persistent threats (APTs) utilize AI to their advantage, network owners must evolve concurrently to address the emergent threat landscape shaped by advanced AI systems. Thus, in this paper, we propose an end-to-end Machine Learning Framework to automate and strengthen cybersecurity operations.</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, machine learning, artificial intelligence, detection, threat detection, framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>From Vulnerability to Defense: The Role of Large Language Models in Enhancing Cybersecurity</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Kasri W.; Himeur Y.; Alkhazaleh H.A.; Tarapiah S.; Atalla S.; Mansoor W.; Al-Ahmad H.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Palestine</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F47" t="n">
+        <v>67</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>10.3390/computation13020030</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>2</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85219181500?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Multidisciplinary Digital Publishing Institute (MDPI)</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>cybersecurity, deep learning, intrusion detection, large language models, malware detection, phishing attack detection, organizational, management, incident management, incident response, detection, threat detection, phishing, malware, datasets, bert</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>The escalating complexity of cyber threats, coupled with the rapid evolution of digital landscapes, poses significant challenges to traditional cybersecurity mechanisms. This review explores the transformative role of LLMs in addressing critical challenges in cybersecurity. With the rapid evolution of digital landscapes and the increasing sophistication of cyber threats, traditional security mechanisms often fall short in detecting, mitigating, and responding to complex risks.</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: models, deep learning, detection, threat detection, intrusion detection, phishing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Toward Robust Security Orchestration and Automated Response in Security Operations Centers with a Hyper-Automation Approach Using Agentic Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ismail; Kurnia R.; Brata Z.A.; Nelistiani G.A.; Heo S.; Kim H.; Kim H.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>10.3390/info16050365</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Information (Switzerland)</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>5</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105006586264?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Multidisciplinary Digital Publishing Institute (MDPI)</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>agentic-LLM, hyper-automation, incident-response, security operation center, SOAR, Intelligent systems, Agentic-large language model, Automated response, Cyber security, Incident response, Language model, Robust security, Security orchestration, automation, and response, Threats mitigations, Cyber attacks, soc, models, detection</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>The evolving landscape of cybersecurity threats demands the modernization of Security Operations Centers (SOCs) to enhance threat detection, response, and mitigation. Security Orchestration, Automation, and Response (SOAR) platforms play a crucial role in addressing operational inefficiencies; however, traditional no-code SOAR solutions face significant limitations, including restricted flexibility, scalability challenges, inadequate support for advanced logic, and difficulties in managing large playbooks. These constraints hinder effective automation, reduce adaptability, and underutilize analysts’ technical expertise, underscoring the need for more sophisticated solutions.</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, model, models, detection, threat detection, framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Empowering Security Operation Center with Artificial Intelligence and Machine Learning - A Systematic Literature Review</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Khayat M.; Barka E.; Adel Serhani M.; Sallabi F.; Shuaib K.; Khater H.M.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F49" t="n">
+        <v>34</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>10.1109/ACCESS.2025.3532951</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>19162-19197</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85216406598?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Artificial intelligence, cyber threats, cybersecurity, healthcare security, incident response, machine learning, neural networks, next-generation SOC, security operation center, threat detection, Cyber security, Machine-learning, Neural-networks, Next-generation security operation center, Adversarial machine learning, sector, organizational, soc, model, deep learning</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Organizational cybersecurity relies heavily on security operation centers (SOCs) to protect businesses and institutions from emerging cyber threats. In recent years, the complexity and sophistication of cyber threats have increased, pushing SOCs to their limits. As a result, SOCs struggle to address the evolving threat landscape due to their reliance on isolation technologies and reactive strategies.</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, artificial intelligence, model, deep learning, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Finding Harmony in the Noise: Blending Security Alerts for Attack Detection</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Roelofs T.-M.; Barbaro E.; Pekarskikh S.; Orzechowska K.; Kwapień M.; Tyrlik J.; Smadu D.; Van Eeten M.; Zhauniarovich Y.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>10.1145/3605098.3635981</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Proceedings of the ACM Symposium on Applied Computing</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1385-1394</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85197686498?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Association for Computing Machinery</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>intrusion detection, machine learning, security alert integration, Blending, Integration, Personnel training, Security systems, Attack detection, End to end, Global organization, Intrusion-Detection, Machine-learning, Medium sized organizations, Securities analysts, Security alerts, Security detection systems, global, organization, incident response, soc</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Large- and medium-sized organizations employ various security systems to protect their assets. These systems, often developed by different vendors, focus on different threats and usually work independently. They generate separate and voluminous alerts that have to be monitored and analyzed by often overburdened security analysts.</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, model, machine learning, intrusion detection, dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Explainable Intelligence and LLM-Based Secure Framework for Industrial Internet of Things</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Mehta D.; Patel C.; Shah M.; Shah A.; Gupta R.; Tanwar S.; Alabdulatif A.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>10.1109/MNET.2025.3637291</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>IEEE Network</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105030704925?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Artificial intelligence, Electronic data interchange, Internet of things, Learning systems, Network security, Decision-making process, Human intervention, Language model, Machine-learning, Manual labors, Model-based OPC, Real-time data exchange, Security frameworks, Security vulnerabilities, Threat identification, Complex networks, Decision making, incident response, processes, model</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>The Industrial Internet of Things (IIoT) is transforming the industrial landscape by enabling real-time data exchange and automation, reducing the need for human intervention and enhancing accuracy beyond manual labor. However, this interconnectedness creates a vast assortment of security vulnerabilities, ranging from device-level attacks to a complex nexus of network breaches. This paper introduces a comprehensive security framework utilizing Machine Learning (ML) for smart threat identification and Explainable AI (XAI) to improve transparency and build trust in decision-making processes.</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: framework, model, models, machine learning, artificial intelligence, prediction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Machine Learning-Based Alert Correlation for Enhanced Cybersecurity: A Multi-Classification Approach</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Diakhame M.L.; Diallo C.; Mejri M.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>10.1109/CSNet67572.2025.11288163</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2025 9th Cyber Security in Networking Conference: GenAI and Cybersecurity, CSNet 2025</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105032100549?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Alert Correlation, Classification, Cybersecurity, Incident Response, Machine Learning, SIEM, Convolutional neural networks, Learning algorithms, Learning systems, Logistic regression, Network security, Pattern recognition, Security systems, Support vector regression, Classification approach, Cyber security, Machine-learning, Multi-classification, Performance, Random forests</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Modern Security Operations Centers (SOCs) struggle with an overwhelming influx of security alerts from diverse sources, leading to alert fatigue and delayed incident response times. Conventional Security Information and Event Management (SIEM) systems typically process alerts in isolation, missing complex attack patterns that unfold across multiple detection points. This research introduces a comprehensive machine learning framework for intelligent alert correlation using three classification approaches: binary correlation detection, correlation type classification, and incident classification.</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, classification, algorithms, models, detection, dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Enhancing Urban Resilience in Smart Cities Through Edge AI, Point of Interest Analysis, and Multi-Criteria Decision-Making</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ke C.-K.; Wu M.-Y.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>10.1109/IS3C65361.2025.11130986</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>IS3C 2025 - International Symposium on Computer, Consumer and Control</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105016200881?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>edge artificial intelligence, multi-criteria decision analysis, point of interest, smart city, urban resilience, Analytic hierarchy process, Artificial intelligence, Decision support systems, Disaster prevention, Distributed computer systems, Emergency services, Information services, Information use, Network security, Quality of service, Multi criteria decision-making, Multicriteria decision-making, Multicriterion decision makings, Real- time, Service oriented computing</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>In today's urban environment, where extreme weather, epidemic outbreaks, and social security threats are frequent, the construction of smart cities must focus not only on efficiency and convenience but also on defensive resilience to handle crises effectively. This study proposes an innovative information service architecture that integrates edge artificial intelligence (Edge AI), point of interest (POI) analysis, and multi-criteria decision analysis (MCDA) to enhance early warning and solution recommendation processes for smart city incidents. The proposed system will identify critical POI maps in the city through POI risk analysis.</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: decision making, management, incident response, process, processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Strategic cyber threat intelligence: Building the situational picture with emerging technologies</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Voutilainen J.; Kari M.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F54" t="n">
+        <v>4</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>10.34190/EWS.20.030</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>European Conference on Information Warfare and Security, ECCWS</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2020-June</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>545-553</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85094639017?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Curran Associates Inc.</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Machine Learning, Strategic Cyber Threat Intelligence, Crime, Cybersecurity, Decision making, Large dataset, Malware, Network security, Cyber threats, Cyber-attacks, Cyberspaces, Decisions makings, Emerging technologies, Incident response, Large organizations, Machine-learning, Strategic cybe threat intelligence, Tacticals, impact</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>In 2019, e-criminals adopted new tactics to demand enormous ransoms from large organizations by using ransomware, a phenomenon known as “big game hunting.” Big game hunting is an excellent example of a sophisticated and coordinated modern cyber-attack that has a significant impact on the target. Cyber threat intelligence (CTI) increases the possibilities to detect and prevent cyber-attacks and gives defenders more time to act. CTI is a combination of incident response and traditional intelligence.</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, artificial intelligence, detection, malware, ransomware, dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Optimization and Implementation of Network Security Incident Handling Process Based on Secure Arrangement</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ni L.; Qian Y.; Zhang S.; Tong S.; Bao C.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>10.1109/ICSECE61636.2024.10729589</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2024 IEEE 2nd International Conference on Sensors, Electronics and Computer Engineering, ICSECE 2024</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>472-478</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85209679637?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Automation, Configuration management, Network security incident, Security arrangement, Decision making, Network security, Resource allocation, Risk management, Handling process, In networks, Incident response, Innovative solutions, Integrating security, Network security incidents, Optimisations, Process-based, Security arrangements, Network intrusion, management, incident management</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>This article addresses the issues of low efficiency and fragmented processes in network security incident response, proposing an innovative solution that utilizes security orchestration technology to optimize the handling process and achieve automation. Through an analysis of existing processes, the limitations of traditional methods are clearly defined. The research elaborates on the principles of security orchestration technology, including its advantages in integrating security tools and designing automated processes.</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: process, management, decision making, incident management, incident response, processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>A Context-Aware, AI-Driven Load Balancing Framework for Incident Escalation in SOCs</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Abuaziz A.; Celiktas B.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>10.1109/ISAS66241.2025.11101733</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>ISAS 2025 - 9th International Symposium on Innovative Approaches in Smart Technologies, Proceedings</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105014912764?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>AI-driven incident escalation, context-aware assignment, escalation, load balancing, security operation center, Artificial intelligence, Computational methods, Programmable logic controllers, System-on-chip, Context-Aware, Cyber-attacks, Incident escalations, Incident Management, Load-Balancing, Rule based, Resource allocation, organizational, management, incident response, soc</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SOCs face growing challenges in incident management due to increasing alert volumes and the complexity of cyberattacks. Traditional rule-based escalation models often fail to account for the workload of the analyst, the severity of the incident, and the organizational context. This paper proposes a context-aware, AI-driven load balancing framework for intelligent analyst assignment and incident escalation.</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: organizational, management, incident management, incident response, soc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Cyber-DRIVE: Dynamic Risk Versatile Engine for Cyber Security Risk Analysis, Situational Awareness and Incident Response</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Solari S.; Pedrotti U.; Castelli E.; Ceccoli G.; Oneto A.; Russo E.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>CEUR Workshop Proceedings</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>3962</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105005824952?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>CEUR-WS</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Cyber Threat Intelligence, Cybersecurity Ontology, Dynamic Risk Analysis, Kill Chain Generation, Markov Decision Process, Security Mechanisms, Situational Awareness, Threat Propagation, Cyber attacks, Intelligent systems, Markov processes, Risk analysis, Cybe threat intelligence, Cyber security, Cyber threats, Dynamic risk analyze, Dynamic risks, Kill chain, Markov Decision Processes, Ontology's</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>In dynamic and regulated critical environments, continuously assessing cyber risks is essential for effective situational awareness and decision-making. While methodologies like Security Risk Analysis (SRA) and Threat Assessment and Remediation Analysis (TARA) provide structured approaches, they often lack dynamic updates, real-time threat modeling, and advanced visualization capabilities. This paper introduces Cyber-DRIVE, a novel framework for dynamic risk analysis, incident response, and situational awareness.</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: incident response, business, soc, process, processes, decision making.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>European framework and proofs-of-concept for the intelliGent aUtomAtion of cybeR Defence Incident mAnagemeNt</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Garcia Cid M.I.; Gil Perez M.; Jorquera Valero J.M.; Lopez Martinez A.; Maestre Vidal J.; Martinez Perez G.; Garcia L.M.; Plaza F.M.; Nespoli P.; Galindo J.P.; Ramon Y Cajal Ramo P.J.; Rodriguez Lopez F.A.; Sanchez Sanchez P.M.; Sotelo Monge M.A.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>10.23919/JNIC58574.2023.10205559</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2023 JNIC Cybersecurity Conference, JNIC 2023</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85168999556?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Cyber defence, Incident management, Automation, Cybersecurity, Decision making, Automatic Detection, Automatic response, Cyber-defense, Defense response, Incident response, Intelligent automation, Proof of concept, Security challenges, Semi-automatics, detection, framework</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence and Automation are revolutionizing cyber defence and incident response by addressing traditional inefficiencies and enabling faster and easier incident resolutions. However, challenges arise in cyber response. The European framework and proofs-of-concept for the EUGUARDIAN project aims to develop a reliable AI-based solution focusing on semi-automatic or automatic detection, mitigation, and response to security challenges, supporting analysts and decision-makers, enhancing cyber situational awareness and military infrastructure resilience.</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, incident management, decision making, incident response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Dynamic Playbooks Quality Metrics</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Zolotarev V.; Oleynikova A.; Zakhir B.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>10.1109/SmartIndustryCon61328.2024.10516048</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Proceedings - 2024 International Russian Smart Industry Conference, SmartIndustryCon 2024</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>249-254</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85193226888?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>continuous detection and response, decision support system, dynamic playbook, incident, information security incidents, investigation, quality metrics, Artificial intelligence, Information management, Security of data, Continuous detections, Control objects, Dynamic controls, Incident response, Quality metrices, Decision support systems, organizational, management, processes, algorithms</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>The text discusses the challenges and solutions related to dynamic control objects in the task of information security monitoring. New approaches for data collection and analysis, as well as the development of methods for creating dynamic incident response scenarios (playbooks), are highlighted. The focus is on resolving these challenges through the creation of applicable algorithms, models, methods, and security management approaches, including at the level of organizational processes, data handling, and formation of the organization's information security architecture.</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: organizational, management, incident response, processes, organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>A collaborative cybersecurity framework for higher education</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Otoom A.A.; Atoum I.; Al-Harahsheh H.; Aljawarneh M.; Al Refai M.N.; Baklizi M.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>10.1108/ICS-02-2024-0048</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Information and Computer Security</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>3</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>362-389</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85204036386?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Emerald Publishing</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Collaboration, Incident Response:, Cybersecurity, Design Science Research (DSR), Higher education, Organizational Learning The-ory (OLT), Decision making, Electronic design automation, Emotional intelligence, Energy policy, Intelligent systems, International cooperation, Knowledge acquisition, Problem solving, Risk management, Structural analysis, Structural dynamics, Systems analysis, Cyber security, Design science research</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Purpose: The purpose of this paper is to present the educational computer emergency response team (EduCERT) framework, an integrated response mechanism to bolster national cybersecurity through collaborative efforts in the higher education sector. The EduCERT framework addresses this gap by enhancing cyber security and mitigating cybercrime through collaborative incident management, knowledge sharing and university awareness campaigns. Design/methodology/approach: The authors propose an EduCERT framework following the design science methodology.</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Clasificado como Macro por coincidencias en metadatos: countries, national, international, global, sector, policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Enhancing Traffic Incident Management and Regulatory Compliance Using IoT and Itms: A Mumbai Traffic Police Case Study</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Salunke S.J.; Bang S.S.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F61" t="n">
+        <v>5</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>10.1109/TQCEBT59414.2024.10545276</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>TQCEBT 2024 - 2nd IEEE International Conference on Trends in Quantum Computing and Emerging Business Technologies 2024</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85204442670?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, City Surveillance System, Computational Intelligenc, Intelligent Transportation Systems, Internet of Things, Mumbai Traffic Management, Advanced traffic management systems, Air traffic control, Decision making, Emergency traffic control, Energy security, Financial markets, Highway administration, Highway traffic control, Information systems, Motor transportation, Nanotechnology, Urban transportation, Incident Management, Incident reports</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>In the rapidly urbanizing landscape of Mumbai, a megacity confronted with significant traffic management and law enforcement challenges, the deployment of an advanced city surveillance system represents a transformative approach to urban governance. This paper examines the integration of over 11,000 CCTV cameras into the Mumbai Traffic Police's operational framework, covering an area of 438 square kilometers encompassing 41 traffic divisions and 94 police stations. Since its inception in 2016, the system has been pivotal in enhancing safety, order, and mobility within the city, especially amid obstacles such as ongoing infrastructure projects, traffic congestion, accidents, and natural...</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, incident management, governance, decision making, incident response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Coordinating Incident Response and Risk Management for Enhanced Cybersecurity: A Comprehensive Analysis</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Loganathan S.; Jayaprakash M.; Gunasekaran K.; Shanmugam R.; Vinoth D.; Agoramoorthy M.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>10.1109/ICCDS64403.2025.11209412</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2025 2nd International Conference on Computing and Data Science, ICCDS 2025</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105023825218?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>AI in Cybersecurity, Automated Risk Assessment, Cybersecurity, Incident Response, Real-Time Monitoring, Risk Management, Threat Detection, Artificial intelligence, Decision making, Human resource management, Network security, Real time systems, Risk analysis, Risk assessment, Cyber security, Incident Response Management, Real time monitoring, Risks assessments, Risks management, management</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>The increasing complexity and frequency of cyber threats have made coordinated incident response and risk management essential components of robust cybersecurity frameworks. This research explores the integration of incident response protocols with risk management strategies to enhance the overall cybersecurity posture of organizations. Through a combination of qualitative and quantitative methods, including case studies, interviews with cybersecurity professionals, and analysis of security incident reports, this study investigates how effective collaboration between these two domains can mitigate the impacts of cyber incidents and improve recovery times.</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, incident response, risk management, decision making, process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Incident Response in Smart Agriculture: An MQTT Case Study</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Rudrakar S.; Rughani P.H.; Sadineni L.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>10.1109/ICCCNT61001.2024.10723835</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2024 15th International Conference on Computing Communication and Networking Technologies, ICCCNT 2024</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85212833348?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Agricultural Internet of Things (Ag-IoT), Incident Response Model, Internet of Things, IoT Security, MQTT Protocol, Smart Agriculture, Quality of service, Agricultural internet of thing, Agriculture systems, Case-studies, Incident response, Internet of thing security, Message queuing telemetry transport protocol, Response model, Smart agricultures, Transport protocols, impact, management, decision making, algorithms</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>The integration of Internet of Things (IoT) technology into agriculture has significantly enhanced farm management and productivity. The Message Queuing Telemetry Transport (MQTT) protocol, pivotal in this transformation, facilitates communication among IoT devices and decision making systems. Being a cost-effective and time-effective system, Ag-IoT is prone to attacks due to its inherent vulnerabilities and weak security policies.</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: algorithms, model, machine learning, datasets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>A Deep Learning-Based Dual-Model Framework for Real-Time Malware and Network Anomaly Detection with MITRE ATT&amp;CK Integration</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Migara H.M.S.; Sandakelum M.D.B.; Maduranga D.B.W.N.; Kumara D.D.K.C.; Fernando H.; Abeywardena K.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>10.14569/IJACSA.2025.0160728</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>International Journal of Advanced Computer Science and Applications</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>7</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>267-272</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105015663861?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Science and Information Organization</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Cybersecurity, deep learning, feedforward neu-ral network, generative adver-sarial networks, malware detection, MITRE ATT&amp;CK, Anomaly detection, Computer viruses, Intrusion detection, Learning systems, Network security, Neural networks, Open systems, Cyber security, Feed forward, Generative adver-sarial network, Network anomaly detection, Real- time, Threat detection, organization</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>The contemporary world of high connectivity in the digital realm has presented cybersecurity with more advanced threats, such as advanced malware and network attacks, which in most cases will not be detected using traditional detection tools. Static cybersecurity tools, which are traditional, often fail to deal with dynamic and hitherto unseen attacks, including signature-based antivirus systems and rule-based intrusion detection. To ad-dress this issue, we would suggest a two-part, AI-powered solution to cybersecurity which would allow real-time threat detection on an endpoint and a network level.</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, deep learning, detection, anomaly detection, malware, framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LINKING EXPLOITS FROM THE DARK WEB TO KNOWN VULNERABILITIES FOR PROACTIVE CYBER THREAT INTELLIGENCE: AN ATTENTION-BASED DEEP STRUCTURED SEMANTIC MODEL1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Samtani S.; Chai Y.; Chen H.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F65" t="n">
+        <v>71</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>10.25300/MISQ/2022/15392</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>MIS Quarterly: Management Information Systems</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>2</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>911-946</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85180129352?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>University of Minnesota</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>cybersecurity, cybersecurity analytics, dark web, design science, hacker forums, online hacker community, Deep learning, Denial-of-service attack, Design, Personal computing, Risk management, SCADA systems, Semantics, Cyber security, Cyber threats, Cybersecurity analytic, Hacker communities, Hacker forum, Semantic modelling, global</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Black hat hackers use malicious exploits to circumvent security controls and take advantage of system vulnerabilities worldwide, costing the global economy over $450 billion annually. While many organizations are increasingly turning to cyber threat intelligence (CTI) to help prioritize their vulnerabilities, extant CTI processes are often criticized as being reactive to known exploits. One promising data source that can help develop proactive CTI is the vast and ever-evolving Dark Web.</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, incident response, processes, risk management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Ai/ml in security orchestration, automation and response: Future research directions</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Kinyua J.; Awuah L.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F66" t="n">
+        <v>68</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>10.32604/iasc.2021.016240</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Intelligent Automation and Soft Computing</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>2</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>527-545</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85104849905?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Tech Science Press</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Deep learning, Deep reinforcement learning, Incident response, Machine learning, Security automation, Security management, Security orchestration, Security orchestration and automation, SOAR, industry, soc, processes, detection, threat detection</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Today’s cyber defense capabilities in many organizations consist of a diversity of tools, products, and solutions, which are very challenging for Security Operations Centre (SOC) teams to manage in current advanced and dynamic cyber threat environments. Security researchers and industry practitioners have proposed security orchestration, automation, and response (SOAR) solutions designed to integrate and automate the disparate security tasks, processes, and applications in response to security incidents to empower SOC teams. The next big step for cyber threat detection, mitigation, and prevention efforts is to leverage AI/ML in SOAR solutions.</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, deep learning, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Harmonizing paradoxical tensions in SOCs: A Strategic model for integrating AI, automation, and human expertise in cyber defense and incident response</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Saadallah M.; Shahim A.; Khapova S.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>10.24251/hicss.2025.738</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Proceedings of the Annual Hawaii International Conference on System Sciences</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>6171-6180</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105005142692?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>IEEE Computer Society</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Automation, Cybernetics, Paradoxical Tensions, Security Operations Centers, Artificial life, Cyber attacks, Decision theory, Intelligent computing, Neural networks, Risk perception, Robotics, Cyber-attacks, Cyber-defense, Defense response, Human expertise, Incident response, Paradoxical tension, Private industries, Research advances</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Security operations centers (SOCs) from public and private industries are under pressure to cope with the surge of cyberattacks, making paradoxical tensions in strategic navigation within security operations centers (SOCs) a priority. Our research advances our understanding of ambidexterity in the cybersecurity field and introduces an equilibrium path for adaptability, consistency, expediency, and authority paradoxes through the strategic integration of artificial intelligence (AI), automation, and human expertise. We developed a conceptual model that incorporates insights from the identified paradoxical tensions, cybernetic, organizational paradox, complexity, and decision-making theories,...</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, artificial intelligence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>A Conceptual Framework to Leverage Heuristics for Effective Human-Machine Collaboration in Incident Handling</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Gurabi M.A.; Mansoor M.U.; Matzutt R.; Mandal A.; Decker S.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-87760-5_3</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Lecture Notes in Computer Science</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>15595 LNCS</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>18-35</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105012919945?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Springer Science and Business Media Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Human-machine Teaming, Incident Handling, Incident Response, Cybersecurity, Decision making, Learning systems, Machine learning, Man machine systems, Phishing, Conceptual frameworks, Cyber security, High-accuracy, Human-machine, Human-machine collaboration, Levels of automation, Machine-learning, Heuristic methods, process, model, classification</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Managing cybersecurity incidents increasingly depends on advanced levels of automation. However, human involvement remains essential due to the need for high accuracy and the risk of severe damage. Therefore, incident response requires a high degree of human-machine teaming to both simplify the complexity of modern incident handling tasks and ensure a reliable decision-making process.</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: framework, model, machine learning, classification, detection, phishing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>UrbanSense: A Multimodal Spatio-Temporal Neural Framework for Real-Incident Detection and Response Prioritization in Smart Cities</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Preethi M.S.; Sarnika Raj D.; Vedhavathy T.R.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>10.1109/ICMSCI67830.2026.11469758</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Proceedings of 2nd International Conference on Multi-Agent Systems for Collaborative Intelligence, ICMSCI 2026</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>1587-1592</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105037952713?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Emergency Response, Incident Detection, Public Safety, Real-time Monitoring, Situational Awareness, Smart Cities, Urban Intelligence, Civil defense, Constrained optimization, Decision making, Emergency services, Emergency traffic control, Highway accidents, Highway traffic control, Intelligent systems, MATLAB, Visual analytics, Incident response, Multi-modal, Prioritization</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>This MobileNet-powered incident detection and prioritization of response to different incidents in a smart city setup through MATLAB and camera images in real-time. The system takes advantage of the low and compressed MobileNet framework to introduce on-the-fly categorization of urban incidents as standard or irregular, such as road accidents, traffic jam, and unauthorized usage. The model supports a high detection accuracy with a low computational complexity by using optimized depthwise separable convictions and transfer learning, allowing it to run in resource- and edge-constrained devices.</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, framework, model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Influence diagrams in cyber security: Conceptualization and potential applications</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Chockalingam S.; Maathuis C.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>10.34190/eccws.22.1.1303</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>European Conference on Information Warfare and Security, ECCWS</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2023-June</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>124-131</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85167602153?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Curran Associates Inc.</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Cyber security, Decision making, Graphical model., Incident response, Influence diagrams, Artificial intelligence, Bayesian networks, Computer crime, Crime, Cybersecurity, Decision support systems, Graphic methods, Network security, Cyber-attacks, Decisions makings, Emerging technologies, Influence diagram, Informed decision, Securities analysts</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Over the last years, cyber-Attacks are increasing in organizations especially due to the use of emerging technologies and transformation in terms of how we work. Informed decision-making in cyber security is critical to prevent, detect, respond, and recover from cyber-Attacks effectively and efficiently. In cyber security, Decision Support System (DSS) plays a crucial role especially in supporting security analysts, managers, and operators in making informed decisions.</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, artificial intelligence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Cross-Attention Feature Fusion for Interpretable Zero-Day MalwareDetection</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Aljarrah N.; Shehadeh H.H.; Obeidat R.A.; Tawfik M.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>10.19139/soic-2310-5070-2900</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Statistics, Optimization and Information Computing</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>3</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2164-2178</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105029956072?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>International Academic Press</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Cross-Attention, Cybersecurity, Explainable AI, Feature Fusion, Malware Detection, Zero-Day Attacks, international, global, incident response, processes, models, machine learning, deep learning, artificial intelligence, classification, detection, malware, datasets, framework</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>The exponential proliferation of sophisticated zero-day malware variants poses critical challenges to traditional signature-based detection systems, necessitating advanced machine learning approaches that combine high-performance classification with transparent decision-making processes. While existing deep learning models achieve remarkable accuracy in malware detection, their black-box nature severely limits adoption in critical cybersecurity applications where interpretability is paramount for threat analysis and incident response. This work presents a novel cross-attention feature fusion architecture integrated with comprehensive explainable artificial intelligence (XAI) techniques for...</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: models, machine learning, deep learning, artificial intelligence, classification, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>AI-Augmented SOC: A Survey of LLMs and Agents for Security Automation</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Srinivas S.; Kirk B.; Zendejas J.; Espino M.; Boskovich M.; Bari A.; Dajani K.; Alzahrani N.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F72" t="n">
+        <v>7</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>10.3390/jcp5040095</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Journal of Cybersecurity and Privacy</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>4</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105025932451?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Multidisciplinary Digital Publishing Institute (MDPI)</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>AI agent, cybersecurity automation, human-AI collaboration, Large Language Models, security operation center, management, incident response, soc, processes, model, models, artificial intelligence, detection</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>The increasing volume, velocity, and sophistication of cyber threats have placed immense pressure on modern Security Operations Centers (SOCs). Traditional rule-based and manual processes are proving insufficient, leading to alert fatigue, delayed responses, high false-positive rates, analyst dependency, and escalating operational costs. Recent advancements in Artificial Intelligence (AI) offer new opportunities to transform SOC workflows through automation and augmentation.</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: soc, management, incident response, processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>The Integration of Stream Data Models in Modern Transportation Networks</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Naval P.; Jain S.K.; Krishna K.G.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>10.1109/ICTBIG59752.2023.10456023</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3rd IEEE International Conference on ICT in Business Industry and Government, ICTBIG 2023</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85189242290?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Commuter Satisfaction, Data Accuracy, Dynamic Routing, Environmental Impact, Incident Response, Network Efficiency, Predictive Analytics, Real-Time Data Processing, Transportation Networks, Application programs, Data mining, Decision making, Digital storage, Traffic control, Travel time, Urban transportation, Stream data, Transport networks, Transportation network, Wait time</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>The study proposal proposes an innovative strategy for managing modern transport networks, with an emphasis on the coordinated use of analytics, real-time data processing, and dynamic decision-making utilizing stream data models. To create a solid infrastructure for real-time data analysis, it is required to use a diverse set of data sources, such as sensors, GPS devices, traffic cameras, and mobile application software. A strategy for reaching this goal is described below.</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: models, algorithms, machine learning, artificial intelligence, prediction, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Explainable AI and Block chain for Cyber Resilient Online Retail: A Framework for Enhanced Security and Trust</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Syed Abuthahir S.; Jagan Naik G.; Damodhar Rao K.; Venkata Naga Ramesh J.; Jangir P.; Prasanth Kumar K.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>IAENG International Journal of Computer Science</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>9</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>3237-3249</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105016094129?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>International Association of Engineers</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Blockchain technologies, Cyber resilience, Explainable deep learning, Online retailing platforms, Operations continuity, Behavioral research, Cybersecurity, Decision making, Deep learning, Network security, Block-chain, Blockchain technology, Cybe resilience, Decisions makings, Online retailing, Online retailing platform, Online retails, Operation continuity, Security and trusts, national</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Online retail platforms frequently encounter challenges such as cyberattacks, data breaches, device malfunctions, and operational disruptions. These issues have intensified in recent years, highlighting the urgent need for businesses to prioritize resilience. Traditional cybersecurity systems are increasingly ineffective against sophisticated cyber threats.</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: framework, deep learning, detection, datasets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Incident Response ChatOps Bot with Automated Dynamic Playbooks for Threat Mitigation</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Decha N.; Chantakhad A.; Ponglimagorn P.; Imsaard S.; Fugkeaw S.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.1109/KST67832.2026.11432408</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>KST 2026 - 18th International Conference on Knowledge and Smart Technology</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>652-658</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105036830399?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>automation, ChatOps bot, dynamic playbook, Gemini, incident response, threat mitigation, Artificial intelligence, Behavioral research, Bot (Internet), Botnet, Chatbots, Decision making, Intelligent agents, Markup languages, Network security, Application security, Chat-based operation bot, Common vulnerabilities and exposures, Cyber-attacks, Geminus</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Cyberattacks have become increasingly complex, exploiting vulnerabilities such as those listed in the Open Worldwide Application Security Project (OWASP) Top 10 to compromise systems and delay response times. Traditional incident response (IR) still depends heavily on manual procedures, which are prone to human error and slow mitigation. To address this challenge, this project proposes an AI-driven ChatOps (chat-based operations) Incident Response Bot that integrates automation, dynamic playbooks, and human-in-the-loop decision-making.</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: incident response, organizational, decision making.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>South East Water holistic catchment based monitoring and operational modelling</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Hydrology and Water Resources Symposium, HWRS 2022</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>590-598</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85150621750?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Engineers Australia</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Decision Support Systems, Incident Management, Managing discharge of contaminated water, Predictive Operational Models, Real-time Event Forecasting and Warning, Artificial intelligence, Catchments, Decision making, Hazardous materials spills, Real time systems, Runoff, Water pollution, Weather forecasting, Contaminated water, Operational modeling, Predictive operational model, Pump station, Real- time, Time event, Toolsets</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Elster Creek is a low-lying coastal catchment that historically suffered from surcharging, localised spills, and discharge to emergency relief structures (ERS) during extreme weather events. Previously, South East Water (SEW) had no means of prediction or early warning for these events; as a result, intervention could not be taken to mitigate the consequences. In addition to wet weather issues at Elster Creek, the whole of SEW network experiences occasional pump station power failures and dry weather pipe blockages.</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, models, artificial intelligence, prediction, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>XAINTRUDER: An Explainable Deep Neural Network-Based Intrusion Detection System for Real-Time Cyber Threats</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Rasmika G.V.; Madhumathi C.S.; Srinivasan L.; Suganya R.T.; Savithadevi T.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>10.1109/ICRTEECT67512.2025.11448726</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>ICRTEECT 2025 - 2nd International Conference on Recent Trends in Electrical, Electronics and Computing Technologies</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105037329786?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Adversarial Training, Concept Drift Detection, Deep Neural Networks (DNN), Explainable Artificial Intelligence (XAI), Graph Attention Network (GAT), Intrusion Detection System (IDS), Temporal Convolutional Network (TCN), Computation theory, Computer crime, Convolution, Convolutional neural networks, Intrusion detection, Network architecture, Network intrusion, Network security, Concept drifts, Convolutional networks, Deep neural network, Graph attention network, Intrusion detection system</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Deep Neural Networks (DNN)-based Intrusion Detection Systems (IDS) can identify advanced cyber threats with high precision but are typically opaque, which restricts the implementation of these systems in operational Security Operations Center (SOCs). Lack of transparency lowers the confidence of the analyst and prevents the efficient incident response. The paper presents the explainable DNN-based IDS named XAINTRUDER, which is a system of real-time cyber threat detection, which combines high classification with multi-level explainability.</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: neural network, detection, intrusion detection, model, models, artificial intelligence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Integrating Artificial Intelligence and Zero Trust Principles in Cloud Forensics and Incident Response: A Comprehensive Review</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Kaur B.; Gupta S.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>10.1109/ISCS69371.2025.11386291</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2nd International Conference on Intelligent Systems for Cybersecurity, ISCS 2025</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105034869481?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Cloud Forensics, Cloud Security, Cyber Resilience, Digital Forensics, Forensic Automation, Incident Response, Machine Learning, Threat Detection, Zero Trust Security, Computer crime, Computer forensics, Decision making, Electronic crime countermeasures, Forensic engineering, Learning systems, Network security, Trusted computing, Cloud securities, Cybe resilience</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>The rapid expansion in the domain of cloud computing has significantly changed digital infrastructures by improving scalability, flexibility, and cost-effectiveness. However, this evolution has introduced new caveats for digital forensics because of data distribution, changing environments, and multi-tenant architecture. This paper presents the AI-driven Zero Trust Cloud Forensics and Incident Response (AIZT-CFIR) framework.</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, machine learning, detection, threat detection, framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning with AI for Autonomous Incident Response in DevSecOps: Using RL Agents to Detect, Classify, and Mitigate Security Threats in Cloud-Native DevOps Environments</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Gunawat C.; Nankani J.S.; Gupta R.K.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-032-14044-9_30</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Lecture Notes in Networks and Systems</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>1772 LNNS</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>366-381</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105030869704?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Springer Science and Business Media Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Autonomous incident response, Reinforcement learning, Threat detection, Autonomous agents, Decision making, DevOps, Intelligent agents, Security systems, Artificial intelligence learning, Incident response, Learning frameworks, Machine-learning, Reinforcement learning agent, Reinforcement learning approach, Reinforcement learnings, Security threats, process, machine learning, artificial intelligence, detection</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>In this paper, we provide a complete framework to operationalize security automation in DevSecOps utilizing Artificial Intelligence (AI) and Machine Learning (ML) with a focus on Reinforcement Learning (RL) approaches. The paper describes the development of a RL framework to enable autonomous and adaptive incident response in a Cloud-native environment. Our RL-based framework utilizes intelligent agents that discover, classify, and mitigate security threats autonomously and learn, improve, and apply their detection and response abilities in the continuous learning process autonomously.</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, artificial intelligence, detection, threat detection, framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Improving Cyber Security Incident Response: A Collaborative Tabletop Game Approach</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Seiler A.; Lechner U.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-94924-1_9</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>IFIP Advances in Information and Communication Technology</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>742 IFIPAICT</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>124-139</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105012918785?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Springer Science and Business Media Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>critical infrastructure, incident response, serious game, tabletop exercise, Decision making, Distributed computer systems, Game design, Human computer interaction, Information systems, Information use, Intelligent systems, Network security, Public works, Cyber security, De facto standard, Game approach, Incident response phase, IT networks, Response process, Security incident</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>This paper explores the potential of a collaborative tabletop game called Operation Raven to improve incident response processes for critical infrastructure. The game material consists of a game board representing the IT network of a critical infrastructure, various cards, and structured response cards to simulate cyber security incident scenarios. The game introduces hypotheses as a collaborative basis for response actions.</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: incident response, decision making, process, processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>QuickSAT/SHERLOCK, An AI Architecture For Vehicle Health Management, Fault Detection and Fault Management For Small Satellites</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Santangelo A.D.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>10.2514/6.2026-0790</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>AIAA Science and Technology Forum and Exposition, AIAA SciTech Forum 2026</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105031181687?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>American Institute of Aeronautics and Astronautics Inc, AIAA</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Anomaly detection, Aviation, Data handling, Fault detection, Industrial management, Information analysis, Interplanetary flight, Knowledge based systems, Knowledge management, Orbits, Safety engineering, Small satellites, Space platforms, Vehicle detection, Assembly operations, Fault classification, Fault management, Faults detection, In-orbit servicing, Management functions</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>sci_Zone, Inc is conducting research to develop QuickSAT/SHERLOCK, a system for Vehicle Health Management, Fault Management and Fault Detection with Fault Classification Functions for deep space satellites, human-rated space vehicles, vehicles operating other terrestrial surfaces and small satellites including those in support of In-Orbit Servicing, Assembly and Manufacturing (ISAM) operations and other mission goals. The QuickSAT/Vehicle Management System (VMS) is a flight proven flight management, Vehicle Health Management plus Fault Detection system flown on DARPA and U.S. Space Force flights and scheduled for flights in 2029.</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, artificial intelligence, classification, anomaly detection, framework, module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>The role of generative AI in cyber security</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Curran K.; Curran E.; Killen J.; Duffy C.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F82" t="n">
+        <v>5</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>10.54517/m.v5i2.2796</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Metaverse</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>2</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2796</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105004234856?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Asia Pacific Academy of Science Pte Ltd</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, cybersecurity, GenAI, Generative AI, incident response, processes, machine learning, detection, threat detection</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>In the ever-evolving landscape of cyber threats, the integration of Artificial Intelligence (AI) has become popular into safeguarding digital assets and sensitive information for organisations throughout the world. This evolution of technology has given rise to a proliferation of cyber threats, necessitating robust cybersecurity measures. Traditional approaches to cybersecurity often struggle to keep pace with these rapidly evolving threats.</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, artificial intelligence, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Human-AI Collaboration and Cyber Security Training: Learning Analytics Opportunities and Challenges</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Maennel K.; Maennel O.M.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F83" t="n">
+        <v>3</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>10.1109/SIN63213.2024.10871610</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2024 17th International Conference on Security of Information and Networks, SIN 2024</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/86000033097?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>artificial intelligence, cyber security, education, human-AI collaboration, incident response, learning analytics, Cyber attacks, Federated learning, Complex decision, Cyber security exercise, Cyber security trainings, Cyber-defense, Exponential growth, Global threats, Human-artificial intelligence collaboration, Learning analytic, Adversarial machine learning, global, processes, model</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Cyber security is becoming more complex due to the exponential growth of interconnected systems and the global threat landscape. To mitigate those risks, there is a need for a skilled cyber security workforce that can navigate the complex decision-making in rapidly evolving cyberspace. Artificial intelligence (AI) is rapidly adopted into cyber defence operations, but we can not effectively train human and AI-assisted cyber defence operators without understanding the underlying learning theory and eco-systems.</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, machine learning, artificial intelligence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Digital technologies in the system of state economic security management</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Kryvonos L.; Logvynenko S.; Zhurba O.; Kukin I.; Pynda Y.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>10.21533/pen.v14.i1.1527</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Periodicals of Engineering and Natural Sciences</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>141-166</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105032432900?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>International University of Sarajevo</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Cyber Resilience, Digitalization, Economic Security, Multi-Criteria Analysis, Ukraine, national, economic, government, management, incident response, security operations center, artificial intelligence, detection, phishing, malware, framework</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>This study investigates how digital technologies can strengthen Ukraine’s system of economic security management under conditions of war, reconstruction, and escalating cyber threats. The research applies systems analysis, strengths-weaknesses-opportunities-threats analysis, comparative benchmarking with Estonia, Lithuania, and Poland, and an evidence-informed modeling framework. An Economic Security Digitalization Index is constructed from the United Nations E-Government Development Index and the Network Readiness Index, and seven candidate technologies are evaluated: a Government Security Operations Center with Security Information and Event Management and Security Orchestration,...</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, detection, phishing, malware, framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>An Integration of Digital Twin and 6G Edge Computing Approach to Secure Cyber Physical Systems</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Suganya R.; Kiran A.; Akila D.; Spandana S.; Rajagopal M.; Nageswaran A.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F85" t="n">
+        <v>17</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>10.1007/s11277-024-11181-5</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Wireless Personal Communications</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85194576350?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Springer</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>6G, Cyber physical systems, Digital twin, Edge of Things, Optimization, Security, Cybersecurity, Decision making, Edge computing, Embedded systems, Emergency services, Learning algorithms, Machine learning, Network security, Cybe-physical systems, Cyber-physical systems, Edge of thing, Optimisations, Proposed architectures, Smart devices</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>The proposed architecture for the 6G Edge of Things (EoT) system integrates two distinct networks: the EoT network and the digital twin (DT) network. The EoT network consists of interconnected smart devices and sensors organized into layers of things, edges, and clouds. Edge computing nodes facilitate low-latency services, emergency responses, and real-time decision-making, while the central cloud layer manages resource-intensive tasks.</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: algorithms, models, machine learning, detection, threat detection, module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Assessing the Frontiers of SIEM Technology: A Rigorous Evaluation and Validation of Innovative Features in SIEM Solutions</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Akbas E.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>10.1145/3704391.3704395</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>ITCC 2024 - 2024 6th International Conference on Information Technology and Computer Communications, ITCC 2024</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>21-29</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85218418595?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Association for Computing Machinery, Inc</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Big Data, Correlation Engine, Cyber Security, Event Correlation, Incident Response, Log, Machine Learning, Security Information and Event Management, Security Operation Center, Threat Detection, Cyber attacks, Risk management, Laws and regulations, Machine-learning, Security information and event managements, Information management, industry, management</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Security Information and Event Management (SIEM) systems play a crucial role in modern cybersecurity by aggregating, correlating, and analyzing vast amounts of security data. As cyber threats continue to evolve, the demand for Next-Generation SIEMs (NG-SIEMs) has grown, promising advanced features and enhanced capabilities. There are dozens of studies related to the analysis and comparison of SIEM solutions in academia and industry, but none of them have examined these analyses in terms of existing laws and regulations related to SIEM worldwide.</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, incident response, risk management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>The vigilance paradox: automation reliance inside the modern SOC</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Tilbury J.; Flowerday S.V.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>10.1108/ICS-08-2025-0318</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Information and Computer Security</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>1-24</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105027400123?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Emerald Publishing</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Automation, Bias, Complacency, Human-Automation Interaction, Security Operations Center, Artificial intelligence, Behavioral research, Human computer interaction, Information use, Least squares approximations, Life cycle, Man machine systems, Security systems, Automation bias, Cognitive factors, Design/methodology/approach, Human-automation interactions, Large scale surveys, Mixed method, Securities analysts</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Purpose – The purpose of this study is to measure how susceptible security analysts are to these cognitive factors. Automation and artificial intelligence (AI) are increasingly leveraged in Security Operations Centers (SOCs) to assist security analysts in managing growing alert volumes and escalating threats. However, their rapid integration introduces the cognitive risks of automation complacency (AC) which can lead to automation bias (AB) among security analysts.</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: algorithm, model, models, artificial intelligence, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>The Risk Operations Center (RoC): A Unified Framework for Proactive, Business-Aligned Cyber Risk Management</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Singh J.P.; Das S.; Verma N.; Katheria S.; Joshi S.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>10.1109/ICSES66558.2026.11478902</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Proceedings - ICSES 2026: 5th International Conference on Innovative Computing, Intelligent Communication and Smart Electrical Systems</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105038326922?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Adaptive decision-making, AI-driven cybersecurity, Cognitive threat modeling, Enterprise Knowledge Graph, Explainable reinforcement learning, Predictive analytics, Risk Operations Center, Bayesian networks, Cybersecurity, Decision making, Deep learning, Inference engines, Intelligent agents, Intelligent systems, Knowledge management, Network security, Neural networks, Risk assessment, Risk management, Adaptive decision making</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>As cybersecurity threats continue to grow in complexity, dynamism and business impact, the demand for advanced intelligence systems that move beyond reactive detection methods grows. Traditional Security Operations Centers (SOCs) are typically not predictive, aligned with the business and agile enough to adapt to changing threats with delayed responses, operational inefficiencies and residual enterprise risk. This study plans to design and assess an AI-driven Risk Operations Center (RoC) based on multi-source data aggregation, cognitive threat modeling, predictive and prescriptive analytics, business context alignment, and explainable reinforcement learning to improve proactive cyber risk...</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: business, management, risk management, enterprise, decision making, incident response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Detection of Network Intrusions Using Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>MacEdo A.M.; Magalhaes J.P.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>10.1109/AICCSA59173.2023.10479349</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Proceedings of IEEE/ACS International Conference on Computer Systems and Applications, AICCSA</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85190131453?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>IEEE Computer Society</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Automation, Incident, Recovery, Security, Security Operations Center, Anomaly detection, Computer crime, Cybersecurity, Digital forensics, Machine learning, Central point, Cyber security, Cyber-attacks, Machine-learning, Network intrusions, Security operation center, Security threats, Network security, incident response</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>The proliferation and widespread use of new technologies has inevitably brought an increase in the occurrence of cyber-attacks. The adoption of cybersecurity technologies and policies are increasingly a central point that requires innovative and appropriate solutions. This paper proposes a solution that aims to help organisations to identify, detect, manage, and respond to security threats assertively and timely.</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, anomaly detection, machine learning, artificial intelligence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>LE2C: LLM-Enhanced Event Evolutionary Graph for Explainable Classification</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Liang J.; Wu S.; Wang X.; Niu J.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>10.1007/978-981-95-5719-6_23</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Lecture Notes in Computer Science</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>16115 LNCS</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>357-372</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105029827215?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Springer Science and Business Media Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Event Evolutionary Graph, Explainable Multi-label Classification, Knowledge Discovery, Large Language Model, Classification (of information), Decision making, Graphic methods, Intelligent systems, Knowledge graph, Knowledge management, Learning systems, Semantics, Customer service management, Decisions makings, Events classification, Incident response, Language model, Multi-label classifications, Multi-labels, Directed graphs</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>In the development of intelligent systems, multi-label event classification plays a vital role in enabling accurate decision-making across diverse scenarios such as incident response, customer service, and urban management. Although existing graph-based approaches for multi-label classification have shown potential, they struggle to model directed label dependencies and lack explainability, resulting in black-box decision-making processes. To address these issues, we propose a novel LLM-enhanced Event Evolutionary graph for Explainable Classification (LE2C) method.</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: classification, model, models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>IP SafeGuard-An AI-Driven Malicious IP Detection Framework</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Siam A.A.; Alazab M.; Awajan A.; Hasan M.R.; Obeidat A.; Faruqui N.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>10.1109/ACCESS.2025.3569289</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>90249-90261</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105005320495?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>artificial intelligence, cyber attack, cyber defense, Cyber security, IP address, SOC, threat intelligence, Computer viruses, Cyber attacks, Search engines, Critical challenges, Cyber-attacks, Cyber-defense, Detection framework, Machine-learning, Real- time, Security operation center, Federated learning, management, incident response</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>The rising frequency and sophistication of cyberattacks have made real-time malicious IP detection a critical challenge for modern Security Operations Center (SOC). Traditional solutions, such as static blacklists and manual IP reputation checks, are no longer sufficient in today's dynamic threat scenario. To overcome these constraints, we present IP SafeGuard, an AI-driven platform that incorporates multi-source threat intelligence, sophisticated feature engineering, and machine learning (ML)for real-time IP categorization.</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, framework, model, machine learning, artificial intelligence, classification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Towards Data Science for Cybersecurity: Machine Learning Advances as Glowing Perspective</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Mihailescu M.I.; Nita S.L.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-16078-3_2</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Lecture Notes in Networks and Systems</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>543 LNNS</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>26-48</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85138264119?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Springer Science and Business Media Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Artificial intelligence, Cyber threat intelligence, Cybersecurity, Data science, Decision making, Deep learning, Intrusion detection, Machine learning, incident response, model, framework</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>The current computing context has developed important opportunities and challenges by the new attacks that occurred recently due to the pandemic situation (COVID-19), cybersecurity has crossed and still passing through significant changes by the technology and its operation. Many computer security incident response teams (CSIRT) and cybersecurity centers had reported significant behaviors of the attacks and they raised multiple warning signs, some of them being ignored by different third parties and others were taken into consideration and new frameworks started to be translated into research directions as a cross-collaboration between researchers and professionals. As a conclusion of...</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, model, deep learning, artificial intelligence, detection, intrusion detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>The Role of Artificial Intelligence in Enhancing Cybersecurity: Trends, Challenges, and Ethical Considerations</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Serafim G.M.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>10.1007/978-981-96-8632-2_1</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Lecture Notes in Networks and Systems</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>1513 LNNS</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>3-24</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105028290178?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Springer Science and Business Media Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>AI-powered cyber-attacks, Cyber threat intelligence, Ethical AI governance human-AI teaming, Predictive security analysis, SOCs, Anomaly detection, Behavioral research, Computer crime, Crime, Cybersecurity, Deep learning, Ethical aspects, Internet of things, Learning algorithms, Learning systems, Network security, Artificial intelligence-powered cybe-attack, Cybe threat intelligence, Cyber security, Cyber threats</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>The increasing integration of Artificial Intelligence (AI) in the Cybersecurity domain has changed the way that countries defend themselves against ever-evolving and dynamic threats. This paper provides a broad survey of the use of AI in Cybersecurity, focusing on the new and emerging trends, the main issues, and the need for ethical steering (Harshith J, Gill MS, Jothimani M (2023) Evaluating the Vulnerabilities in ML systems in terms of adversarial attacks. arXiv preprint arXiv:2308.12918.</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, algorithms, models, machine learning, deep learning, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>An Integrated Approach to AI-Enhanced Security Information and Event Management</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Mugeshwaran K.; Maharajan K.; Nithish D.; Dinesh S.; Uday N.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>10.1109/ICCRTEE64519.2025.11053120</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>International Conference on Computational Robotics, Testing and Engineering Evaluation, ICCRTEE 2025</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105012172245?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>adaptive threat defense, AI-driven security event processing, AI-powered SIEM, automated incident response, deep learning security analytics, Innovation &amp; Infrastructure, machine learning for cybersecurity, real-time threat detection, Resilient Digital Infrastructure, Secure &amp; Sustainable Societies, Security information and event management (SIEM), Computer architecture, Cybersecurity, Learning systems, Machine learning, Network security, Security systems, Systems analysis, Artificial intelligence-driven security event processing, Artificial intelligence-powered security information and event management</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>An SIEM system enabled by Artificial Intelligence (AI) was proposed to solve the major challenges of current security monitoring practices. The proposed architecture incorporates the use of artificial intelligence at all levels of the security operation center to transform traditional security operations from passive detection to active protection. The system design incorporates the application of machine learning for pattern recognition, contextual analysis, and alert prioritization to overcome the major challenges of traditional SIEM solutions that are based on rules and produce numerous alerts.</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, deep learning, artificial intelligence, detection, threat detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Application of Large Language Models for Cybersecurity of Power Distribution Grids: Challenges and Opportunities</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Rahman M.M.; Rahman A.; Sun W.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>10.1109/NAPS66256.2025.11272351</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2025 57th North American Power Symposium, NAPS 2025</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105030501856?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Cyber-physical power system, cybersecurity, human-in-the-loop, large language model, vulnerability, Artificial intelligence, Cyber Physical System, Electric power system security, Embedded systems, Learning systems, Network security, Probability distributions, Cybe-physical power system, Cyber physicals, Cyber security, Domain specific, Language model, Physical power, Threat detection, Predictive analytics</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>This paper explores the application of domain-specific large language models (LLMs) as a transformative approach to enhancing cybersecurity in power distribution networks. We propose a comprehensive framework that integrates LLMs with existing grid infrastructure to enable predictive analytics, proactive vulnerability assessment, intelligent threat detection, and automated incident response. By incorporating reinforcement learning (RL) agents and a human-in-the-loop mechanism, the framework supports robust and trustworthy decision-making.</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: models, model, artificial intelligence, detection, threat detection, framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>LLMs for Cybersecurity in the Big Data Era: A Comprehensive Review of Applications, Challenges, and Future Directions</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Karras A.; Theodorakopoulos L.; Karras C.; Theodoropoulou A.; Kalliampakou I.; Kalogeratos G.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F96" t="n">
+        <v>7</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>10.3390/info16110957</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Information (Switzerland)</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>11</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105023160557?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Multidisciplinary Digital Publishing Institute (MDPI)</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>adversarial attacks, AI-powered cybercrime, big data, cyber threat intelligence, cybersecurity, decision-making, ethical AI, explainable AI (XAI), governance, human–AI collaboration, incident response, large language models (LLMs), security analytics, threat detection, Artificial intelligence, Computer crime, Cyber attacks, Data integration, Decision making, Network security</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>This paper presents a systematic review of research (2020–2025) on the role of Large Language Models (LLMs) in cybersecurity, with emphasis on their integration into Big Data infrastructures. Based on a curated corpus of 235 peer-reviewed studies, this review synthesizes evidence across multiple domains to evaluate how models such as GPT-4, BERT, and domain-specific variants support threat detection, incident response, vulnerability assessment, and cyber threat intelligence. The findings confirm that LLMs, particularly when coupled with scalable Big Data pipelines, improve detection accuracy and reduce response latency compared with traditional approaches.</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, models, artificial intelligence, detection, threat detection, bert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Serious Games for Cybersecurity: How to Improve Perception and Human Factors</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Barletta V.S.; Calvano M.; Caruso F.; Curci A.; Piccinno A.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F97" t="n">
+        <v>9</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>10.1109/MetroXRAINE58569.2023.10405607</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2023 IEEE International Conference on Metrology for eXtended Reality, Artificial Intelligence and Neural Engineering, MetroXRAINE 2023 - Proceedings</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>1110-1115</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85185784224?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>cybersecurity, Explainable AI, human factors, serious game, Behavioral research, Decision making, Domain Knowledge, Human engineering, Risk management, Behaviour models, Cognitive model, Cyber security, Cyber threats, Dark web, Digital economy, Explainable artificial intelligence, Research analysis, Technological innovation, Threat detection, Serious games</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Cybersecurity is a growing problem in today's technological innovation and new digital economy. Threat actors cause a danger to people's safety or lead to the compromise of intellectual property, either sold on the dark web or used as leverage for ransom. Many executives believe cybersecurity is the responsibility of Information Technologies (IT).</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: management, decision making, incident response, processes, risk management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Analysis of Explainable Artificial Intelligence Methods in Security Information and Event Management Systems</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Bulgakova E.V.; Vasilevskiy P.A.; Doynikov D.S.; Kubankov A.N.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>10.1109/IEEECONF64229.2025.10948089</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2025 Systems of Signals Generating and Processing in the Field of on Board Communications, SOSG 2025 - Conference Proceedings</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105003211873?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>AI, cyber threats, cybersecurity, incident response, information security, LIME, threat detection, XAI SIEM, Decision making, Information management, Artificial intelligence methods, Cyber security, Data volume, Information security systems, Intelligence models, Security information and event management systems, Cyber attacks, management, processes, models</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>The present article engages with the ongoing discourse surrounding the implementation of artificial intelligence and explainable artificial intelligence within the domain of information security systems. In the context of escalating cyber threats and mounting data volumes, conventional defense methodologies are proving to be inadequate. Consequently, the integration of artificial intelligence has emerged as a pivotal strategy to enhance the efficacy of threat detection and response processes.</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, models, detection, threat detection, model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Advancing the Threat Intelligence with AI: An Overview, Taxonomy and Roadmap</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Tomičić I.; Grd P.; Bernik A.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>10.3897/jucs.137544</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Journal of Universal Computer Science</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>10</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>1102-1129</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105014981591?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>IICM</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Cybersecurity, Incident Response, SOC, Threat Detection, Threat Intelligence, processes, workflow, machine learning, deep learning, classification, prediction, detection, framework</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>This paper presents a comprehensive analysis of the integration of artificial intelligence (AI) into threat intelligence (TI) systems, focusing on its potential to enhance cybersecurity operations. The paper presents an extensive literature review, covering the current state of AI applications in TI, including machine learning, deep learning, and natural language processing for automating threat detection, classification, and analysis. It outlines the core functions of AI in TI, such as threat detection, correlation, prediction, and automated response, and introduces a detailed taxonomy categorizing AI techniques based on their roles in enhancing TI processes.</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, deep learning, artificial intelligence, classification, prediction, detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>AI-Driven Threat Intelligence for Predictive Cyber Defense in Smart Cities</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Nagpal M.; Singh R.P.; Shubneet; Yadav A.R.; Siwach P.; Talwandi N.S.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-032-17020-0_23</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Communications in Computer and Information Science</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2854 CCIS</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>362-372</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105030325187?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Springer Science and Business Media Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>AI-Driven Threat Intelligence, Federated Learning, Predictive Cyber Defense, Smart City Security, Zero-Day Attacks, Anomaly detection, Artificial intelligence, Blockchain, Critical infrastructures, Cybersecurity, Data privacy, Malware, Network security, Predictive analytics, Public works, Resource allocation, City securities, Cyber security, Cyber-defense, Polymorphic malware</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Smart cities are rapidly embracing interconnected IoT devices and critical infrastructure, expanding the complexity and vulnerability of urban cyberspace. Conventional cybersecurity remains largely reactive and signature-based, falling short against advanced attacks such as zero-day exploits and polymorphic malware. This research introduces a novel AI-driven threat intelligence framework for predictive cyber defense in smart city environments that integrates federated learning for privacy-preserving analytics, blockchain-secured data provenance for immutable logging, and real-time anomaly detection to anticipate and mitigate threats across municipal networks.</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, detection, threat detection, anomaly detection, malware, benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>QuickSAT/SHERLOCK, An AI Architecture For Vehicle Health Management, Fault Detection and Fault Management and complex Human-Machine Systems</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Santangelo A.D.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>10.2514/6.2026-0995</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>AIAA Science and Technology Forum and Exposition, AIAA SciTech Forum 2026</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105031158045?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>American Institute of Aeronautics and Astronautics Inc, AIAA</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Aerospace vehicles, Anomaly detection, Aviation, Data handling, Fault detection, Industrial management, Information analysis, Interplanetary flight, Knowledge based systems, Knowledge management, Man machine systems, Orbits, Risk perception, Safety engineering, Small satellites, Space platforms, Vehicle detection, Assembly operations, Fault classification, Fault management</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>sci_Zone, Inc is conducting research to develop QuickSAT/SHERLOCK, a system for Vehicle Health Management, Fault Management and Fault Detection with Fault Classification Functions for deep space satellites, human-rated space vehicles, vehicles operating other terrestrial surfaces and small satellites including those in support of In-Orbit Servicing, Assembly and Manufacturing (ISAM) operations and other mission goals. The QuickSAT/Vehicle Management System (VMS) is a flight proven flight management, Vehicle Health Management plus Fault Detection system flown on DARPA and U.S. Space Force flights and scheduled for flights in 2029.</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, artificial intelligence, classification, anomaly detection, framework, module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Generative AI in Cybersecurity: Threats, Vulnerabilities, and Protective Measures</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ugale S.P.; Sinha A.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>10.1109/ICFT66708.2025.11336288</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2025 International Conference on Future Technologies, ICFT 2025</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105033612768?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Cybersecurity, Deepfakes, Generative Adversarial Networks (GANs), Generative AI, Large Language Models (LLMs), Model Vulnerabilities, Behavioral research, Computer crime, Data privacy, Generative adversarial networks, Network security, Adversarial networks, Cyber security, Decisions makings, Deepfake, Generative adversarial network, Language model, Large language model, Model vulnerability, Protective measures</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence: Generation GenAI will turn entire industries on their heads because it can generate and simulate content, roleplaying or decision making. But in the case of cybersecurity, GenAI is a double-edged sword: It can strengthen defense systems even as it broadens the attack surface for bad actors. The rest of this paper is organized as follow: Section II presents an overview regarding the threats, vulnerabilities and countermeasure existed for cyber security from GenAI aspect.</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: model, models, artificial intelligence, phishing, malware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Vulnerability Assessment in Heterogeneous Web Environment Using Probabilistic Arithmetic Automata</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Moshika A.; Thirumaran M.; Natarajan B.; Andal K.; Sambasivam G.; Manoharan R.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F103" t="n">
+        <v>12</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>10.1109/ACCESS.2021.3081567</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>9433582</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85107126255?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Deterministic Arithmetic Automata (DAA), heterogeneous web application, probabilistic arithmetic automata (PAA), Security analytics, Automata theory, Decision making, Learning systems, Predictive analytics, Robots, Business enterprise, Incident response, Machine learning techniques, Probabilistic arithmetics, Security programs, Statistical datas, Vulnerability assessments, Vulnerability detection, Web services, enterprise, business</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>In the current scenario most of the business enterprises are running through web applications. But the major drawback is that they fail to provide a secure environment. To overcome this security issue in web applications, there are many vulnerability detection tools are available at present.</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: enterprise, business, decision making, incident response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Use of Explainable Artificial Intelligence for Analyzing and Explaining Intrusion Detection Systems</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Hermosilla P.; Díaz M.; Berríos S.; Allende-Cid H.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F104" t="n">
+        <v>7</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>10.3390/computers14050160</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Computers</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>5</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105006643982?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Multidisciplinary Digital Publishing Institute (MDPI)</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>forensic analysis, LIME, SHAP, TabNet, UNSW-NB15, XAI, XGBoost, Computer forensics, Forensic engineering, Intelligent computing, Intelligent systems, Decision-making process, Intrusion Detection Systems, Local interpretable model-agnostic explanation, Shapley, Shapley additive explanation, Deep learning, global, incident response, process</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>The increase in malicious cyber activities has generated the need to produce effective tools for the field of digital forensics and incident response. Artificial intelligence (AI) and its fields, specifically machine learning (ML) and deep learning (DL), have shown great potential to aid the task of processing and analyzing large amounts of information. However, models generated by DL are often considered “black boxes”, a name derived due to the difficulties faced by users when trying to understand the decision-making process for obtaining results.</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: artificial intelligence, detection, intrusion detection, model, models, machine learning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Protecting Public Safety and Critical Infrastructure Systems in Smart Cities via Cybersecurity: AI- Based Threat Detection and Response</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Sethi M.; Verma V.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>10.1109/GINOTECH63460.2025.11077039</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2025 Global Conference in Emerging Technology, GINOTECH 2025</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/105013619117?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers Inc.</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Adversarial attacks, AI-based threat detection, Anomaly detection, Critical infrastructure, Distributed systems, Federated learning, Incident response, Internet of Things (IoT), Machine learning, Public safety, Automation, Behavioral research, Civil defense, Cybersecurity, Data privacy, Denial-of-service attack, Distributed computer systems, Emergency services, Health care, Internet of things</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Smart cities are evolving rapidly (enhanced public safety, improved infrastructure management and optimized urban services) as IoT and automation technologies are embraced in urban spaces worldwide. Yet this very transformation exposes critical infrastructure systems to risks of cyberattacks unprecedented in scale and in nature. That said, safeguarding public safety within smart cities - especially at critical infrastructure sectors such as energy, transportation, health care, and emergency response - requires proactive measures against emerging cyber threats against both physical and digital infrastructures.</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, threat detection, algorithms, models, machine learning, deep learning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Security Tools' API Recommendation Using Machine Learning</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Sworna Z.T.; Sreekumar A.; Islam C.; Babar M.A.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Conferencia</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>10.5220/0011708300003464</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>International Conference on Evaluation of Novel Approaches to Software Engineering, ENASE - Proceedings</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>2023-April</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>27-38</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/publications/85160563783?origin=resultslist</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Science and Technology Publications, Lda</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>API Recommendation, Security Operation Center, Security Orchestration, Security Tools' API, Information use, Learning systems, Regression analysis, System-on-chip, Incident response, Learning models, Machine learning models, Security incident, Security tool' API, Security tools, State of the art, Deep learning, soc, model, models, machine learning</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Security Operation Center (SOC) teams manually analyze numerous tools' API documentation to find appropriate APIs to define, update and execute incident response plans for responding to security incidents. Manually identifying security tools' APIs is time consuming that can slow down security incident response. To mitigate this manual process's negative effects, automated API recommendation support is desired.</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, model, models, deep learning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>The impact of artificial intelligence on organisational cyber security: An outcome of a systematic literature review</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Irshaad Jada, Thembekile O. Mayayise</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F107" t="n">
+        <v>124</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>10.1016/j.dim.2023.100063</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Data and Information Management</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>2</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>100063</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.dim.2023.100063</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Elsevier BV</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Resilience (materials science), Computer security, Computer science, Process (computing), Knowledge management</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>In the past few years, advanced cyber security capabilities have flourished via a new era of use in dangerous A.I. technologies rapidly developed strategies using dozens of different online risks to even more effectively prevent, detect, and respond prolifically. With digital infrastructures being the backbone of enterprises today, cyber-attacks have grown in complexity and sophistication over time to thrive as we know them now this effectively means that security frameworks would need AI after that.</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: organisational, management, process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial en la toma de decisiones: implicaciones éticas y eficiencia</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ana Maritza Boy Barreto, Elvis Doberto Osorio Arrascue, Lino Rolando Rodríguez Alegre, Rosario del Pilar López Padilla</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F108" t="n">
+        <v>4</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>10.52080/rvgluz.29.e11.20</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Revista Venezolana de Gerencia</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Especial 11</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>342-355</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.52080/rvgluz.29.e11.20</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Universidad del Zulia</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Humanities, Political science, Philosophy</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>La inteligencia artificial (IA) ha emergido como una fuerza transformadora en el mundo contemporáneo, impactando de manera significativa la forma en que tomamos decisiones en una amplia gama de áreas. En el ámbito empresarial, la IA se ha convertido en una herramienta invaluable para optimizar la eficiencia operativa y mejorar la precisión en la toma de decisiones estratégicas. El uso de IA en la toma de decisiones plantea interrogantes sobre la transparencia de los algoritmos, la equidad en el acceso a las oportunidades y la responsabilidad en caso de decisiones erróneas o sesgadas.</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: toma de decisiones, business, organizational.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial en la gestión predictiva de incidentes de TI</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Luigui Jampierre Amaya Jave, Roger Alejandro Querevalú Galán, Alberto Carlos Mendoza de los Santos</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>10.48168/innosoft.s16.a177</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Innovación y Software</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>85-103</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.48168/innosoft.s16.a177</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Universidad La Salle Arequipa</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Computer science</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Esta revisión sistemática sintetiza la literatura sobre la aplicación de la inteligencia artificial (IA) en la gestión predictiva de incidentes de Tecnologías de la Información (TI). El estudio se enfoca en evaluar la capacidad predictiva de las soluciones basadas en IA y en identificar áreas de oportunidad para investigaciones futuras. Utilizando la metodología PRISMA, se realizaron búsquedas exhaustivas en bases de datos académicas utilizando ecuaciones de búsqueda específicas.</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: inteligencia artificial, detection, anomaly detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>El papel de la inteligencia artificial en la seguridad de la información: una revisión de su aplicación en la industria cibernética</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Josue Eduardo David Chavez Flores, Jean Carlos Joel Pacheco Guzmán, Alberto Carlos Mendoza de los Santos</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>10.15381/risi.v16i1.25390</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Revista de investigación de Sistemas e Informática</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>71-80</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.15381/risi.v16i1.25390</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Mayor de San Marcos, Vicerectorado de Investigacion</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Distrust, Computer science, Computer security, Workload, Automation</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>At present, the implementation of information technologies in organizations is increasingly common, since it benefits the development and automation of the processes they carry out; however, it is important to take into account that the incorporation of these technological solutions may affect the security of your systems and the information contained in them. This is where artificial intelligence can help organizations improve their ability to protect their sensitive information against possible cybersecurity threats, while reducing the workload on the teams in charge of it; however, executing this strategy comes with its own drawbacks, which organizations implementing it will need to...</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: business, management, processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Meso</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>The Intersection of Artificial Intelligence and Human Decision-Making in Cybersecurity Resilience: Business Analysis Perspective</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Blessing Unwana Umoh, Alliy Bello, Nonso Okika, Chioma Emmanuela Ukatu, Agboola Olatoye Kabiru</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>10.63084/cognexus.v1i02.58</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>CogNexus</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>26-36</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.63084/cognexus.v1i02.58</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Wenjibra University Press</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Intersection (aeronautics), Resilience (materials science), Perspective (graphical), Business intelligence, Computer science</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>This review investigated the complex interplay of Artificial Intelligence (AI) with human decision in building cybersecurity resilience from a business analysis viewpoint. It investigated how AI can optimize human decision-making, escalate security measures, and guarantee swift action in response to any form of cyber-attack while factoring in the contribution of human judgment, intuition, and oversight into consideration for intense decisions. This review further investigated the impact of automation AI on information technology security risks in conjunction with human strategic management, focusing on their collective role in enhancing and sustaining cybersecurity resilience in...</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>Clasificado como Meso por coincidencias en metadatos: business, decision making, management, risk management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Cutting-edge advances in AI and ML for cybersecurity: a comprehensive review of emerging trends and future directions</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Nachaat Mohamed</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F112" t="n">
+        <v>4</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Artículo</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>10.1080/23311975.2025.2518496</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Cogent Business &amp;amp; Management</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2518496</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/23311975.2025.2518496</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Informa UK Limited</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Enhanced Data Rates for GSM Evolution, Computer security, Computer science, Data science, Artificial intelligence</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>This review investigated the complex interplay of Artificial Intelligence (AI) with human decision in building cybersecurity resilience from a business analysis viewpoint. It investigated how AI can optimize human decision-making, escalate security measures, and guarantee swift action in response to any form of cyber-attack while factoring in the contribution of human judgment, intuition, and oversight into consideration for intense decisions. This review further investigated the impact of automation AI on information technology security risks in conjunction with human strategic management, focusing on their collective role in enhancing and sustaining cybersecurity resilience in...</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: machine learning, artificial intelligence, detection, intrusion detection, malware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Micro</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Journal of Internet Services and Information Security</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Jack Tilbury, Stephen Flowerday</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F113" t="n">
+        <v>93</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>10.58346/JISIS</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Computers</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.58346/jisis</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>SASA Publications</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>The Internet, Internet privacy, Information security, World Wide Web, Computer security</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>The volume and complexity of alerts that security operation center (SOC) analysts must manage necessitate automation. Increased automation in SOCs amplifies the risk of automation bias and complacency whereby security analysts become over-reliant on automation, failing to seek confirmatory or contradictory information. To identify automation characteristics that assist in the mitigation of automation bias and complacency, we investigated the current and proposed application areas of automation in SOCs and discussed its implications for security analysts.</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Clasificado como Micro por coincidencias en metadatos: detection, intrusion detection.</t>
         </is>
       </c>
     </row>
